--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.11</v>
+        <v>1.72</v>
       </c>
       <c r="O13" t="n">
-        <v>3.78</v>
+        <v>3.84</v>
       </c>
       <c r="P13" t="n">
-        <v>3.04</v>
+        <v>4.46</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2678,10 +2678,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2996,10 +2996,10 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="O11" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="P11" t="n">
-        <v>4.4</v>
+        <v>4.46</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>2.11</v>
+        <v>1.79</v>
       </c>
       <c r="O17" t="n">
-        <v>3.78</v>
+        <v>3.83</v>
       </c>
       <c r="P17" t="n">
-        <v>3.04</v>
+        <v>4.4</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G35" t="n">

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2360,10 +2360,10 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2996,10 +2996,10 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -3386,22 +3386,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N19" t="n">
@@ -3545,22 +3545,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N20" t="n">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU9"/>
+  <dimension ref="A1:AU35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,27 +588,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G2">
@@ -739,7 +739,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2026-07-27 13:00:00</t>
+          <t>2026-07-27 12:00:00</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Voluntari</t>
         </is>
       </c>
       <c r="G3">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>14.1</v>
+        <v>1.56</v>
       </c>
       <c r="O3">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="P3">
-        <v>1.18</v>
+        <v>5.51</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2026-07-27 13:00:00</t>
+          <t>2026-07-27 12:30:00</t>
         </is>
       </c>
     </row>
@@ -914,27 +914,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G4">
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC4">
         <v>0</v>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-07-27 14:00:00</t>
+          <t>2026-07-27 12:45:00</t>
         </is>
       </c>
     </row>
@@ -1077,27 +1077,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O5">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1169,10 +1169,10 @@
         <v>0</v>
       </c>
       <c r="AC5">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-07-27 14:00:00</t>
+          <t>2026-07-27 13:00:00</t>
         </is>
       </c>
     </row>
@@ -1240,27 +1240,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC6">
         <v>0</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-07-27 15:15:00</t>
+          <t>2026-07-27 13:00:00</t>
         </is>
       </c>
     </row>
@@ -1403,27 +1403,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G7">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-07-27 19:30:00</t>
+          <t>2026-07-27 13:00:00</t>
         </is>
       </c>
     </row>
@@ -1566,27 +1566,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-07-27 19:30:00</t>
+          <t>2026-07-27 13:00:00</t>
         </is>
       </c>
     </row>
@@ -1729,158 +1729,4396 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Poland 1. Liga</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Miedź Legnica</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Podbeskidzie</t>
+        </is>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>-1</v>
+      </c>
+      <c r="AN9">
+        <v>-1</v>
+      </c>
+      <c r="AO9">
+        <v>-1</v>
+      </c>
+      <c r="AP9">
+        <v>-1</v>
+      </c>
+      <c r="AQ9">
+        <v>0</v>
+      </c>
+      <c r="AR9">
+        <v>0</v>
+      </c>
+      <c r="AS9">
+        <v>0</v>
+      </c>
+      <c r="AT9">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2026-07-27 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Russia FNL</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>KAMAZ</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rotor Volgograd</t>
+        </is>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>-1</v>
+      </c>
+      <c r="AN10">
+        <v>-1</v>
+      </c>
+      <c r="AO10">
+        <v>-1</v>
+      </c>
+      <c r="AP10">
+        <v>-1</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2026-07-27 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Poland Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Zagłębie Lubin</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Piast Gliwice</t>
+        </is>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>-1</v>
+      </c>
+      <c r="AN11">
+        <v>-1</v>
+      </c>
+      <c r="AO11">
+        <v>-1</v>
+      </c>
+      <c r="AP11">
+        <v>-1</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2026-07-27 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Sweden Superettan</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Oddevold</t>
+        </is>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>-1</v>
+      </c>
+      <c r="AN12">
+        <v>-1</v>
+      </c>
+      <c r="AO12">
+        <v>-1</v>
+      </c>
+      <c r="AP12">
+        <v>-1</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2026-07-27 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Norway Eliteserien</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Rosenborg</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N13">
+        <v>1.79</v>
+      </c>
+      <c r="O13">
+        <v>3.83</v>
+      </c>
+      <c r="P13">
+        <v>4.4</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>-1</v>
+      </c>
+      <c r="AN13">
+        <v>-1</v>
+      </c>
+      <c r="AO13">
+        <v>-1</v>
+      </c>
+      <c r="AP13">
+        <v>-1</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2026-07-27 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Sweden Damallsvenskan</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Vittsjö</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Malmö FF W</t>
+        </is>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>-1</v>
+      </c>
+      <c r="AN14">
+        <v>-1</v>
+      </c>
+      <c r="AO14">
+        <v>-1</v>
+      </c>
+      <c r="AP14">
+        <v>-1</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2026-07-27 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Sweden Allsvenskan</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Häcken</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>AIK</t>
+        </is>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N15">
+        <v>2.11</v>
+      </c>
+      <c r="O15">
+        <v>3.78</v>
+      </c>
+      <c r="P15">
+        <v>3.04</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>-1</v>
+      </c>
+      <c r="AN15">
+        <v>-1</v>
+      </c>
+      <c r="AO15">
+        <v>-1</v>
+      </c>
+      <c r="AP15">
+        <v>-1</v>
+      </c>
+      <c r="AQ15">
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2026-07-27 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Denmark Superliga</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Randers</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Silkeborg</t>
+        </is>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N16">
+        <v>1.72</v>
+      </c>
+      <c r="O16">
+        <v>3.84</v>
+      </c>
+      <c r="P16">
+        <v>4.46</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>1.63</v>
+      </c>
+      <c r="AB16">
+        <v>2.1</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>0</v>
+      </c>
+      <c r="AG16">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
+        <v>0</v>
+      </c>
+      <c r="AK16">
+        <v>0</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>-1</v>
+      </c>
+      <c r="AN16">
+        <v>-1</v>
+      </c>
+      <c r="AO16">
+        <v>-1</v>
+      </c>
+      <c r="AP16">
+        <v>-1</v>
+      </c>
+      <c r="AQ16">
+        <v>0</v>
+      </c>
+      <c r="AR16">
+        <v>0</v>
+      </c>
+      <c r="AS16">
+        <v>0</v>
+      </c>
+      <c r="AT16">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2026-07-27 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Norway First Division</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Stabæk</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Hødd</t>
+        </is>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N17">
+        <v>1.55</v>
+      </c>
+      <c r="O17">
+        <v>4.65</v>
+      </c>
+      <c r="P17">
+        <v>4.69</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>1.85</v>
+      </c>
+      <c r="AD17">
+        <v>1.84</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>-1</v>
+      </c>
+      <c r="AN17">
+        <v>-1</v>
+      </c>
+      <c r="AO17">
+        <v>-1</v>
+      </c>
+      <c r="AP17">
+        <v>-1</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2026-07-27 14:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sweden Superettan</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Öster</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Varberg</t>
+        </is>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>-1</v>
+      </c>
+      <c r="AN18">
+        <v>-1</v>
+      </c>
+      <c r="AO18">
+        <v>-1</v>
+      </c>
+      <c r="AP18">
+        <v>-1</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2026-07-27 14:05:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Lithuania A Lyga</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Trakai</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>FA Šiauliai</t>
+        </is>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>canceled</t>
+        </is>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>-1</v>
+      </c>
+      <c r="AN19">
+        <v>-1</v>
+      </c>
+      <c r="AO19">
+        <v>-1</v>
+      </c>
+      <c r="AP19">
+        <v>-1</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2026-07-27 14:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Hungary NB I</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>MTK</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Zalaegerszegi TE</t>
+        </is>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>-1</v>
+      </c>
+      <c r="AN20">
+        <v>-1</v>
+      </c>
+      <c r="AO20">
+        <v>-1</v>
+      </c>
+      <c r="AP20">
+        <v>-1</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2026-07-27 14:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Iceland Úrvalsdeild</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Breidablik</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ÍBV</t>
+        </is>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>-1</v>
+      </c>
+      <c r="AN21">
+        <v>-1</v>
+      </c>
+      <c r="AO21">
+        <v>-1</v>
+      </c>
+      <c r="AP21">
+        <v>-1</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2026-07-27 15:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Bulgaria First League</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>CSKA Sofia</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Botev Plovdiv</t>
+        </is>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N22">
+        <v>1.48</v>
+      </c>
+      <c r="O22">
+        <v>3.9</v>
+      </c>
+      <c r="P22">
+        <v>7</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>1.98</v>
+      </c>
+      <c r="AB22">
+        <v>1.83</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>-1</v>
+      </c>
+      <c r="AN22">
+        <v>-1</v>
+      </c>
+      <c r="AO22">
+        <v>-1</v>
+      </c>
+      <c r="AP22">
+        <v>-1</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2026-07-27 15:15:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Romania Liga I</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Botoşani</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Rapid Bucureşti</t>
+        </is>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N23">
+        <v>3.27</v>
+      </c>
+      <c r="O23">
+        <v>3</v>
+      </c>
+      <c r="P23">
+        <v>2.3</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>-1</v>
+      </c>
+      <c r="AN23">
+        <v>-1</v>
+      </c>
+      <c r="AO23">
+        <v>-1</v>
+      </c>
+      <c r="AP23">
+        <v>-1</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2026-07-27 15:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Gualberto Villarroel SJ</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Universitario de Vinto</t>
+        </is>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
+        <v>0</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>-1</v>
+      </c>
+      <c r="AN24">
+        <v>-1</v>
+      </c>
+      <c r="AO24">
+        <v>-1</v>
+      </c>
+      <c r="AP24">
+        <v>-1</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>2026-07-27 16:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Iceland Úrvalsdeild</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>KA</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Thór</t>
+        </is>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>0</v>
+      </c>
+      <c r="AG25">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>-1</v>
+      </c>
+      <c r="AN25">
+        <v>-1</v>
+      </c>
+      <c r="AO25">
+        <v>-1</v>
+      </c>
+      <c r="AP25">
+        <v>-1</v>
+      </c>
+      <c r="AQ25">
+        <v>0</v>
+      </c>
+      <c r="AR25">
+        <v>0</v>
+      </c>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>2026-07-27 16:15:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>0</v>
+      </c>
+      <c r="AG26">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
+        <v>0</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>-1</v>
+      </c>
+      <c r="AN26">
+        <v>-1</v>
+      </c>
+      <c r="AO26">
+        <v>-1</v>
+      </c>
+      <c r="AP26">
+        <v>-1</v>
+      </c>
+      <c r="AQ26">
+        <v>0</v>
+      </c>
+      <c r="AR26">
+        <v>0</v>
+      </c>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>2026-07-27 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>0</v>
+      </c>
+      <c r="AK27">
+        <v>0</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>-1</v>
+      </c>
+      <c r="AN27">
+        <v>-1</v>
+      </c>
+      <c r="AO27">
+        <v>-1</v>
+      </c>
+      <c r="AP27">
+        <v>-1</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>2026-07-27 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>CRB</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Vila Nova</t>
         </is>
       </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9" t="inlineStr">
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
-      <c r="W9">
-        <v>0</v>
-      </c>
-      <c r="X9">
-        <v>0</v>
-      </c>
-      <c r="Y9">
-        <v>0</v>
-      </c>
-      <c r="Z9">
-        <v>0</v>
-      </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0</v>
-      </c>
-      <c r="AC9">
-        <v>0</v>
-      </c>
-      <c r="AD9">
-        <v>0</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>0</v>
-      </c>
-      <c r="AG9">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>0</v>
-      </c>
-      <c r="AK9">
-        <v>0</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <v>-1</v>
-      </c>
-      <c r="AN9">
-        <v>-1</v>
-      </c>
-      <c r="AO9">
-        <v>-1</v>
-      </c>
-      <c r="AP9">
-        <v>-1</v>
-      </c>
-      <c r="AQ9">
-        <v>0</v>
-      </c>
-      <c r="AR9">
-        <v>0</v>
-      </c>
-      <c r="AS9">
-        <v>0</v>
-      </c>
-      <c r="AT9">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
+        <v>0</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>-1</v>
+      </c>
+      <c r="AN28">
+        <v>-1</v>
+      </c>
+      <c r="AO28">
+        <v>-1</v>
+      </c>
+      <c r="AP28">
+        <v>-1</v>
+      </c>
+      <c r="AQ28">
+        <v>0</v>
+      </c>
+      <c r="AR28">
+        <v>0</v>
+      </c>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+      <c r="AT28">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
         <is>
           <t>2026-07-27 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Unión Española</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Recoleta</t>
+        </is>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>0</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0</v>
+      </c>
+      <c r="AG29">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
+        <v>0</v>
+      </c>
+      <c r="AK29">
+        <v>0</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>-1</v>
+      </c>
+      <c r="AN29">
+        <v>-1</v>
+      </c>
+      <c r="AO29">
+        <v>-1</v>
+      </c>
+      <c r="AP29">
+        <v>-1</v>
+      </c>
+      <c r="AQ29">
+        <v>0</v>
+      </c>
+      <c r="AR29">
+        <v>0</v>
+      </c>
+      <c r="AS29">
+        <v>0</v>
+      </c>
+      <c r="AT29">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>2026-07-27 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Guarani</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Inter de Limeira</t>
+        </is>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>0</v>
+      </c>
+      <c r="Y30">
+        <v>0</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <v>0</v>
+      </c>
+      <c r="AD30">
+        <v>0</v>
+      </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <v>0</v>
+      </c>
+      <c r="AG30">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
+        <v>0</v>
+      </c>
+      <c r="AK30">
+        <v>0</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>-1</v>
+      </c>
+      <c r="AN30">
+        <v>-1</v>
+      </c>
+      <c r="AO30">
+        <v>-1</v>
+      </c>
+      <c r="AP30">
+        <v>-1</v>
+      </c>
+      <c r="AQ30">
+        <v>0</v>
+      </c>
+      <c r="AR30">
+        <v>0</v>
+      </c>
+      <c r="AS30">
+        <v>0</v>
+      </c>
+      <c r="AT30">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>2026-07-27 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Floresta</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Maringá</t>
+        </is>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <v>0</v>
+      </c>
+      <c r="AD31">
+        <v>0</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>0</v>
+      </c>
+      <c r="AG31">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
+        <v>0</v>
+      </c>
+      <c r="AK31">
+        <v>0</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>-1</v>
+      </c>
+      <c r="AN31">
+        <v>-1</v>
+      </c>
+      <c r="AO31">
+        <v>-1</v>
+      </c>
+      <c r="AP31">
+        <v>-1</v>
+      </c>
+      <c r="AQ31">
+        <v>0</v>
+      </c>
+      <c r="AR31">
+        <v>0</v>
+      </c>
+      <c r="AS31">
+        <v>0</v>
+      </c>
+      <c r="AT31">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>2026-07-27 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32">
+        <v>0</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+      <c r="AG32">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
+        <v>0</v>
+      </c>
+      <c r="AK32">
+        <v>0</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>-1</v>
+      </c>
+      <c r="AN32">
+        <v>-1</v>
+      </c>
+      <c r="AO32">
+        <v>-1</v>
+      </c>
+      <c r="AP32">
+        <v>-1</v>
+      </c>
+      <c r="AQ32">
+        <v>0</v>
+      </c>
+      <c r="AR32">
+        <v>0</v>
+      </c>
+      <c r="AS32">
+        <v>0</v>
+      </c>
+      <c r="AT32">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>2026-07-27 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Xorazm</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Termez Surkhon</t>
+        </is>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <v>0</v>
+      </c>
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>0</v>
+      </c>
+      <c r="U33">
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <v>0</v>
+      </c>
+      <c r="Y33">
+        <v>0</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+      <c r="AA33">
+        <v>0</v>
+      </c>
+      <c r="AB33">
+        <v>0</v>
+      </c>
+      <c r="AC33">
+        <v>0</v>
+      </c>
+      <c r="AD33">
+        <v>0</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>0</v>
+      </c>
+      <c r="AG33">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33">
+        <v>0</v>
+      </c>
+      <c r="AK33">
+        <v>0</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>-1</v>
+      </c>
+      <c r="AN33">
+        <v>-1</v>
+      </c>
+      <c r="AO33">
+        <v>-1</v>
+      </c>
+      <c r="AP33">
+        <v>-1</v>
+      </c>
+      <c r="AQ33">
+        <v>0</v>
+      </c>
+      <c r="AR33">
+        <v>0</v>
+      </c>
+      <c r="AS33">
+        <v>0</v>
+      </c>
+      <c r="AT33">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>2026-07-27 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Neftchi</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Navbahor</t>
+        </is>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+      <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <v>0</v>
+      </c>
+      <c r="AC34">
+        <v>0</v>
+      </c>
+      <c r="AD34">
+        <v>0</v>
+      </c>
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
+        <v>0</v>
+      </c>
+      <c r="AG34">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34">
+        <v>0</v>
+      </c>
+      <c r="AK34">
+        <v>0</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>-1</v>
+      </c>
+      <c r="AN34">
+        <v>-1</v>
+      </c>
+      <c r="AO34">
+        <v>-1</v>
+      </c>
+      <c r="AP34">
+        <v>-1</v>
+      </c>
+      <c r="AQ34">
+        <v>0</v>
+      </c>
+      <c r="AR34">
+        <v>0</v>
+      </c>
+      <c r="AS34">
+        <v>0</v>
+      </c>
+      <c r="AT34">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>2026-07-27 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Uzbekistan Uzbekistan Super League</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Nasaf</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Qizilqum</t>
+        </is>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+      <c r="Y35">
+        <v>0</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+      <c r="AA35">
+        <v>0</v>
+      </c>
+      <c r="AB35">
+        <v>0</v>
+      </c>
+      <c r="AC35">
+        <v>0</v>
+      </c>
+      <c r="AD35">
+        <v>0</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>0</v>
+      </c>
+      <c r="AG35">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
+        <v>0</v>
+      </c>
+      <c r="AK35">
+        <v>0</v>
+      </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>-1</v>
+      </c>
+      <c r="AN35">
+        <v>-1</v>
+      </c>
+      <c r="AO35">
+        <v>-1</v>
+      </c>
+      <c r="AP35">
+        <v>-1</v>
+      </c>
+      <c r="AQ35">
+        <v>0</v>
+      </c>
+      <c r="AR35">
+        <v>0</v>
+      </c>
+      <c r="AS35">
+        <v>0</v>
+      </c>
+      <c r="AT35">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>2026-07-27 21:00:00</t>
         </is>
       </c>
     </row>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q11">
         <v>0</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3777,10 +3777,10 @@
         <v>0</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE21">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4429,10 +4429,10 @@
         <v>0</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE25">
         <v>0</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q18">
         <v>0</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU35"/>
+  <dimension ref="A1:AU38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -593,7 +593,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G2">
@@ -751,27 +751,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Voluntari</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G3">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>5.51</v>
+        <v>0</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2026-07-27 12:30:00</t>
+          <t>2026-07-27 12:00:00</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G4">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-07-27 12:45:00</t>
+          <t>2026-07-27 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1077,27 +1077,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G5">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-07-27 13:00:00</t>
+          <t>2026-07-27 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1240,27 +1240,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Voluntari</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>5.51</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-07-27 13:00:00</t>
+          <t>2026-07-27 12:30:00</t>
         </is>
       </c>
     </row>
@@ -1403,27 +1403,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G7">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-07-27 13:00:00</t>
+          <t>2026-07-27 12:45:00</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>14.1</v>
+        <v>0</v>
       </c>
       <c r="O8">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1729,27 +1729,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Podbeskidzie</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="G9">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-07-27 14:00:00</t>
+          <t>2026-07-27 13:00:00</t>
         </is>
       </c>
     </row>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-07-27 14:00:00</t>
+          <t>2026-07-27 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>3.36</v>
+        <v>14.1</v>
       </c>
       <c r="O11">
-        <v>3.22</v>
+        <v>6.5</v>
       </c>
       <c r="P11">
-        <v>2.15</v>
+        <v>1.18</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-07-27 14:00:00</t>
+          <t>2026-07-27 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2223,22 +2223,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Podbeskidzie</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2386,22 +2386,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.79</v>
+        <v>3.03</v>
       </c>
       <c r="O13">
-        <v>3.83</v>
+        <v>3.07</v>
       </c>
       <c r="P13">
-        <v>4.4</v>
+        <v>2.56</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2549,22 +2549,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.11</v>
+        <v>2.64</v>
       </c>
       <c r="O15">
-        <v>3.78</v>
+        <v>3.42</v>
       </c>
       <c r="P15">
-        <v>3.04</v>
+        <v>2.45</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2875,22 +2875,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="O16">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
       <c r="P16">
-        <v>4.46</v>
+        <v>4.4</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -2956,10 +2956,10 @@
         <v>0</v>
       </c>
       <c r="AA16">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC16">
         <v>0</v>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -3125,10 +3125,10 @@
         <v>0</v>
       </c>
       <c r="AC17">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE17">
         <v>0</v>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.79</v>
+        <v>2.11</v>
       </c>
       <c r="O18">
-        <v>3.64</v>
+        <v>3.78</v>
       </c>
       <c r="P18">
-        <v>2.27</v>
+        <v>3.04</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-07-27 14:05:00</t>
+          <t>2026-07-27 14:00:00</t>
         </is>
       </c>
     </row>
@@ -3359,27 +3359,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G19">
@@ -3402,17 +3402,17 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3445,10 +3445,10 @@
         <v>0</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC19">
         <v>0</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-07-27 14:30:00</t>
+          <t>2026-07-27 14:00:00</t>
         </is>
       </c>
     </row>
@@ -3522,27 +3522,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G20">
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3614,10 +3614,10 @@
         <v>0</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE20">
         <v>0</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-07-27 14:30:00</t>
+          <t>2026-07-27 14:00:00</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.7</v>
+        <v>2.79</v>
       </c>
       <c r="O21">
-        <v>4.3</v>
+        <v>3.64</v>
       </c>
       <c r="P21">
-        <v>3.96</v>
+        <v>2.27</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3777,10 +3777,10 @@
         <v>0</v>
       </c>
       <c r="AC21">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD21">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE21">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2026-07-27 15:00:00</t>
+          <t>2026-07-27 14:05:00</t>
         </is>
       </c>
     </row>
@@ -3848,27 +3848,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G22">
@@ -3891,17 +3891,17 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N22">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -3934,10 +3934,10 @@
         <v>0</v>
       </c>
       <c r="AA22">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB22">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC22">
         <v>0</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-07-27 15:15:00</t>
+          <t>2026-07-27 14:30:00</t>
         </is>
       </c>
     </row>
@@ -4011,12 +4011,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="O23">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P23">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-07-27 15:30:00</t>
+          <t>2026-07-27 14:30:00</t>
         </is>
       </c>
     </row>
@@ -4174,12 +4174,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gualberto Villarroel SJ</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="G24">
@@ -4217,17 +4217,17 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4266,10 +4266,10 @@
         <v>0</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE24">
         <v>0</v>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-07-27 16:00:00</t>
+          <t>2026-07-27 15:00:00</t>
         </is>
       </c>
     </row>
@@ -4337,27 +4337,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Thór</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="O25">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="P25">
-        <v>4.08</v>
+        <v>7</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4423,16 +4423,16 @@
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC25">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD25">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AE25">
         <v>0</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-07-27 16:15:00</t>
+          <t>2026-07-27 15:15:00</t>
         </is>
       </c>
     </row>
@@ -4500,27 +4500,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-07-27 19:30:00</t>
+          <t>2026-07-27 15:30:00</t>
         </is>
       </c>
     </row>
@@ -4663,12 +4663,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G27">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N27">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>2026-07-27 19:30:00</t>
+          <t>2026-07-27 16:00:00</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="G28">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-07-27 19:30:00</t>
+          <t>2026-07-27 16:00:00</t>
         </is>
       </c>
     </row>
@@ -4989,12 +4989,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Thór</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5081,10 +5081,10 @@
         <v>0</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AE29">
         <v>0</v>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-07-27 20:00:00</t>
+          <t>2026-07-27 16:15:00</t>
         </is>
       </c>
     </row>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G30">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-07-27 20:00:00</t>
+          <t>2026-07-27 18:30:00</t>
         </is>
       </c>
     </row>
@@ -5315,12 +5315,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G31">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-07-27 20:00:00</t>
+          <t>2026-07-27 19:30:00</t>
         </is>
       </c>
     </row>
@@ -5478,12 +5478,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G32">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-07-27 20:00:00</t>
+          <t>2026-07-27 19:30:00</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G33">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-07-27 21:00:00</t>
+          <t>2026-07-27 19:30:00</t>
         </is>
       </c>
     </row>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="G34">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-07-27 21:00:00</t>
+          <t>2026-07-27 20:00:00</t>
         </is>
       </c>
     </row>
@@ -5967,156 +5967,645 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Guarani</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Inter de Limeira</t>
+        </is>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+      <c r="Y35">
+        <v>0</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+      <c r="AA35">
+        <v>0</v>
+      </c>
+      <c r="AB35">
+        <v>0</v>
+      </c>
+      <c r="AC35">
+        <v>0</v>
+      </c>
+      <c r="AD35">
+        <v>0</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>0</v>
+      </c>
+      <c r="AG35">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
+        <v>0</v>
+      </c>
+      <c r="AK35">
+        <v>0</v>
+      </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>-1</v>
+      </c>
+      <c r="AN35">
+        <v>-1</v>
+      </c>
+      <c r="AO35">
+        <v>-1</v>
+      </c>
+      <c r="AP35">
+        <v>-1</v>
+      </c>
+      <c r="AQ35">
+        <v>0</v>
+      </c>
+      <c r="AR35">
+        <v>0</v>
+      </c>
+      <c r="AS35">
+        <v>0</v>
+      </c>
+      <c r="AT35">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>2026-07-27 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Floresta</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Maringá</t>
+        </is>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>0</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0</v>
+      </c>
+      <c r="X36">
+        <v>0</v>
+      </c>
+      <c r="Y36">
+        <v>0</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>0</v>
+      </c>
+      <c r="AC36">
+        <v>0</v>
+      </c>
+      <c r="AD36">
+        <v>0</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>0</v>
+      </c>
+      <c r="AG36">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
+        <v>0</v>
+      </c>
+      <c r="AK36">
+        <v>0</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>-1</v>
+      </c>
+      <c r="AN36">
+        <v>-1</v>
+      </c>
+      <c r="AO36">
+        <v>-1</v>
+      </c>
+      <c r="AP36">
+        <v>-1</v>
+      </c>
+      <c r="AQ36">
+        <v>0</v>
+      </c>
+      <c r="AR36">
+        <v>0</v>
+      </c>
+      <c r="AS36">
+        <v>0</v>
+      </c>
+      <c r="AT36">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>2026-07-27 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0</v>
+      </c>
+      <c r="X37">
+        <v>0</v>
+      </c>
+      <c r="Y37">
+        <v>0</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+      <c r="AA37">
+        <v>0</v>
+      </c>
+      <c r="AB37">
+        <v>0</v>
+      </c>
+      <c r="AC37">
+        <v>0</v>
+      </c>
+      <c r="AD37">
+        <v>0</v>
+      </c>
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37">
+        <v>0</v>
+      </c>
+      <c r="AG37">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37">
+        <v>0</v>
+      </c>
+      <c r="AK37">
+        <v>0</v>
+      </c>
+      <c r="AL37">
+        <v>0</v>
+      </c>
+      <c r="AM37">
+        <v>-1</v>
+      </c>
+      <c r="AN37">
+        <v>-1</v>
+      </c>
+      <c r="AO37">
+        <v>-1</v>
+      </c>
+      <c r="AP37">
+        <v>-1</v>
+      </c>
+      <c r="AQ37">
+        <v>0</v>
+      </c>
+      <c r="AR37">
+        <v>0</v>
+      </c>
+      <c r="AS37">
+        <v>0</v>
+      </c>
+      <c r="AT37">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>2026-07-27 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Nasaf</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Qizilqum</t>
-        </is>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35" t="inlineStr">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Deportivo Cuenca</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>CS Emelec</t>
+        </is>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
-      <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="P35">
-        <v>0</v>
-      </c>
-      <c r="Q35">
-        <v>0</v>
-      </c>
-      <c r="R35">
-        <v>0</v>
-      </c>
-      <c r="S35">
-        <v>0</v>
-      </c>
-      <c r="T35">
-        <v>0</v>
-      </c>
-      <c r="U35">
-        <v>0</v>
-      </c>
-      <c r="V35">
-        <v>0</v>
-      </c>
-      <c r="W35">
-        <v>0</v>
-      </c>
-      <c r="X35">
-        <v>0</v>
-      </c>
-      <c r="Y35">
-        <v>0</v>
-      </c>
-      <c r="Z35">
-        <v>0</v>
-      </c>
-      <c r="AA35">
-        <v>0</v>
-      </c>
-      <c r="AB35">
-        <v>0</v>
-      </c>
-      <c r="AC35">
-        <v>0</v>
-      </c>
-      <c r="AD35">
-        <v>0</v>
-      </c>
-      <c r="AE35">
-        <v>0</v>
-      </c>
-      <c r="AF35">
-        <v>0</v>
-      </c>
-      <c r="AG35">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>0</v>
-      </c>
-      <c r="AK35">
-        <v>0</v>
-      </c>
-      <c r="AL35">
-        <v>0</v>
-      </c>
-      <c r="AM35">
-        <v>-1</v>
-      </c>
-      <c r="AN35">
-        <v>-1</v>
-      </c>
-      <c r="AO35">
-        <v>-1</v>
-      </c>
-      <c r="AP35">
-        <v>-1</v>
-      </c>
-      <c r="AQ35">
-        <v>0</v>
-      </c>
-      <c r="AR35">
-        <v>0</v>
-      </c>
-      <c r="AS35">
-        <v>0</v>
-      </c>
-      <c r="AT35">
-        <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38">
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0</v>
+      </c>
+      <c r="X38">
+        <v>0</v>
+      </c>
+      <c r="Y38">
+        <v>0</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+      <c r="AA38">
+        <v>0</v>
+      </c>
+      <c r="AB38">
+        <v>0</v>
+      </c>
+      <c r="AC38">
+        <v>0</v>
+      </c>
+      <c r="AD38">
+        <v>0</v>
+      </c>
+      <c r="AE38">
+        <v>0</v>
+      </c>
+      <c r="AF38">
+        <v>0</v>
+      </c>
+      <c r="AG38">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
+        <v>0</v>
+      </c>
+      <c r="AK38">
+        <v>0</v>
+      </c>
+      <c r="AL38">
+        <v>0</v>
+      </c>
+      <c r="AM38">
+        <v>-1</v>
+      </c>
+      <c r="AN38">
+        <v>-1</v>
+      </c>
+      <c r="AO38">
+        <v>-1</v>
+      </c>
+      <c r="AP38">
+        <v>-1</v>
+      </c>
+      <c r="AQ38">
+        <v>0</v>
+      </c>
+      <c r="AR38">
+        <v>0</v>
+      </c>
+      <c r="AS38">
+        <v>0</v>
+      </c>
+      <c r="AT38">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
         <is>
           <t>2026-07-27 21:00:00</t>
         </is>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1169,10 +1169,10 @@
         <v>0</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE5">
         <v>0</v>
@@ -1296,55 +1296,55 @@
         <v>5.51</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2304,10 +2304,10 @@
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC12">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6373,10 +6373,10 @@
         <v>0</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA37">
         <v>0</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -1133,40 +1133,40 @@
         <v>1.14</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>9.35</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC5">
         <v>1.9</v>
@@ -1175,13 +1175,13 @@
         <v>1.9</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1785,55 +1785,55 @@
         <v>4.87</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2763,55 +2763,55 @@
         <v>2.45</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2926,55 +2926,55 @@
         <v>4.4</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3252,55 +3252,55 @@
         <v>3.04</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3578,40 +3578,40 @@
         <v>4.69</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AC20">
         <v>1.85</v>
@@ -3620,13 +3620,13 @@
         <v>1.84</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3741,55 +3741,55 @@
         <v>2.27</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL21">
         <v>0</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -1622,55 +1622,55 @@
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1948,55 +1948,55 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2111,55 +2111,55 @@
         <v>1.18</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>7.98</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2274,34 +2274,34 @@
         <v>3.57</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AA12">
         <v>1.79</v>
@@ -2310,19 +2310,19 @@
         <v>1.88</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,55 +2437,55 @@
         <v>2.56</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2600,55 +2600,55 @@
         <v>2.15</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3415,34 +3415,34 @@
         <v>4.46</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA19">
         <v>1.63</v>
@@ -3451,19 +3451,19 @@
         <v>2.1</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4067,55 +4067,55 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4393,34 +4393,34 @@
         <v>7</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA25">
         <v>1.98</v>
@@ -4429,19 +4429,19 @@
         <v>1.83</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4556,55 +4556,55 @@
         <v>2.3</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G33">

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -1459,10 +1459,10 @@
         <v>1.79</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1471,10 +1471,10 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
         <v>0</v>
@@ -1483,31 +1483,31 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -4230,40 +4230,40 @@
         <v>3.96</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AC24">
         <v>1.79</v>
@@ -4272,13 +4272,13 @@
         <v>1.89</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -5045,40 +5045,40 @@
         <v>4.08</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC29">
         <v>1.81</v>
@@ -5087,13 +5087,13 @@
         <v>1.86</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S32">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T32">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U32">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V32">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y32">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z32">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA32">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC32">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE32">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF32">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG32">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK32">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6349,28 +6349,28 @@
         <v>5.4</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y37">
         <v>1.51</v>
@@ -6379,25 +6379,25 @@
         <v>2.35</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>5.11</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL37">
         <v>0</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU38"/>
+  <dimension ref="A1:AU39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
+        <v>2.3</v>
+      </c>
+      <c r="O37">
+        <v>3.1</v>
+      </c>
+      <c r="P37">
+        <v>2.75</v>
+      </c>
+      <c r="Q37">
+        <v>3.07</v>
+      </c>
+      <c r="R37">
+        <v>2.11</v>
+      </c>
+      <c r="S37">
+        <v>1.43</v>
+      </c>
+      <c r="T37">
+        <v>2.62</v>
+      </c>
+      <c r="U37">
+        <v>3.21</v>
+      </c>
+      <c r="V37">
+        <v>1.32</v>
+      </c>
+      <c r="W37">
+        <v>1.06</v>
+      </c>
+      <c r="X37">
+        <v>1.04</v>
+      </c>
+      <c r="Y37">
+        <v>1.38</v>
+      </c>
+      <c r="Z37">
+        <v>2.7</v>
+      </c>
+      <c r="AA37">
+        <v>2.15</v>
+      </c>
+      <c r="AB37">
         <v>1.65</v>
       </c>
-      <c r="O37">
-        <v>3.24</v>
-      </c>
-      <c r="P37">
-        <v>5.4</v>
-      </c>
-      <c r="Q37">
-        <v>2.27</v>
-      </c>
-      <c r="R37">
+      <c r="AC37">
+        <v>3.7</v>
+      </c>
+      <c r="AD37">
+        <v>1.23</v>
+      </c>
+      <c r="AE37">
+        <v>1.05</v>
+      </c>
+      <c r="AF37">
+        <v>1.85</v>
+      </c>
+      <c r="AG37">
         <v>1.91</v>
-      </c>
-      <c r="S37">
-        <v>1.55</v>
-      </c>
-      <c r="T37">
-        <v>2.28</v>
-      </c>
-      <c r="U37">
-        <v>3.5</v>
-      </c>
-      <c r="V37">
-        <v>1.25</v>
-      </c>
-      <c r="W37">
-        <v>1.04</v>
-      </c>
-      <c r="X37">
-        <v>1.1</v>
-      </c>
-      <c r="Y37">
-        <v>1.51</v>
-      </c>
-      <c r="Z37">
-        <v>2.35</v>
-      </c>
-      <c r="AA37">
-        <v>2.6</v>
-      </c>
-      <c r="AB37">
-        <v>1.47</v>
-      </c>
-      <c r="AC37">
-        <v>5.11</v>
-      </c>
-      <c r="AD37">
-        <v>1.15</v>
-      </c>
-      <c r="AE37">
-        <v>1.01</v>
-      </c>
-      <c r="AF37">
-        <v>2.45</v>
-      </c>
-      <c r="AG37">
-        <v>1.48</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.25</v>
       </c>
       <c r="AK37">
-        <v>2.08</v>
+        <v>1.42</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6456,156 +6456,319 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N38">
+        <v>1.65</v>
+      </c>
+      <c r="O38">
+        <v>3.24</v>
+      </c>
+      <c r="P38">
+        <v>5.4</v>
+      </c>
+      <c r="Q38">
+        <v>2.27</v>
+      </c>
+      <c r="R38">
+        <v>1.91</v>
+      </c>
+      <c r="S38">
+        <v>1.55</v>
+      </c>
+      <c r="T38">
+        <v>2.28</v>
+      </c>
+      <c r="U38">
+        <v>3.5</v>
+      </c>
+      <c r="V38">
+        <v>1.25</v>
+      </c>
+      <c r="W38">
+        <v>1.04</v>
+      </c>
+      <c r="X38">
+        <v>1.1</v>
+      </c>
+      <c r="Y38">
+        <v>1.51</v>
+      </c>
+      <c r="Z38">
+        <v>2.35</v>
+      </c>
+      <c r="AA38">
+        <v>2.6</v>
+      </c>
+      <c r="AB38">
+        <v>1.47</v>
+      </c>
+      <c r="AC38">
+        <v>5.11</v>
+      </c>
+      <c r="AD38">
+        <v>1.15</v>
+      </c>
+      <c r="AE38">
+        <v>1.01</v>
+      </c>
+      <c r="AF38">
+        <v>2.45</v>
+      </c>
+      <c r="AG38">
+        <v>1.48</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
+        <v>1.25</v>
+      </c>
+      <c r="AK38">
+        <v>2.08</v>
+      </c>
+      <c r="AL38">
+        <v>0</v>
+      </c>
+      <c r="AM38">
+        <v>-1</v>
+      </c>
+      <c r="AN38">
+        <v>-1</v>
+      </c>
+      <c r="AO38">
+        <v>-1</v>
+      </c>
+      <c r="AP38">
+        <v>-1</v>
+      </c>
+      <c r="AQ38">
+        <v>0</v>
+      </c>
+      <c r="AR38">
+        <v>0</v>
+      </c>
+      <c r="AS38">
+        <v>0</v>
+      </c>
+      <c r="AT38">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>2026-07-27 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Deportivo Cuenca</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>CS Emelec</t>
         </is>
       </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-      <c r="H38">
-        <v>0</v>
-      </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
-      <c r="K38">
-        <v>0</v>
-      </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-      <c r="M38" t="inlineStr">
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
-      <c r="O38">
-        <v>0</v>
-      </c>
-      <c r="P38">
-        <v>0</v>
-      </c>
-      <c r="Q38">
-        <v>0</v>
-      </c>
-      <c r="R38">
-        <v>0</v>
-      </c>
-      <c r="S38">
-        <v>0</v>
-      </c>
-      <c r="T38">
-        <v>0</v>
-      </c>
-      <c r="U38">
-        <v>0</v>
-      </c>
-      <c r="V38">
-        <v>0</v>
-      </c>
-      <c r="W38">
-        <v>0</v>
-      </c>
-      <c r="X38">
-        <v>0</v>
-      </c>
-      <c r="Y38">
-        <v>0</v>
-      </c>
-      <c r="Z38">
-        <v>0</v>
-      </c>
-      <c r="AA38">
-        <v>0</v>
-      </c>
-      <c r="AB38">
-        <v>0</v>
-      </c>
-      <c r="AC38">
-        <v>0</v>
-      </c>
-      <c r="AD38">
-        <v>0</v>
-      </c>
-      <c r="AE38">
-        <v>0</v>
-      </c>
-      <c r="AF38">
-        <v>0</v>
-      </c>
-      <c r="AG38">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38">
-        <v>0</v>
-      </c>
-      <c r="AK38">
-        <v>0</v>
-      </c>
-      <c r="AL38">
-        <v>0</v>
-      </c>
-      <c r="AM38">
-        <v>-1</v>
-      </c>
-      <c r="AN38">
-        <v>-1</v>
-      </c>
-      <c r="AO38">
-        <v>-1</v>
-      </c>
-      <c r="AP38">
-        <v>-1</v>
-      </c>
-      <c r="AQ38">
-        <v>0</v>
-      </c>
-      <c r="AR38">
-        <v>0</v>
-      </c>
-      <c r="AS38">
-        <v>0</v>
-      </c>
-      <c r="AT38">
-        <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0</v>
+      </c>
+      <c r="X39">
+        <v>0</v>
+      </c>
+      <c r="Y39">
+        <v>0</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+      <c r="AA39">
+        <v>0</v>
+      </c>
+      <c r="AB39">
+        <v>0</v>
+      </c>
+      <c r="AC39">
+        <v>0</v>
+      </c>
+      <c r="AD39">
+        <v>0</v>
+      </c>
+      <c r="AE39">
+        <v>0</v>
+      </c>
+      <c r="AF39">
+        <v>0</v>
+      </c>
+      <c r="AG39">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
+        <v>0</v>
+      </c>
+      <c r="AK39">
+        <v>0</v>
+      </c>
+      <c r="AL39">
+        <v>0</v>
+      </c>
+      <c r="AM39">
+        <v>-1</v>
+      </c>
+      <c r="AN39">
+        <v>-1</v>
+      </c>
+      <c r="AO39">
+        <v>-1</v>
+      </c>
+      <c r="AP39">
+        <v>-1</v>
+      </c>
+      <c r="AQ39">
+        <v>0</v>
+      </c>
+      <c r="AR39">
+        <v>0</v>
+      </c>
+      <c r="AS39">
+        <v>0</v>
+      </c>
+      <c r="AT39">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
         <is>
           <t>2026-07-27 21:00:00</t>
         </is>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -1133,7 +1133,7 @@
         <v>1.14</v>
       </c>
       <c r="Q5">
-        <v>9.35</v>
+        <v>8.9</v>
       </c>
       <c r="R5">
         <v>2.64</v>
@@ -1151,7 +1151,7 @@
         <v>1.67</v>
       </c>
       <c r="W5">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X5">
         <v>1</v>
@@ -1160,28 +1160,28 @@
         <v>1.14</v>
       </c>
       <c r="Z5">
-        <v>4.5</v>
+        <v>5.35</v>
       </c>
       <c r="AA5">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AB5">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="AC5">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AD5">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AE5">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AF5">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AG5">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AK5">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -3089,10 +3089,10 @@
         <v>0</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S17">
         <v>0</v>
@@ -3101,10 +3101,10 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W17">
         <v>0</v>
@@ -3113,31 +3113,31 @@
         <v>0</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL32">
         <v>0</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.23</v>
+        <v>1.92</v>
       </c>
       <c r="O32">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="P32">
-        <v>3.22</v>
+        <v>3.86</v>
       </c>
       <c r="Q32">
-        <v>2.94</v>
+        <v>2.55</v>
       </c>
       <c r="R32">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="S32">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T32">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="U32">
+        <v>3</v>
+      </c>
+      <c r="V32">
+        <v>1.33</v>
+      </c>
+      <c r="W32">
+        <v>1.08</v>
+      </c>
+      <c r="X32">
+        <v>1.03</v>
+      </c>
+      <c r="Y32">
+        <v>1.31</v>
+      </c>
+      <c r="Z32">
         <v>3.1</v>
       </c>
-      <c r="V32">
-        <v>1.31</v>
-      </c>
-      <c r="W32">
-        <v>1.01</v>
-      </c>
-      <c r="X32">
-        <v>1.02</v>
-      </c>
-      <c r="Y32">
-        <v>1.33</v>
-      </c>
-      <c r="Z32">
-        <v>2.83</v>
-      </c>
       <c r="AA32">
-        <v>2.19</v>
+        <v>1.81</v>
       </c>
       <c r="AB32">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="AC32">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AD32">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE32">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AF32">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AG32">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK32">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.92</v>
+        <v>2.23</v>
       </c>
       <c r="O33">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="P33">
-        <v>3.86</v>
+        <v>3.22</v>
       </c>
       <c r="Q33">
-        <v>2.55</v>
+        <v>2.94</v>
       </c>
       <c r="R33">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="S33">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T33">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="U33">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V33">
+        <v>1.31</v>
+      </c>
+      <c r="W33">
+        <v>1.01</v>
+      </c>
+      <c r="X33">
+        <v>1.02</v>
+      </c>
+      <c r="Y33">
         <v>1.33</v>
       </c>
-      <c r="W33">
-        <v>1.08</v>
-      </c>
-      <c r="X33">
-        <v>1.03</v>
-      </c>
-      <c r="Y33">
-        <v>1.31</v>
-      </c>
       <c r="Z33">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="AA33">
-        <v>1.81</v>
+        <v>2.19</v>
       </c>
       <c r="AB33">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="AC33">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AD33">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE33">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AF33">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AG33">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK33">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AL33">
         <v>0</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="O6">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P6">
-        <v>5.51</v>
+        <v>4.2</v>
       </c>
       <c r="Q6">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="R6">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
       <c r="S6">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T6">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="U6">
         <v>2.73</v>
       </c>
       <c r="V6">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="W6">
         <v>1.07</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z6">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AA6">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AB6">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AC6">
         <v>3.08</v>
       </c>
       <c r="AD6">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE6">
         <v>1.07</v>
       </c>
       <c r="AF6">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AG6">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK6">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -4547,61 +4547,61 @@
         </is>
       </c>
       <c r="N26">
-        <v>3.27</v>
+        <v>2.9</v>
       </c>
       <c r="O26">
+        <v>3.04</v>
+      </c>
+      <c r="P26">
+        <v>2.26</v>
+      </c>
+      <c r="Q26">
+        <v>3.52</v>
+      </c>
+      <c r="R26">
+        <v>1.96</v>
+      </c>
+      <c r="S26">
+        <v>1.43</v>
+      </c>
+      <c r="T26">
+        <v>2.59</v>
+      </c>
+      <c r="U26">
         <v>3</v>
       </c>
-      <c r="P26">
-        <v>2.3</v>
-      </c>
-      <c r="Q26">
-        <v>3.6</v>
-      </c>
-      <c r="R26">
+      <c r="V26">
+        <v>1.33</v>
+      </c>
+      <c r="W26">
+        <v>1.02</v>
+      </c>
+      <c r="X26">
+        <v>1.01</v>
+      </c>
+      <c r="Y26">
+        <v>1.28</v>
+      </c>
+      <c r="Z26">
+        <v>3.05</v>
+      </c>
+      <c r="AA26">
         <v>2.05</v>
       </c>
-      <c r="S26">
-        <v>1.37</v>
-      </c>
-      <c r="T26">
-        <v>2.7</v>
-      </c>
-      <c r="U26">
-        <v>2.85</v>
-      </c>
-      <c r="V26">
-        <v>1.34</v>
-      </c>
-      <c r="W26">
-        <v>1.05</v>
-      </c>
-      <c r="X26">
-        <v>1.04</v>
-      </c>
-      <c r="Y26">
-        <v>1.34</v>
-      </c>
-      <c r="Z26">
-        <v>3.14</v>
-      </c>
-      <c r="AA26">
-        <v>2</v>
-      </c>
       <c r="AB26">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AC26">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="AD26">
         <v>1.22</v>
       </c>
       <c r="AE26">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF26">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG26">
         <v>1.94</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK26">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AL26">
         <v>0</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -1136,7 +1136,7 @@
         <v>8.9</v>
       </c>
       <c r="R5">
-        <v>2.64</v>
+        <v>3.1</v>
       </c>
       <c r="S5">
         <v>1.23</v>
@@ -1148,28 +1148,28 @@
         <v>2.05</v>
       </c>
       <c r="V5">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="W5">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="X5">
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z5">
-        <v>5.35</v>
+        <v>4.5</v>
       </c>
       <c r="AA5">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AB5">
-        <v>2.66</v>
+        <v>2.33</v>
       </c>
       <c r="AC5">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="AD5">
         <v>1.75</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.07</v>
+        <v>2.95</v>
       </c>
       <c r="AK5">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1776,19 +1776,19 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="O9">
-        <v>3.94</v>
+        <v>3.75</v>
       </c>
       <c r="P9">
-        <v>4.87</v>
+        <v>4.2</v>
       </c>
       <c r="Q9">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="R9">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="S9">
         <v>1.28</v>
@@ -1797,7 +1797,7 @@
         <v>3.12</v>
       </c>
       <c r="U9">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V9">
         <v>1.44</v>
@@ -1809,10 +1809,10 @@
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z9">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="AA9">
         <v>1.68</v>
@@ -1827,13 +1827,13 @@
         <v>1.36</v>
       </c>
       <c r="AE9">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF9">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AG9">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AK9">
-        <v>2.07</v>
+        <v>1.88</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5362,16 +5362,16 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="O31">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="P31">
-        <v>3.87</v>
+        <v>3.7</v>
       </c>
       <c r="Q31">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R31">
         <v>1.98</v>
@@ -5392,7 +5392,7 @@
         <v>1.01</v>
       </c>
       <c r="X31">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y31">
         <v>1.38</v>
@@ -5410,7 +5410,7 @@
         <v>4.2</v>
       </c>
       <c r="AD31">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE31">
         <v>1.01</v>
@@ -5435,7 +5435,7 @@
         <v>1.3</v>
       </c>
       <c r="AK31">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5537,13 +5537,13 @@
         <v>2.55</v>
       </c>
       <c r="R32">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S32">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T32">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="U32">
         <v>3</v>
@@ -5555,50 +5555,50 @@
         <v>1.08</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z32">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AA32">
-        <v>1.81</v>
+        <v>1.99</v>
       </c>
       <c r="AB32">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AC32">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="AD32">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE32">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF32">
+        <v>1.72</v>
+      </c>
+      <c r="AG32">
+        <v>1.98</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
+        <v>1.22</v>
+      </c>
+      <c r="AK32">
         <v>1.83</v>
-      </c>
-      <c r="AG32">
-        <v>1.94</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32">
-        <v>1.3</v>
-      </c>
-      <c r="AK32">
-        <v>1.8</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,28 +5688,28 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="O33">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="P33">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="Q33">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="R33">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="S33">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T33">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="U33">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="V33">
         <v>1.31</v>
@@ -5727,13 +5727,13 @@
         <v>2.83</v>
       </c>
       <c r="AA33">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AB33">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC33">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="AD33">
         <v>1.18</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -1290,28 +1290,28 @@
         <v>1.55</v>
       </c>
       <c r="O6">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P6">
-        <v>4.2</v>
+        <v>5.51</v>
       </c>
       <c r="Q6">
-        <v>2.06</v>
+        <v>2.21</v>
       </c>
       <c r="R6">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="S6">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T6">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="U6">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="V6">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W6">
         <v>1.07</v>
@@ -1320,10 +1320,10 @@
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z6">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AA6">
         <v>1.89</v>
@@ -1338,13 +1338,13 @@
         <v>1.28</v>
       </c>
       <c r="AE6">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF6">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AG6">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK6">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1625,25 +1625,25 @@
         <v>4.47</v>
       </c>
       <c r="R8">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="S8">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T8">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="U8">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V8">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W8">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y8">
         <v>1.19</v>
@@ -1655,13 +1655,13 @@
         <v>1.73</v>
       </c>
       <c r="AB8">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AC8">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="AD8">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AE8">
         <v>1.11</v>
@@ -1670,7 +1670,7 @@
         <v>1.65</v>
       </c>
       <c r="AG8">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.25</v>
+        <v>1.91</v>
       </c>
       <c r="AK8">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="O9">
         <v>3.75</v>
@@ -1948,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="R10">
         <v>2.12</v>
@@ -1978,7 +1978,7 @@
         <v>3.5</v>
       </c>
       <c r="AA10">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AB10">
         <v>1.9</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK10">
         <v>1.5</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>14.1</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="P11">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="Q11">
-        <v>7.98</v>
+        <v>7.52</v>
       </c>
       <c r="R11">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="S11">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T11">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="U11">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="V11">
         <v>1.5</v>
       </c>
       <c r="W11">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z11">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA11">
         <v>1.66</v>
       </c>
       <c r="AB11">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="AC11">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="AD11">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE11">
         <v>1.16</v>
       </c>
       <c r="AF11">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AG11">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.17</v>
+        <v>3.3</v>
       </c>
       <c r="AK11">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="O12">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="P12">
-        <v>3.57</v>
+        <v>3.2</v>
       </c>
       <c r="Q12">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="R12">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S12">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T12">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="U12">
         <v>2.41</v>
       </c>
       <c r="V12">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W12">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z12">
-        <v>4.14</v>
+        <v>3.84</v>
       </c>
       <c r="AA12">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AB12">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="AC12">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AD12">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE12">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF12">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG12">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK12">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,25 +2428,25 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.03</v>
+        <v>2.92</v>
       </c>
       <c r="O13">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="P13">
-        <v>2.56</v>
+        <v>2.33</v>
       </c>
       <c r="Q13">
-        <v>3.88</v>
+        <v>3.46</v>
       </c>
       <c r="R13">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="S13">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="T13">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="U13">
         <v>3.44</v>
@@ -2467,13 +2467,13 @@
         <v>2.49</v>
       </c>
       <c r="AA13">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="AB13">
         <v>1.52</v>
       </c>
       <c r="AC13">
-        <v>4.68</v>
+        <v>4.6</v>
       </c>
       <c r="AD13">
         <v>1.13</v>
@@ -2591,25 +2591,25 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.36</v>
+        <v>2.84</v>
       </c>
       <c r="O14">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="P14">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="Q14">
-        <v>3.7</v>
+        <v>3.63</v>
       </c>
       <c r="R14">
         <v>1.96</v>
       </c>
       <c r="S14">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T14">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="U14">
         <v>3</v>
@@ -2618,25 +2618,25 @@
         <v>1.33</v>
       </c>
       <c r="W14">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X14">
         <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="Z14">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AA14">
         <v>2.2</v>
       </c>
       <c r="AB14">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC14">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AD14">
         <v>1.18</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AK14">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3406,49 +3406,49 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="O19">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="P19">
-        <v>4.46</v>
+        <v>3.9</v>
       </c>
       <c r="Q19">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="R19">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="S19">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T19">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U19">
         <v>2.4</v>
       </c>
       <c r="V19">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="W19">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X19">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z19">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA19">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB19">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC19">
         <v>2.7</v>
@@ -3457,13 +3457,13 @@
         <v>1.4</v>
       </c>
       <c r="AE19">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF19">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG19">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AK19">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,34 +3569,34 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="O20">
         <v>4.65</v>
       </c>
       <c r="P20">
-        <v>4.69</v>
+        <v>5.15</v>
       </c>
       <c r="Q20">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="R20">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="S20">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="T20">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="U20">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="V20">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="W20">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X20">
         <v>1.01</v>
@@ -3605,25 +3605,25 @@
         <v>1.06</v>
       </c>
       <c r="Z20">
-        <v>5.25</v>
+        <v>7.5</v>
       </c>
       <c r="AA20">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AB20">
-        <v>3.26</v>
+        <v>2.97</v>
       </c>
       <c r="AC20">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AD20">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AE20">
         <v>1.35</v>
       </c>
       <c r="AF20">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG20">
         <v>2.25</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AK20">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4076,37 +4076,37 @@
         <v>1.31</v>
       </c>
       <c r="T23">
-        <v>3.02</v>
+        <v>3.27</v>
       </c>
       <c r="U23">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="V23">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="W23">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X23">
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z23">
-        <v>3.78</v>
+        <v>3.97</v>
       </c>
       <c r="AA23">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB23">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AC23">
         <v>2.74</v>
       </c>
       <c r="AD23">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE23">
         <v>1.1</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AK23">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="O24">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="P24">
-        <v>3.96</v>
+        <v>3.85</v>
       </c>
       <c r="Q24">
         <v>2.12</v>
@@ -4239,46 +4239,46 @@
         <v>1.17</v>
       </c>
       <c r="T24">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="U24">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="V24">
         <v>1.78</v>
       </c>
       <c r="W24">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z24">
         <v>5.9</v>
       </c>
       <c r="AA24">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AB24">
-        <v>3.25</v>
+        <v>2.83</v>
       </c>
       <c r="AC24">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="AD24">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AE24">
         <v>1.31</v>
       </c>
       <c r="AF24">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AG24">
-        <v>2.72</v>
+        <v>2.77</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AK24">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,25 +4384,25 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="O25">
         <v>3.9</v>
       </c>
       <c r="P25">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q25">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="R25">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="S25">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T25">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="U25">
         <v>2.59</v>
@@ -4411,25 +4411,25 @@
         <v>1.43</v>
       </c>
       <c r="W25">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z25">
         <v>3.5</v>
       </c>
       <c r="AA25">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AB25">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AC25">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="AD25">
         <v>1.36</v>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4550,25 +4550,25 @@
         <v>2.9</v>
       </c>
       <c r="O26">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="P26">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
       <c r="Q26">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="R26">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="S26">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T26">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="U26">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="V26">
         <v>1.33</v>
@@ -4580,31 +4580,31 @@
         <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="Z26">
         <v>3.05</v>
       </c>
       <c r="AA26">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB26">
         <v>1.73</v>
       </c>
       <c r="AC26">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AD26">
         <v>1.22</v>
       </c>
       <c r="AE26">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF26">
         <v>1.77</v>
       </c>
       <c r="AG26">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="AK26">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5036,28 +5036,28 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="O29">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="P29">
-        <v>4.08</v>
+        <v>3.9</v>
       </c>
       <c r="Q29">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="R29">
         <v>2.49</v>
       </c>
       <c r="S29">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="T29">
-        <v>4.5</v>
+        <v>3.84</v>
       </c>
       <c r="U29">
-        <v>2.11</v>
+        <v>2.01</v>
       </c>
       <c r="V29">
         <v>1.74</v>
@@ -5081,10 +5081,10 @@
         <v>2.7</v>
       </c>
       <c r="AC29">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AD29">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AE29">
         <v>1.28</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK29">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="O30">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="P30">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="O31">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P31">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="Q31">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="R31">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="S31">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="T31">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="U31">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="V31">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W31">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X31">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y31">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="Z31">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AA31">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AB31">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AC31">
-        <v>4.2</v>
+        <v>4.55</v>
       </c>
       <c r="AD31">
         <v>1.17</v>
       </c>
       <c r="AE31">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF31">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="AG31">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AK31">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5537,7 +5537,7 @@
         <v>2.55</v>
       </c>
       <c r="R32">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S32">
         <v>1.36</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK32">
         <v>1.83</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="O33">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P33">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Q33">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="R33">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S33">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T33">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="U33">
         <v>3.2</v>
       </c>
       <c r="V33">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W33">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y33">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z33">
-        <v>2.83</v>
+        <v>3.03</v>
       </c>
       <c r="AA33">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB33">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC33">
-        <v>3.88</v>
+        <v>3.68</v>
       </c>
       <c r="AD33">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE33">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AF33">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AG33">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK33">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O37">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="P37">
-        <v>2.75</v>
+        <v>3.01</v>
       </c>
       <c r="Q37">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="R37">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="S37">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T37">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="U37">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="V37">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W37">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X37">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y37">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z37">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="AA37">
         <v>2.15</v>
       </c>
       <c r="AB37">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC37">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AD37">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE37">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF37">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG37">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK37">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,22 +6503,22 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="O38">
-        <v>3.24</v>
+        <v>3.4</v>
       </c>
       <c r="P38">
-        <v>5.4</v>
+        <v>6.15</v>
       </c>
       <c r="Q38">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="R38">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="S38">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="T38">
         <v>2.28</v>
@@ -6533,13 +6533,13 @@
         <v>1.04</v>
       </c>
       <c r="X38">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y38">
         <v>1.51</v>
       </c>
       <c r="Z38">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="AA38">
         <v>2.6</v>
@@ -6548,19 +6548,19 @@
         <v>1.47</v>
       </c>
       <c r="AC38">
-        <v>5.11</v>
+        <v>5</v>
       </c>
       <c r="AD38">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AE38">
         <v>1.01</v>
       </c>
       <c r="AF38">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="AG38">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK38">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL39">
         <v>0</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -1133,7 +1133,7 @@
         <v>1.14</v>
       </c>
       <c r="Q5">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R5">
         <v>3.1</v>
@@ -1145,7 +1145,7 @@
         <v>3.42</v>
       </c>
       <c r="U5">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="V5">
         <v>1.73</v>
@@ -1788,7 +1788,7 @@
         <v>2</v>
       </c>
       <c r="R9">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="S9">
         <v>1.28</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="O15">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="P15">
         <v>2.45</v>
       </c>
       <c r="Q15">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="R15">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="S15">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T15">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U15">
         <v>2.5</v>
       </c>
       <c r="V15">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="W15">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z15">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AA15">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AB15">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AC15">
         <v>2.75</v>
       </c>
       <c r="AD15">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE15">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF15">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG15">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK15">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,25 +2917,25 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="O16">
-        <v>3.83</v>
+        <v>3.78</v>
       </c>
       <c r="P16">
-        <v>4.4</v>
+        <v>4.16</v>
       </c>
       <c r="Q16">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="R16">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="S16">
         <v>1.32</v>
       </c>
       <c r="T16">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="U16">
         <v>2.56</v>
@@ -2947,34 +2947,34 @@
         <v>1.07</v>
       </c>
       <c r="X16">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z16">
         <v>3.78</v>
       </c>
       <c r="AA16">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB16">
         <v>2.07</v>
       </c>
       <c r="AC16">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AD16">
         <v>1.36</v>
       </c>
       <c r="AE16">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF16">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG16">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.11</v>
+        <v>1.82</v>
       </c>
       <c r="O18">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="P18">
-        <v>3.04</v>
+        <v>3.5</v>
       </c>
       <c r="Q18">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="R18">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="S18">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T18">
-        <v>3.66</v>
+        <v>3.55</v>
       </c>
       <c r="U18">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="V18">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W18">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X18">
         <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z18">
-        <v>4.95</v>
+        <v>5.25</v>
       </c>
       <c r="AA18">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AB18">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AC18">
         <v>2.17</v>
       </c>
       <c r="AD18">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AE18">
         <v>1.21</v>
       </c>
       <c r="AF18">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AG18">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3732,58 +3732,58 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="O21">
-        <v>3.64</v>
+        <v>3.45</v>
       </c>
       <c r="P21">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="Q21">
-        <v>3.37</v>
+        <v>3</v>
       </c>
       <c r="R21">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="S21">
         <v>1.24</v>
       </c>
       <c r="T21">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="U21">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="V21">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="W21">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="Z21">
-        <v>5.25</v>
+        <v>4.9</v>
       </c>
       <c r="AA21">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AB21">
         <v>2.33</v>
       </c>
       <c r="AC21">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AD21">
         <v>1.57</v>
       </c>
       <c r="AE21">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AF21">
         <v>1.44</v>
@@ -3805,7 +3805,7 @@
         <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="O38">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P38">
         <v>6.15</v>
@@ -6518,19 +6518,19 @@
         <v>1.92</v>
       </c>
       <c r="S38">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="T38">
         <v>2.28</v>
       </c>
       <c r="U38">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="V38">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W38">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X38">
         <v>1.06</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="AK38">
         <v>2.12</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -1139,10 +1139,10 @@
         <v>3.1</v>
       </c>
       <c r="S5">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="T5">
-        <v>3.42</v>
+        <v>4.5</v>
       </c>
       <c r="U5">
         <v>2.03</v>
@@ -1151,7 +1151,7 @@
         <v>1.73</v>
       </c>
       <c r="W5">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X5">
         <v>1</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="O6">
         <v>3.6</v>
       </c>
       <c r="P6">
-        <v>5.51</v>
+        <v>4.3</v>
       </c>
       <c r="Q6">
         <v>2.21</v>
@@ -1305,46 +1305,46 @@
         <v>1.38</v>
       </c>
       <c r="T6">
+        <v>2.77</v>
+      </c>
+      <c r="U6">
+        <v>2.73</v>
+      </c>
+      <c r="V6">
+        <v>1.35</v>
+      </c>
+      <c r="W6">
+        <v>1.05</v>
+      </c>
+      <c r="X6">
+        <v>1.05</v>
+      </c>
+      <c r="Y6">
+        <v>1.25</v>
+      </c>
+      <c r="Z6">
         <v>3.2</v>
-      </c>
-      <c r="U6">
-        <v>2.62</v>
-      </c>
-      <c r="V6">
-        <v>1.41</v>
-      </c>
-      <c r="W6">
-        <v>1.07</v>
-      </c>
-      <c r="X6">
-        <v>1.01</v>
-      </c>
-      <c r="Y6">
-        <v>1.28</v>
-      </c>
-      <c r="Z6">
-        <v>3.6</v>
       </c>
       <c r="AA6">
         <v>1.89</v>
       </c>
       <c r="AB6">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AC6">
         <v>3.08</v>
       </c>
       <c r="AD6">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE6">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF6">
         <v>1.85</v>
       </c>
       <c r="AG6">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1634,19 +1634,19 @@
         <v>3.05</v>
       </c>
       <c r="U8">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V8">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="W8">
         <v>1.08</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z8">
         <v>3.74</v>
@@ -1655,13 +1655,13 @@
         <v>1.73</v>
       </c>
       <c r="AB8">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AC8">
         <v>2.66</v>
       </c>
       <c r="AD8">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE8">
         <v>1.11</v>
@@ -1788,13 +1788,13 @@
         <v>2</v>
       </c>
       <c r="R9">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="S9">
         <v>1.28</v>
       </c>
       <c r="T9">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="U9">
         <v>2.5</v>
@@ -1948,10 +1948,10 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="R10">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="S10">
         <v>1.33</v>
@@ -1960,10 +1960,10 @@
         <v>2.88</v>
       </c>
       <c r="U10">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V10">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W10">
         <v>1.05</v>
@@ -1978,10 +1978,10 @@
         <v>3.5</v>
       </c>
       <c r="AA10">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AB10">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC10">
         <v>2.92</v>
@@ -1996,7 +1996,7 @@
         <v>1.67</v>
       </c>
       <c r="AG10">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.24</v>
       </c>
       <c r="AK10">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,34 +2102,34 @@
         </is>
       </c>
       <c r="N11">
-        <v>7</v>
+        <v>6.73</v>
       </c>
       <c r="O11">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="P11">
         <v>1.33</v>
       </c>
       <c r="Q11">
-        <v>7.52</v>
+        <v>7.78</v>
       </c>
       <c r="R11">
         <v>2.55</v>
       </c>
       <c r="S11">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="T11">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="U11">
         <v>2.3</v>
       </c>
       <c r="V11">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X11">
         <v>1.01</v>
@@ -2141,25 +2141,25 @@
         <v>4.1</v>
       </c>
       <c r="AA11">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB11">
         <v>2.12</v>
       </c>
       <c r="AC11">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="AD11">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE11">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF11">
         <v>1.95</v>
       </c>
       <c r="AG11">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="O12">
         <v>3.45</v>
@@ -2274,7 +2274,7 @@
         <v>3.2</v>
       </c>
       <c r="Q12">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="R12">
         <v>2.25</v>
@@ -2289,13 +2289,13 @@
         <v>2.41</v>
       </c>
       <c r="V12">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W12">
         <v>1.12</v>
       </c>
       <c r="X12">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
         <v>1.18</v>
@@ -2310,13 +2310,13 @@
         <v>2.04</v>
       </c>
       <c r="AC12">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="AD12">
         <v>1.38</v>
       </c>
       <c r="AE12">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AF12">
         <v>1.57</v>
@@ -2437,10 +2437,10 @@
         <v>2.33</v>
       </c>
       <c r="Q13">
-        <v>3.46</v>
+        <v>3.88</v>
       </c>
       <c r="R13">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="S13">
         <v>1.52</v>
@@ -2455,7 +2455,7 @@
         <v>1.24</v>
       </c>
       <c r="W13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X13">
         <v>1.05</v>
@@ -2467,7 +2467,7 @@
         <v>2.49</v>
       </c>
       <c r="AA13">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="AB13">
         <v>1.52</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.84</v>
+        <v>2.47</v>
       </c>
       <c r="O14">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="P14">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="Q14">
         <v>3.63</v>
@@ -2633,7 +2633,7 @@
         <v>2.2</v>
       </c>
       <c r="AB14">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC14">
         <v>3.9</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AK14">
         <v>1.38</v>
@@ -2920,10 +2920,10 @@
         <v>1.7</v>
       </c>
       <c r="O16">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="P16">
-        <v>4.16</v>
+        <v>4.3</v>
       </c>
       <c r="Q16">
         <v>2.2</v>
@@ -2947,7 +2947,7 @@
         <v>1.07</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
         <v>1.25</v>
@@ -2959,13 +2959,13 @@
         <v>1.73</v>
       </c>
       <c r="AB16">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC16">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AD16">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AE16">
         <v>1.12</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="O19">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P19">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="Q19">
         <v>2.21</v>
@@ -3421,10 +3421,10 @@
         <v>2.23</v>
       </c>
       <c r="S19">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T19">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="U19">
         <v>2.4</v>
@@ -3433,22 +3433,22 @@
         <v>1.49</v>
       </c>
       <c r="W19">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y19">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z19">
         <v>4.2</v>
       </c>
       <c r="AA19">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB19">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC19">
         <v>2.7</v>
@@ -3457,13 +3457,13 @@
         <v>1.4</v>
       </c>
       <c r="AE19">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF19">
         <v>1.58</v>
       </c>
       <c r="AG19">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="O20">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="P20">
-        <v>5.15</v>
+        <v>5.7</v>
       </c>
       <c r="Q20">
         <v>1.78</v>
@@ -3590,10 +3590,10 @@
         <v>4.2</v>
       </c>
       <c r="U20">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="V20">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="W20">
         <v>1.21</v>
@@ -3605,19 +3605,19 @@
         <v>1.06</v>
       </c>
       <c r="Z20">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="AA20">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AB20">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AC20">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AD20">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AE20">
         <v>1.35</v>
@@ -3626,7 +3626,7 @@
         <v>1.5</v>
       </c>
       <c r="AG20">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -4067,22 +4067,22 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="R23">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="S23">
         <v>1.31</v>
       </c>
       <c r="T23">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="U23">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="V23">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W23">
         <v>1.11</v>
@@ -4091,22 +4091,22 @@
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z23">
-        <v>3.97</v>
+        <v>3.96</v>
       </c>
       <c r="AA23">
         <v>1.73</v>
       </c>
       <c r="AB23">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AC23">
         <v>2.74</v>
       </c>
       <c r="AD23">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE23">
         <v>1.1</v>
@@ -4115,7 +4115,7 @@
         <v>1.62</v>
       </c>
       <c r="AG23">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.23</v>
       </c>
       <c r="AK23">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4224,10 +4224,10 @@
         <v>1.52</v>
       </c>
       <c r="O24">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="P24">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="Q24">
         <v>2.12</v>
@@ -4242,19 +4242,19 @@
         <v>4.1</v>
       </c>
       <c r="U24">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="V24">
         <v>1.78</v>
       </c>
       <c r="W24">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z24">
         <v>5.9</v>
@@ -4263,7 +4263,7 @@
         <v>1.4</v>
       </c>
       <c r="AB24">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="AC24">
         <v>1.94</v>
@@ -4272,10 +4272,10 @@
         <v>1.82</v>
       </c>
       <c r="AE24">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AF24">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AG24">
         <v>2.77</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AK24">
         <v>2.06</v>
@@ -4387,28 +4387,28 @@
         <v>1.5</v>
       </c>
       <c r="O25">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="P25">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q25">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="R25">
         <v>2.14</v>
       </c>
       <c r="S25">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="T25">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="U25">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="V25">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W25">
         <v>1.1</v>
@@ -4423,16 +4423,16 @@
         <v>3.5</v>
       </c>
       <c r="AA25">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AB25">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AC25">
         <v>2.88</v>
       </c>
       <c r="AD25">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AE25">
         <v>1.12</v>
@@ -4441,7 +4441,7 @@
         <v>1.83</v>
       </c>
       <c r="AG25">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK25">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,25 +4547,25 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="O26">
         <v>3.2</v>
       </c>
       <c r="P26">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="Q26">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R26">
         <v>2.1</v>
       </c>
       <c r="S26">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T26">
-        <v>2.53</v>
+        <v>2.8</v>
       </c>
       <c r="U26">
         <v>2.99</v>
@@ -4574,10 +4574,10 @@
         <v>1.33</v>
       </c>
       <c r="W26">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
         <v>1.36</v>
@@ -4589,7 +4589,7 @@
         <v>2</v>
       </c>
       <c r="AB26">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AC26">
         <v>3.5</v>
@@ -4598,7 +4598,7 @@
         <v>1.22</v>
       </c>
       <c r="AE26">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF26">
         <v>1.77</v>
@@ -4912,10 +4912,10 @@
         <v>0</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC28">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="O30">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P30">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="Q30">
-        <v>3.84</v>
+        <v>4.35</v>
       </c>
       <c r="R30">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="S30">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T30">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="U30">
-        <v>3.04</v>
+        <v>2.98</v>
       </c>
       <c r="V30">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W30">
         <v>1.05</v>
       </c>
       <c r="X30">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
+        <v>1.27</v>
+      </c>
+      <c r="Z30">
+        <v>3</v>
+      </c>
+      <c r="AA30">
+        <v>2.02</v>
+      </c>
+      <c r="AB30">
+        <v>1.8</v>
+      </c>
+      <c r="AC30">
+        <v>3.46</v>
+      </c>
+      <c r="AD30">
         <v>1.28</v>
       </c>
-      <c r="Z30">
-        <v>3.05</v>
-      </c>
-      <c r="AA30">
-        <v>2.05</v>
-      </c>
-      <c r="AB30">
-        <v>1.74</v>
-      </c>
-      <c r="AC30">
-        <v>3.5</v>
-      </c>
-      <c r="AD30">
-        <v>1.22</v>
-      </c>
       <c r="AE30">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF30">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AG30">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK30">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,16 +5362,16 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O31">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P31">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="Q31">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="R31">
         <v>1.89</v>
@@ -5380,16 +5380,16 @@
         <v>1.53</v>
       </c>
       <c r="T31">
-        <v>2.43</v>
+        <v>2.32</v>
       </c>
       <c r="U31">
         <v>3.42</v>
       </c>
       <c r="V31">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W31">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X31">
         <v>1.1</v>
@@ -5398,28 +5398,28 @@
         <v>1.5</v>
       </c>
       <c r="Z31">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="AA31">
-        <v>2.35</v>
+        <v>2.47</v>
       </c>
       <c r="AB31">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC31">
-        <v>4.55</v>
+        <v>4.88</v>
       </c>
       <c r="AD31">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE31">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF31">
         <v>2.15</v>
       </c>
       <c r="AG31">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AK31">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5534,16 +5534,16 @@
         <v>3.86</v>
       </c>
       <c r="Q32">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="R32">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S32">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T32">
-        <v>2.9</v>
+        <v>2.66</v>
       </c>
       <c r="U32">
         <v>3</v>
@@ -5558,22 +5558,22 @@
         <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z32">
-        <v>2.97</v>
+        <v>3.55</v>
       </c>
       <c r="AA32">
         <v>1.99</v>
       </c>
       <c r="AB32">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AC32">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="AD32">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AE32">
         <v>1.05</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK32">
         <v>1.83</v>
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O33">
         <v>3.1</v>
       </c>
       <c r="P33">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q33">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R33">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="S33">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T33">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="U33">
         <v>3.2</v>
       </c>
       <c r="V33">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W33">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X33">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z33">
-        <v>3.03</v>
+        <v>2.92</v>
       </c>
       <c r="AA33">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AB33">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC33">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="AD33">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE33">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF33">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AG33">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK33">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6023,55 +6023,55 @@
         <v>4.43</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6198,16 +6198,16 @@
         <v>2.56</v>
       </c>
       <c r="U36">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="V36">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W36">
         <v>1.03</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y36">
         <v>1.35</v>
@@ -6225,7 +6225,7 @@
         <v>3.82</v>
       </c>
       <c r="AD36">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE36">
         <v>1.03</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O37">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="P37">
-        <v>3.01</v>
+        <v>2.75</v>
       </c>
       <c r="Q37">
         <v>3</v>
@@ -6355,16 +6355,16 @@
         <v>2.05</v>
       </c>
       <c r="S37">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T37">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="U37">
         <v>3.2</v>
       </c>
       <c r="V37">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W37">
         <v>1.04</v>
@@ -6373,31 +6373,31 @@
         <v>1.05</v>
       </c>
       <c r="Y37">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z37">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="AA37">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AB37">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AC37">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AD37">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE37">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF37">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG37">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK37">
         <v>1.43</v>
@@ -6675,7 +6675,7 @@
         <v>3.45</v>
       </c>
       <c r="Q39">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
       <c r="R39">
         <v>1.91</v>
@@ -6708,13 +6708,13 @@
         <v>2.42</v>
       </c>
       <c r="AB39">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AC39">
         <v>4.45</v>
       </c>
       <c r="AD39">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE39">
         <v>1.01</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AK39">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AL39">
         <v>0</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -1290,10 +1290,10 @@
         <v>1.7</v>
       </c>
       <c r="O6">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P6">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q6">
         <v>2.21</v>
@@ -1302,49 +1302,49 @@
         <v>2.15</v>
       </c>
       <c r="S6">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T6">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="U6">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="V6">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="W6">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z6">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA6">
         <v>1.89</v>
       </c>
       <c r="AB6">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="AC6">
         <v>3.08</v>
       </c>
       <c r="AD6">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE6">
         <v>1.07</v>
       </c>
       <c r="AF6">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG6">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>1.14</v>
       </c>
       <c r="AK6">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2102,40 +2102,40 @@
         </is>
       </c>
       <c r="N11">
-        <v>6.73</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>4.35</v>
+        <v>4.75</v>
       </c>
       <c r="P11">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Q11">
         <v>7.78</v>
       </c>
       <c r="R11">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="S11">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T11">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="U11">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="V11">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="W11">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z11">
         <v>4.1</v>
@@ -2144,19 +2144,19 @@
         <v>1.67</v>
       </c>
       <c r="AB11">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AC11">
         <v>2.71</v>
       </c>
       <c r="AD11">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE11">
         <v>1.15</v>
       </c>
       <c r="AF11">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AG11">
         <v>1.73</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>3.3</v>
+        <v>1.15</v>
       </c>
       <c r="AK11">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2304,7 +2304,7 @@
         <v>3.84</v>
       </c>
       <c r="AA12">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB12">
         <v>2.04</v>
@@ -2754,37 +2754,37 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="O15">
         <v>3.4</v>
       </c>
       <c r="P15">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Q15">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="R15">
         <v>2.3</v>
       </c>
       <c r="S15">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T15">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U15">
         <v>2.5</v>
       </c>
       <c r="V15">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="W15">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
         <v>1.22</v>
@@ -2799,7 +2799,7 @@
         <v>2.08</v>
       </c>
       <c r="AC15">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AD15">
         <v>1.38</v>
@@ -3243,16 +3243,16 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="O18">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P18">
         <v>3.5</v>
       </c>
       <c r="Q18">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="R18">
         <v>2.5</v>
@@ -3270,37 +3270,37 @@
         <v>1.65</v>
       </c>
       <c r="W18">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X18">
         <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z18">
-        <v>5.25</v>
+        <v>4.95</v>
       </c>
       <c r="AA18">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AB18">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AC18">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="AD18">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AE18">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF18">
         <v>1.46</v>
       </c>
       <c r="AG18">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3732,28 +3732,28 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.77</v>
+        <v>2.43</v>
       </c>
       <c r="O21">
-        <v>3.45</v>
+        <v>3.29</v>
       </c>
       <c r="P21">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="Q21">
         <v>3</v>
       </c>
       <c r="R21">
-        <v>2.45</v>
+        <v>2.27</v>
       </c>
       <c r="S21">
         <v>1.24</v>
       </c>
       <c r="T21">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="U21">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="V21">
         <v>1.58</v>
@@ -3774,7 +3774,7 @@
         <v>1.53</v>
       </c>
       <c r="AB21">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AC21">
         <v>2.4</v>
@@ -3783,7 +3783,7 @@
         <v>1.57</v>
       </c>
       <c r="AE21">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF21">
         <v>1.44</v>
@@ -4067,10 +4067,10 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="R23">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="S23">
         <v>1.31</v>
@@ -4079,10 +4079,10 @@
         <v>3.26</v>
       </c>
       <c r="U23">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V23">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W23">
         <v>1.11</v>
@@ -4091,31 +4091,31 @@
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z23">
-        <v>3.96</v>
+        <v>3.99</v>
       </c>
       <c r="AA23">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AB23">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="AC23">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AD23">
         <v>1.4</v>
       </c>
       <c r="AE23">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF23">
         <v>1.62</v>
       </c>
       <c r="AG23">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.23</v>
       </c>
       <c r="AK23">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4384,16 +4384,16 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="O25">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P25">
-        <v>4.8</v>
+        <v>6.65</v>
       </c>
       <c r="Q25">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="R25">
         <v>2.14</v>
@@ -4411,7 +4411,7 @@
         <v>1.42</v>
       </c>
       <c r="W25">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X25">
         <v>1.01</v>
@@ -4423,7 +4423,7 @@
         <v>3.5</v>
       </c>
       <c r="AA25">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB25">
         <v>1.93</v>
@@ -4435,13 +4435,13 @@
         <v>1.32</v>
       </c>
       <c r="AE25">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF25">
         <v>1.83</v>
       </c>
       <c r="AG25">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4547,55 +4547,55 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="O26">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="P26">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q26">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="R26">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="S26">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T26">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="U26">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="V26">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W26">
         <v>1.05</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="Z26">
         <v>3.05</v>
       </c>
       <c r="AA26">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AB26">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AC26">
         <v>3.5</v>
       </c>
       <c r="AD26">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE26">
         <v>1.04</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="AK26">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,80 +6014,80 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.69</v>
+        <v>3</v>
       </c>
       <c r="O35">
-        <v>3.52</v>
+        <v>2.85</v>
       </c>
       <c r="P35">
-        <v>4.43</v>
+        <v>2.25</v>
       </c>
       <c r="Q35">
-        <v>2.2</v>
+        <v>3.84</v>
       </c>
       <c r="R35">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="S35">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T35">
-        <v>2.73</v>
+        <v>2.56</v>
       </c>
       <c r="U35">
-        <v>2.75</v>
+        <v>3.04</v>
       </c>
       <c r="V35">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W35">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y35">
+        <v>1.35</v>
+      </c>
+      <c r="Z35">
+        <v>2.74</v>
+      </c>
+      <c r="AA35">
+        <v>2.14</v>
+      </c>
+      <c r="AB35">
+        <v>1.62</v>
+      </c>
+      <c r="AC35">
+        <v>3.82</v>
+      </c>
+      <c r="AD35">
+        <v>1.2</v>
+      </c>
+      <c r="AE35">
+        <v>1.03</v>
+      </c>
+      <c r="AF35">
+        <v>1.85</v>
+      </c>
+      <c r="AG35">
+        <v>1.82</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
         <v>1.27</v>
       </c>
-      <c r="Z35">
-        <v>3.14</v>
-      </c>
-      <c r="AA35">
-        <v>1.91</v>
-      </c>
-      <c r="AB35">
-        <v>1.78</v>
-      </c>
-      <c r="AC35">
-        <v>3.25</v>
-      </c>
-      <c r="AD35">
-        <v>1.28</v>
-      </c>
-      <c r="AE35">
-        <v>1.06</v>
-      </c>
-      <c r="AF35">
-        <v>1.84</v>
-      </c>
-      <c r="AG35">
-        <v>1.83</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.21</v>
-      </c>
       <c r="AK35">
-        <v>2.1</v>
+        <v>1.31</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>3</v>
+        <v>1.69</v>
       </c>
       <c r="O36">
-        <v>2.85</v>
+        <v>3.52</v>
       </c>
       <c r="P36">
-        <v>2.25</v>
+        <v>4.43</v>
       </c>
       <c r="Q36">
-        <v>3.84</v>
+        <v>2.2</v>
       </c>
       <c r="R36">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="S36">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="T36">
-        <v>2.56</v>
+        <v>2.73</v>
       </c>
       <c r="U36">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="V36">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W36">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X36">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="Z36">
-        <v>2.74</v>
+        <v>3.14</v>
       </c>
       <c r="AA36">
-        <v>2.14</v>
+        <v>1.91</v>
       </c>
       <c r="AB36">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AC36">
-        <v>3.82</v>
+        <v>3.25</v>
       </c>
       <c r="AD36">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AE36">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF36">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG36">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AK36">
-        <v>1.31</v>
+        <v>2.1</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="O38">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P38">
         <v>6.15</v>
@@ -6518,13 +6518,13 @@
         <v>1.92</v>
       </c>
       <c r="S38">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="T38">
         <v>2.28</v>
       </c>
       <c r="U38">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="V38">
         <v>1.21</v>
@@ -6545,7 +6545,7 @@
         <v>2.6</v>
       </c>
       <c r="AB38">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AC38">
         <v>5</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="AK38">
         <v>2.12</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="O12">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="P12">
         <v>3.2</v>
       </c>
       <c r="Q12">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="R12">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S12">
         <v>1.3</v>
@@ -2295,28 +2295,28 @@
         <v>1.12</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z12">
-        <v>3.84</v>
+        <v>4.14</v>
       </c>
       <c r="AA12">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AB12">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="AC12">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AD12">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE12">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF12">
         <v>1.57</v>
@@ -2600,34 +2600,34 @@
         <v>2.25</v>
       </c>
       <c r="Q14">
-        <v>3.63</v>
+        <v>3.77</v>
       </c>
       <c r="R14">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="S14">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="T14">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="U14">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="V14">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W14">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X14">
         <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z14">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AA14">
         <v>2.2</v>
@@ -2636,7 +2636,7 @@
         <v>1.65</v>
       </c>
       <c r="AC14">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="AD14">
         <v>1.18</v>
@@ -2664,7 +2664,7 @@
         <v>1.32</v>
       </c>
       <c r="AK14">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -4224,10 +4224,10 @@
         <v>1.52</v>
       </c>
       <c r="O24">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="P24">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="Q24">
         <v>2.12</v>
@@ -4248,7 +4248,7 @@
         <v>1.78</v>
       </c>
       <c r="W24">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X24">
         <v>1.01</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="AK24">
         <v>2.06</v>
@@ -4879,7 +4879,7 @@
         <v>3.7</v>
       </c>
       <c r="P28">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5211,7 +5211,7 @@
         <v>4.35</v>
       </c>
       <c r="R30">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="S30">
         <v>1.38</v>
@@ -5235,13 +5235,13 @@
         <v>1.27</v>
       </c>
       <c r="Z30">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="AA30">
         <v>2.02</v>
       </c>
       <c r="AB30">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC30">
         <v>3.46</v>
@@ -5253,10 +5253,10 @@
         <v>1.08</v>
       </c>
       <c r="AF30">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AG30">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5365,10 +5365,10 @@
         <v>1.85</v>
       </c>
       <c r="O31">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P31">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="Q31">
         <v>2.58</v>
@@ -5377,19 +5377,19 @@
         <v>1.89</v>
       </c>
       <c r="S31">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="T31">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="U31">
         <v>3.42</v>
       </c>
       <c r="V31">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="W31">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X31">
         <v>1.1</v>
@@ -5404,22 +5404,22 @@
         <v>2.47</v>
       </c>
       <c r="AB31">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AC31">
-        <v>4.88</v>
+        <v>4.75</v>
       </c>
       <c r="AD31">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE31">
         <v>1.01</v>
       </c>
       <c r="AF31">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AG31">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.32</v>
       </c>
       <c r="AK31">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5534,31 +5534,31 @@
         <v>3.86</v>
       </c>
       <c r="Q32">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R32">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="S32">
         <v>1.41</v>
       </c>
       <c r="T32">
-        <v>2.66</v>
+        <v>2.79</v>
       </c>
       <c r="U32">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="V32">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Z32">
         <v>3.55</v>
@@ -5567,22 +5567,22 @@
         <v>1.99</v>
       </c>
       <c r="AB32">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="AC32">
-        <v>3.73</v>
+        <v>3.25</v>
       </c>
       <c r="AD32">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AE32">
         <v>1.05</v>
       </c>
       <c r="AF32">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="AG32">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O33">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P33">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="Q33">
         <v>2.75</v>
@@ -5712,40 +5712,40 @@
         <v>3.2</v>
       </c>
       <c r="V33">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W33">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X33">
         <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="Z33">
-        <v>2.92</v>
+        <v>3.04</v>
       </c>
       <c r="AA33">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="AB33">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AC33">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="AD33">
         <v>1.21</v>
       </c>
       <c r="AE33">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF33">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG33">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AK33">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6708,7 +6708,7 @@
         <v>2.42</v>
       </c>
       <c r="AB39">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AC39">
         <v>4.45</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -1960,10 +1960,10 @@
         <v>2.88</v>
       </c>
       <c r="U10">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="V10">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W10">
         <v>1.05</v>
@@ -1978,10 +1978,10 @@
         <v>3.5</v>
       </c>
       <c r="AA10">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB10">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AC10">
         <v>2.92</v>
@@ -2102,31 +2102,31 @@
         </is>
       </c>
       <c r="N11">
-        <v>7</v>
+        <v>10.6</v>
       </c>
       <c r="O11">
         <v>4.75</v>
       </c>
       <c r="P11">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Q11">
-        <v>7.78</v>
+        <v>7.5</v>
       </c>
       <c r="R11">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="S11">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T11">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="U11">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="V11">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W11">
         <v>1.08</v>
@@ -2138,7 +2138,7 @@
         <v>1.18</v>
       </c>
       <c r="Z11">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AA11">
         <v>1.67</v>
@@ -2153,13 +2153,13 @@
         <v>1.4</v>
       </c>
       <c r="AE11">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF11">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AG11">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.15</v>
+        <v>3.12</v>
       </c>
       <c r="AK11">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -3406,55 +3406,55 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="O19">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="P19">
         <v>3.75</v>
       </c>
       <c r="Q19">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="R19">
-        <v>2.23</v>
+        <v>2.48</v>
       </c>
       <c r="S19">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T19">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="U19">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V19">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W19">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X19">
         <v>1.04</v>
       </c>
       <c r="Y19">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z19">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AA19">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AB19">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AC19">
         <v>2.7</v>
       </c>
       <c r="AD19">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE19">
         <v>1.18</v>
@@ -3479,7 +3479,7 @@
         <v>1.14</v>
       </c>
       <c r="AK19">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4390,13 +4390,13 @@
         <v>3.9</v>
       </c>
       <c r="P25">
-        <v>6.65</v>
+        <v>4.6</v>
       </c>
       <c r="Q25">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="R25">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="S25">
         <v>1.35</v>
@@ -4405,10 +4405,10 @@
         <v>2.9</v>
       </c>
       <c r="U25">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="V25">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W25">
         <v>1.06</v>
@@ -4423,10 +4423,10 @@
         <v>3.5</v>
       </c>
       <c r="AA25">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB25">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AC25">
         <v>2.88</v>
@@ -4438,10 +4438,10 @@
         <v>1.08</v>
       </c>
       <c r="AF25">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG25">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>1.23</v>
       </c>
       <c r="AK25">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="O28">
         <v>3.7</v>
       </c>
       <c r="P28">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5202,61 +5202,61 @@
         <v>3.6</v>
       </c>
       <c r="O30">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P30">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="Q30">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="R30">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="S30">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T30">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="U30">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="V30">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W30">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X30">
         <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="Z30">
         <v>3.14</v>
       </c>
       <c r="AA30">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AB30">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AC30">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="AD30">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE30">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF30">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AG30">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,65 +5362,65 @@
         </is>
       </c>
       <c r="N31">
+        <v>2.05</v>
+      </c>
+      <c r="O31">
+        <v>3.2</v>
+      </c>
+      <c r="P31">
+        <v>3.7</v>
+      </c>
+      <c r="Q31">
+        <v>2.75</v>
+      </c>
+      <c r="R31">
+        <v>1.93</v>
+      </c>
+      <c r="S31">
+        <v>1.46</v>
+      </c>
+      <c r="T31">
+        <v>2.5</v>
+      </c>
+      <c r="U31">
+        <v>3.2</v>
+      </c>
+      <c r="V31">
+        <v>1.3</v>
+      </c>
+      <c r="W31">
+        <v>1.05</v>
+      </c>
+      <c r="X31">
+        <v>1.02</v>
+      </c>
+      <c r="Y31">
+        <v>1.38</v>
+      </c>
+      <c r="Z31">
+        <v>3.04</v>
+      </c>
+      <c r="AA31">
+        <v>2.17</v>
+      </c>
+      <c r="AB31">
+        <v>1.63</v>
+      </c>
+      <c r="AC31">
+        <v>4.1</v>
+      </c>
+      <c r="AD31">
+        <v>1.21</v>
+      </c>
+      <c r="AE31">
+        <v>1.05</v>
+      </c>
+      <c r="AF31">
+        <v>1.83</v>
+      </c>
+      <c r="AG31">
         <v>1.85</v>
       </c>
-      <c r="O31">
-        <v>3</v>
-      </c>
-      <c r="P31">
-        <v>4</v>
-      </c>
-      <c r="Q31">
-        <v>2.58</v>
-      </c>
-      <c r="R31">
-        <v>1.89</v>
-      </c>
-      <c r="S31">
-        <v>1.54</v>
-      </c>
-      <c r="T31">
-        <v>2.27</v>
-      </c>
-      <c r="U31">
-        <v>3.42</v>
-      </c>
-      <c r="V31">
-        <v>1.26</v>
-      </c>
-      <c r="W31">
-        <v>1</v>
-      </c>
-      <c r="X31">
-        <v>1.1</v>
-      </c>
-      <c r="Y31">
-        <v>1.5</v>
-      </c>
-      <c r="Z31">
-        <v>2.55</v>
-      </c>
-      <c r="AA31">
-        <v>2.47</v>
-      </c>
-      <c r="AB31">
-        <v>1.51</v>
-      </c>
-      <c r="AC31">
-        <v>4.75</v>
-      </c>
-      <c r="AD31">
-        <v>1.17</v>
-      </c>
-      <c r="AE31">
-        <v>1.01</v>
-      </c>
-      <c r="AF31">
-        <v>2.02</v>
-      </c>
-      <c r="AG31">
-        <v>1.65</v>
-      </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK31">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="O32">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P32">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="Q32">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="R32">
-        <v>2.18</v>
+        <v>1.89</v>
       </c>
       <c r="S32">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="T32">
-        <v>2.79</v>
+        <v>2.27</v>
       </c>
       <c r="U32">
-        <v>3.09</v>
+        <v>3.42</v>
       </c>
       <c r="V32">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="W32">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Y32">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="Z32">
-        <v>3.55</v>
+        <v>2.55</v>
       </c>
       <c r="AA32">
-        <v>1.99</v>
+        <v>2.47</v>
       </c>
       <c r="AB32">
-        <v>1.88</v>
+        <v>1.51</v>
       </c>
       <c r="AC32">
-        <v>3.25</v>
+        <v>4.75</v>
       </c>
       <c r="AD32">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AE32">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF32">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="AG32">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AK32">
         <v>1.83</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,80 +5688,80 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="O33">
         <v>3.2</v>
       </c>
       <c r="P33">
-        <v>3.7</v>
+        <v>3.86</v>
       </c>
       <c r="Q33">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="R33">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="S33">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="T33">
-        <v>2.5</v>
+        <v>2.79</v>
       </c>
       <c r="U33">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="V33">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W33">
         <v>1.05</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z33">
-        <v>3.04</v>
+        <v>3.55</v>
       </c>
       <c r="AA33">
-        <v>2.17</v>
+        <v>1.99</v>
       </c>
       <c r="AB33">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="AC33">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="AD33">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AE33">
         <v>1.05</v>
       </c>
       <c r="AF33">
+        <v>1.86</v>
+      </c>
+      <c r="AG33">
+        <v>1.82</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33">
+        <v>1.22</v>
+      </c>
+      <c r="AK33">
         <v>1.83</v>
-      </c>
-      <c r="AG33">
-        <v>1.85</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ33">
-        <v>1.29</v>
-      </c>
-      <c r="AK33">
-        <v>1.73</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6343,61 +6343,61 @@
         <v>2.3</v>
       </c>
       <c r="O37">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P37">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="Q37">
         <v>3</v>
       </c>
       <c r="R37">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="S37">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T37">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="U37">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="V37">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W37">
         <v>1.04</v>
       </c>
       <c r="X37">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z37">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AA37">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AB37">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AC37">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="AD37">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE37">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF37">
         <v>1.8</v>
       </c>
       <c r="AG37">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.36</v>
       </c>
       <c r="AK37">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6681,10 +6681,10 @@
         <v>1.91</v>
       </c>
       <c r="S39">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="T39">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="U39">
         <v>3.38</v>
@@ -6693,37 +6693,37 @@
         <v>1.25</v>
       </c>
       <c r="W39">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X39">
         <v>1.05</v>
       </c>
       <c r="Y39">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="Z39">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="AA39">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="AB39">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AC39">
-        <v>4.45</v>
+        <v>4.75</v>
       </c>
       <c r="AD39">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE39">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF39">
         <v>2.04</v>
       </c>
       <c r="AG39">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.27</v>
       </c>
       <c r="AK39">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AL39">
         <v>0</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -1133,55 +1133,55 @@
         <v>1.14</v>
       </c>
       <c r="Q5">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="R5">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="S5">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="T5">
-        <v>4.5</v>
+        <v>3.34</v>
       </c>
       <c r="U5">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="V5">
         <v>1.73</v>
       </c>
       <c r="W5">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X5">
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z5">
         <v>4.5</v>
       </c>
       <c r="AA5">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AB5">
-        <v>2.33</v>
+        <v>2.59</v>
       </c>
       <c r="AC5">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AD5">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AE5">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AF5">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AG5">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>2.95</v>
+        <v>1.08</v>
       </c>
       <c r="AK5">
         <v>1.03</v>
@@ -1287,34 +1287,34 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="O6">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="P6">
-        <v>4.2</v>
+        <v>5.51</v>
       </c>
       <c r="Q6">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="R6">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S6">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T6">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="U6">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="V6">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
         <v>1.01</v>
@@ -1323,28 +1323,28 @@
         <v>1.28</v>
       </c>
       <c r="Z6">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA6">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AB6">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC6">
         <v>3.08</v>
       </c>
       <c r="AD6">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE6">
         <v>1.07</v>
       </c>
       <c r="AF6">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG6">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AK6">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1622,10 +1622,10 @@
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>4.47</v>
+        <v>3.74</v>
       </c>
       <c r="R8">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="S8">
         <v>1.3</v>
@@ -1634,10 +1634,10 @@
         <v>3.05</v>
       </c>
       <c r="U8">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="V8">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="W8">
         <v>1.08</v>
@@ -1646,28 +1646,28 @@
         <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z8">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="AA8">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AB8">
         <v>2.05</v>
       </c>
       <c r="AC8">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="AD8">
         <v>1.36</v>
       </c>
       <c r="AE8">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF8">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG8">
         <v>2.02</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1785,13 +1785,13 @@
         <v>4.2</v>
       </c>
       <c r="Q9">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="R9">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="S9">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T9">
         <v>3.25</v>
@@ -1800,7 +1800,7 @@
         <v>2.5</v>
       </c>
       <c r="V9">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W9">
         <v>1.07</v>
@@ -1809,16 +1809,16 @@
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z9">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="AA9">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AB9">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="AC9">
         <v>2.7</v>
@@ -1827,13 +1827,13 @@
         <v>1.36</v>
       </c>
       <c r="AE9">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF9">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AG9">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK9">
-        <v>1.88</v>
+        <v>2.01</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2271,13 +2271,13 @@
         <v>3.8</v>
       </c>
       <c r="P12">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q12">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="R12">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="S12">
         <v>1.3</v>
@@ -2286,37 +2286,37 @@
         <v>3.08</v>
       </c>
       <c r="U12">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="V12">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W12">
         <v>1.12</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z12">
-        <v>4.14</v>
+        <v>3.84</v>
       </c>
       <c r="AA12">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB12">
         <v>2.14</v>
       </c>
       <c r="AC12">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AD12">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE12">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF12">
         <v>1.57</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AK12">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>2.33</v>
       </c>
       <c r="Q13">
-        <v>3.88</v>
+        <v>3.46</v>
       </c>
       <c r="R13">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="S13">
         <v>1.52</v>
@@ -2455,7 +2455,7 @@
         <v>1.24</v>
       </c>
       <c r="W13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X13">
         <v>1.05</v>
@@ -2467,10 +2467,10 @@
         <v>2.49</v>
       </c>
       <c r="AA13">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="AB13">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AC13">
         <v>4.6</v>
@@ -2485,7 +2485,7 @@
         <v>2.01</v>
       </c>
       <c r="AG13">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AK13">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,43 +2591,43 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.47</v>
+        <v>2.95</v>
       </c>
       <c r="O14">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="P14">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="Q14">
-        <v>3.77</v>
+        <v>3.35</v>
       </c>
       <c r="R14">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="S14">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T14">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="U14">
         <v>3.16</v>
       </c>
       <c r="V14">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W14">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y14">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="Z14">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AA14">
         <v>2.2</v>
@@ -2636,19 +2636,19 @@
         <v>1.65</v>
       </c>
       <c r="AC14">
-        <v>3.88</v>
+        <v>4.07</v>
       </c>
       <c r="AD14">
         <v>1.18</v>
       </c>
       <c r="AE14">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF14">
         <v>1.86</v>
       </c>
       <c r="AG14">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="AK14">
         <v>1.36</v>
@@ -2754,49 +2754,49 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="O15">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P15">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q15">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="R15">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="S15">
         <v>1.32</v>
       </c>
       <c r="T15">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="U15">
         <v>2.5</v>
       </c>
       <c r="V15">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
         <v>1.22</v>
       </c>
       <c r="Z15">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA15">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AB15">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AC15">
         <v>2.8</v>
@@ -2808,10 +2808,10 @@
         <v>1.17</v>
       </c>
       <c r="AF15">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG15">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK15">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2920,10 +2920,10 @@
         <v>1.7</v>
       </c>
       <c r="O16">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P16">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="Q16">
         <v>2.2</v>
@@ -2932,25 +2932,25 @@
         <v>2.22</v>
       </c>
       <c r="S16">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T16">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U16">
         <v>2.56</v>
       </c>
       <c r="V16">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W16">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z16">
         <v>3.78</v>
@@ -2959,13 +2959,13 @@
         <v>1.73</v>
       </c>
       <c r="AB16">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC16">
         <v>2.95</v>
       </c>
       <c r="AD16">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE16">
         <v>1.12</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK16">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3246,10 +3246,10 @@
         <v>1.73</v>
       </c>
       <c r="O18">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="P18">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="Q18">
         <v>2.32</v>
@@ -3258,49 +3258,49 @@
         <v>2.5</v>
       </c>
       <c r="S18">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T18">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="U18">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V18">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="W18">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X18">
         <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z18">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="AA18">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AB18">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AC18">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AD18">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE18">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF18">
         <v>1.46</v>
       </c>
       <c r="AG18">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK18">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="O20">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="P20">
-        <v>5.7</v>
+        <v>5.15</v>
       </c>
       <c r="Q20">
         <v>1.78</v>
@@ -3587,10 +3587,10 @@
         <v>1.16</v>
       </c>
       <c r="T20">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="U20">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V20">
         <v>1.8</v>
@@ -3608,25 +3608,25 @@
         <v>6.25</v>
       </c>
       <c r="AA20">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB20">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AC20">
         <v>1.85</v>
       </c>
       <c r="AD20">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AE20">
         <v>1.35</v>
       </c>
       <c r="AF20">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG20">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AK20">
         <v>2.83</v>
@@ -3738,25 +3738,25 @@
         <v>3.29</v>
       </c>
       <c r="P21">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="Q21">
         <v>3</v>
       </c>
       <c r="R21">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="S21">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T21">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="U21">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="V21">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W21">
         <v>1.11</v>
@@ -3774,19 +3774,19 @@
         <v>1.53</v>
       </c>
       <c r="AB21">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AC21">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AD21">
         <v>1.57</v>
       </c>
       <c r="AE21">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF21">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG21">
         <v>2.5</v>
@@ -3805,7 +3805,7 @@
         <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q23">
         <v>2.72</v>
@@ -4073,31 +4073,31 @@
         <v>2.18</v>
       </c>
       <c r="S23">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T23">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="U23">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V23">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W23">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z23">
-        <v>3.99</v>
+        <v>3.6</v>
       </c>
       <c r="AA23">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AB23">
         <v>2.06</v>
@@ -4106,13 +4106,13 @@
         <v>2.7</v>
       </c>
       <c r="AD23">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE23">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF23">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG23">
         <v>2.21</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK23">
         <v>1.56</v>
@@ -4221,22 +4221,22 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="O24">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="P24">
         <v>3.85</v>
       </c>
       <c r="Q24">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="R24">
-        <v>2.57</v>
+        <v>2.51</v>
       </c>
       <c r="S24">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T24">
         <v>4.1</v>
@@ -4254,25 +4254,25 @@
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z24">
         <v>5.9</v>
       </c>
       <c r="AA24">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AB24">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="AC24">
         <v>1.94</v>
       </c>
       <c r="AD24">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="AE24">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AF24">
         <v>1.39</v>
@@ -4294,7 +4294,7 @@
         <v>1.19</v>
       </c>
       <c r="AK24">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="O26">
         <v>3.04</v>
       </c>
       <c r="P26">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="Q26">
         <v>3.5</v>
@@ -4562,28 +4562,28 @@
         <v>1.96</v>
       </c>
       <c r="S26">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T26">
         <v>2.59</v>
       </c>
       <c r="U26">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="V26">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W26">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
         <v>1.28</v>
       </c>
       <c r="Z26">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AA26">
         <v>2.07</v>
@@ -4595,10 +4595,10 @@
         <v>3.5</v>
       </c>
       <c r="AD26">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE26">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF26">
         <v>1.77</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AK26">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5036,58 +5036,58 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="O29">
         <v>3.75</v>
       </c>
       <c r="P29">
-        <v>3.9</v>
+        <v>3.39</v>
       </c>
       <c r="Q29">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="R29">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="S29">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="T29">
-        <v>3.84</v>
+        <v>4.5</v>
       </c>
       <c r="U29">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="V29">
         <v>1.74</v>
       </c>
       <c r="W29">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z29">
-        <v>5.55</v>
+        <v>5.85</v>
       </c>
       <c r="AA29">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB29">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="AC29">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AD29">
-        <v>1.77</v>
+        <v>1.96</v>
       </c>
       <c r="AE29">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AF29">
         <v>1.42</v>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK29">
         <v>2.1</v>
@@ -5546,7 +5546,7 @@
         <v>2.27</v>
       </c>
       <c r="U32">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="V32">
         <v>1.26</v>
@@ -5573,7 +5573,7 @@
         <v>4.75</v>
       </c>
       <c r="AD32">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE32">
         <v>1.01</v>
@@ -5700,7 +5700,7 @@
         <v>2.5</v>
       </c>
       <c r="R33">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="S33">
         <v>1.41</v>
@@ -5718,19 +5718,19 @@
         <v>1.05</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y33">
         <v>1.35</v>
       </c>
       <c r="Z33">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AA33">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="AB33">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AC33">
         <v>3.25</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="O34">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P34">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="Q34">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R34">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S34">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T34">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="U34">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="V34">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X34">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="Z34">
         <v>3.5</v>
       </c>
       <c r="AA34">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AB34">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC34">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AD34">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE34">
         <v>1.07</v>
       </c>
       <c r="AF34">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AG34">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK34">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6017,28 +6017,28 @@
         <v>3</v>
       </c>
       <c r="O35">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="P35">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q35">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="R35">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="S35">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="T35">
         <v>2.56</v>
       </c>
       <c r="U35">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="V35">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W35">
         <v>1.03</v>
@@ -6047,31 +6047,31 @@
         <v>1.05</v>
       </c>
       <c r="Y35">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z35">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AA35">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AB35">
         <v>1.62</v>
       </c>
       <c r="AC35">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="AD35">
         <v>1.2</v>
       </c>
       <c r="AE35">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF35">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG35">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.27</v>
       </c>
       <c r="AK35">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6189,13 +6189,13 @@
         <v>2.2</v>
       </c>
       <c r="R36">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="S36">
         <v>1.36</v>
       </c>
       <c r="T36">
-        <v>2.73</v>
+        <v>2.89</v>
       </c>
       <c r="U36">
         <v>2.75</v>
@@ -6222,10 +6222,10 @@
         <v>1.78</v>
       </c>
       <c r="AC36">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AD36">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE36">
         <v>1.06</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK36">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6509,31 +6509,31 @@
         <v>3.4</v>
       </c>
       <c r="P38">
-        <v>6.15</v>
+        <v>5.25</v>
       </c>
       <c r="Q38">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="R38">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="S38">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="T38">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="U38">
         <v>3.5</v>
       </c>
       <c r="V38">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="W38">
         <v>1</v>
       </c>
       <c r="X38">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y38">
         <v>1.51</v>
@@ -6560,7 +6560,7 @@
         <v>2.48</v>
       </c>
       <c r="AG38">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -5371,16 +5371,16 @@
         <v>3.7</v>
       </c>
       <c r="Q31">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="R31">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="S31">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T31">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="U31">
         <v>3.2</v>
@@ -5407,13 +5407,13 @@
         <v>1.63</v>
       </c>
       <c r="AC31">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="AD31">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AE31">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF31">
         <v>1.83</v>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="O32">
         <v>3</v>
@@ -5546,7 +5546,7 @@
         <v>2.27</v>
       </c>
       <c r="U32">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="V32">
         <v>1.26</v>
@@ -5564,10 +5564,10 @@
         <v>2.55</v>
       </c>
       <c r="AA32">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AB32">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AC32">
         <v>4.75</v>
@@ -5576,7 +5576,7 @@
         <v>1.13</v>
       </c>
       <c r="AE32">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF32">
         <v>2.02</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AK32">
         <v>1.83</v>
@@ -5703,19 +5703,19 @@
         <v>2.07</v>
       </c>
       <c r="S33">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="T33">
+        <v>2.66</v>
+      </c>
+      <c r="U33">
         <v>2.79</v>
       </c>
-      <c r="U33">
-        <v>3.09</v>
-      </c>
       <c r="V33">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W33">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X33">
         <v>1.04</v>
@@ -5724,19 +5724,19 @@
         <v>1.35</v>
       </c>
       <c r="Z33">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AA33">
         <v>2.1</v>
       </c>
       <c r="AB33">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AC33">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="AD33">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE33">
         <v>1.05</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,80 +5362,80 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="O31">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P31">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="Q31">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="R31">
-        <v>2.07</v>
+        <v>1.89</v>
       </c>
       <c r="S31">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="T31">
+        <v>2.27</v>
+      </c>
+      <c r="U31">
+        <v>3.42</v>
+      </c>
+      <c r="V31">
+        <v>1.26</v>
+      </c>
+      <c r="W31">
+        <v>1</v>
+      </c>
+      <c r="X31">
+        <v>1.1</v>
+      </c>
+      <c r="Y31">
+        <v>1.5</v>
+      </c>
+      <c r="Z31">
         <v>2.55</v>
       </c>
-      <c r="U31">
-        <v>3.2</v>
-      </c>
-      <c r="V31">
-        <v>1.3</v>
-      </c>
-      <c r="W31">
+      <c r="AA31">
+        <v>2.45</v>
+      </c>
+      <c r="AB31">
+        <v>1.53</v>
+      </c>
+      <c r="AC31">
+        <v>4.75</v>
+      </c>
+      <c r="AD31">
+        <v>1.13</v>
+      </c>
+      <c r="AE31">
         <v>1.05</v>
       </c>
-      <c r="X31">
-        <v>1.02</v>
-      </c>
-      <c r="Y31">
-        <v>1.38</v>
-      </c>
-      <c r="Z31">
-        <v>3.04</v>
-      </c>
-      <c r="AA31">
-        <v>2.17</v>
-      </c>
-      <c r="AB31">
-        <v>1.63</v>
-      </c>
-      <c r="AC31">
-        <v>3.58</v>
-      </c>
-      <c r="AD31">
-        <v>1.26</v>
-      </c>
-      <c r="AE31">
-        <v>1.03</v>
-      </c>
       <c r="AF31">
+        <v>2.02</v>
+      </c>
+      <c r="AG31">
+        <v>1.65</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
+        <v>1.2</v>
+      </c>
+      <c r="AK31">
         <v>1.83</v>
-      </c>
-      <c r="AG31">
-        <v>1.85</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1.29</v>
-      </c>
-      <c r="AK31">
-        <v>1.73</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="O32">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P32">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="Q32">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="R32">
-        <v>1.89</v>
+        <v>2.07</v>
       </c>
       <c r="S32">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="T32">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="U32">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="V32">
+        <v>1.3</v>
+      </c>
+      <c r="W32">
+        <v>1.05</v>
+      </c>
+      <c r="X32">
+        <v>1.02</v>
+      </c>
+      <c r="Y32">
+        <v>1.38</v>
+      </c>
+      <c r="Z32">
+        <v>3.04</v>
+      </c>
+      <c r="AA32">
+        <v>2.17</v>
+      </c>
+      <c r="AB32">
+        <v>1.63</v>
+      </c>
+      <c r="AC32">
+        <v>3.58</v>
+      </c>
+      <c r="AD32">
         <v>1.26</v>
       </c>
-      <c r="W32">
-        <v>1</v>
-      </c>
-      <c r="X32">
-        <v>1.1</v>
-      </c>
-      <c r="Y32">
-        <v>1.5</v>
-      </c>
-      <c r="Z32">
-        <v>2.55</v>
-      </c>
-      <c r="AA32">
-        <v>2.45</v>
-      </c>
-      <c r="AB32">
-        <v>1.53</v>
-      </c>
-      <c r="AC32">
-        <v>4.75</v>
-      </c>
-      <c r="AD32">
-        <v>1.13</v>
-      </c>
       <c r="AE32">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF32">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AG32">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK32">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL32">
         <v>0</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -1948,10 +1948,10 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R10">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="S10">
         <v>1.33</v>
@@ -1966,7 +1966,7 @@
         <v>1.4</v>
       </c>
       <c r="W10">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X10">
         <v>1.01</v>
@@ -1978,10 +1978,10 @@
         <v>3.5</v>
       </c>
       <c r="AA10">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AB10">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AC10">
         <v>2.92</v>
@@ -1996,7 +1996,7 @@
         <v>1.67</v>
       </c>
       <c r="AG10">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         <v>2.92</v>
       </c>
       <c r="O13">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="P13">
         <v>2.33</v>
@@ -2443,10 +2443,10 @@
         <v>1.86</v>
       </c>
       <c r="S13">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="T13">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="U13">
         <v>3.44</v>
@@ -2455,7 +2455,7 @@
         <v>1.24</v>
       </c>
       <c r="W13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X13">
         <v>1.05</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.45</v>
+        <v>1.29</v>
       </c>
       <c r="AK13">
         <v>1.3</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="O14">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="P14">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="Q14">
         <v>3.35</v>
@@ -2615,7 +2615,7 @@
         <v>3.16</v>
       </c>
       <c r="V14">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W14">
         <v>1.05</v>
@@ -2627,7 +2627,7 @@
         <v>1.38</v>
       </c>
       <c r="Z14">
-        <v>2.74</v>
+        <v>2.98</v>
       </c>
       <c r="AA14">
         <v>2.2</v>
@@ -2636,7 +2636,7 @@
         <v>1.65</v>
       </c>
       <c r="AC14">
-        <v>4.07</v>
+        <v>4.2</v>
       </c>
       <c r="AD14">
         <v>1.18</v>
@@ -2760,22 +2760,22 @@
         <v>3.3</v>
       </c>
       <c r="P15">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="Q15">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="R15">
         <v>2.34</v>
       </c>
       <c r="S15">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T15">
         <v>3.05</v>
       </c>
       <c r="U15">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V15">
         <v>1.46</v>
@@ -2787,7 +2787,7 @@
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z15">
         <v>4.1</v>
@@ -2811,7 +2811,7 @@
         <v>1.57</v>
       </c>
       <c r="AG15">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="O18">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="P18">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Q18">
         <v>2.32</v>
@@ -3264,7 +3264,7 @@
         <v>3.8</v>
       </c>
       <c r="U18">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="V18">
         <v>1.6</v>
@@ -3276,19 +3276,19 @@
         <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z18">
-        <v>5</v>
+        <v>5.39</v>
       </c>
       <c r="AA18">
         <v>1.49</v>
       </c>
       <c r="AB18">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="AC18">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD18">
         <v>1.62</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK18">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3732,22 +3732,22 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.43</v>
+        <v>2.8</v>
       </c>
       <c r="O21">
         <v>3.29</v>
       </c>
       <c r="P21">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="Q21">
         <v>3</v>
       </c>
       <c r="R21">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="S21">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T21">
         <v>3.5</v>
@@ -3771,7 +3771,7 @@
         <v>4.9</v>
       </c>
       <c r="AA21">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB21">
         <v>2.33</v>
@@ -3783,10 +3783,10 @@
         <v>1.57</v>
       </c>
       <c r="AE21">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AF21">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG21">
         <v>2.5</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK21">
         <v>1.39</v>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N27">
@@ -4719,55 +4719,55 @@
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,80 +5525,80 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="O32">
         <v>3.2</v>
       </c>
       <c r="P32">
-        <v>3.7</v>
+        <v>3.86</v>
       </c>
       <c r="Q32">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="R32">
         <v>2.07</v>
       </c>
       <c r="S32">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T32">
-        <v>2.55</v>
+        <v>2.66</v>
       </c>
       <c r="U32">
-        <v>3.2</v>
+        <v>2.79</v>
       </c>
       <c r="V32">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="W32">
+        <v>1.04</v>
+      </c>
+      <c r="X32">
+        <v>1.04</v>
+      </c>
+      <c r="Y32">
+        <v>1.35</v>
+      </c>
+      <c r="Z32">
+        <v>3.14</v>
+      </c>
+      <c r="AA32">
+        <v>2.1</v>
+      </c>
+      <c r="AB32">
+        <v>1.7</v>
+      </c>
+      <c r="AC32">
+        <v>3.8</v>
+      </c>
+      <c r="AD32">
+        <v>1.22</v>
+      </c>
+      <c r="AE32">
         <v>1.05</v>
       </c>
-      <c r="X32">
-        <v>1.02</v>
-      </c>
-      <c r="Y32">
-        <v>1.38</v>
-      </c>
-      <c r="Z32">
-        <v>3.04</v>
-      </c>
-      <c r="AA32">
-        <v>2.17</v>
-      </c>
-      <c r="AB32">
-        <v>1.63</v>
-      </c>
-      <c r="AC32">
-        <v>3.58</v>
-      </c>
-      <c r="AD32">
-        <v>1.26</v>
-      </c>
-      <c r="AE32">
-        <v>1.03</v>
-      </c>
       <c r="AF32">
+        <v>1.86</v>
+      </c>
+      <c r="AG32">
+        <v>1.82</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
+        <v>1.22</v>
+      </c>
+      <c r="AK32">
         <v>1.83</v>
-      </c>
-      <c r="AG32">
-        <v>1.85</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32">
-        <v>1.29</v>
-      </c>
-      <c r="AK32">
-        <v>1.73</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="O33">
         <v>3.2</v>
       </c>
       <c r="P33">
-        <v>3.86</v>
+        <v>3.7</v>
       </c>
       <c r="Q33">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="R33">
         <v>2.07</v>
       </c>
       <c r="S33">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T33">
-        <v>2.66</v>
+        <v>2.55</v>
       </c>
       <c r="U33">
-        <v>2.79</v>
+        <v>3.2</v>
       </c>
       <c r="V33">
+        <v>1.3</v>
+      </c>
+      <c r="W33">
+        <v>1.05</v>
+      </c>
+      <c r="X33">
+        <v>1.02</v>
+      </c>
+      <c r="Y33">
         <v>1.38</v>
       </c>
-      <c r="W33">
-        <v>1.04</v>
-      </c>
-      <c r="X33">
-        <v>1.04</v>
-      </c>
-      <c r="Y33">
-        <v>1.35</v>
-      </c>
       <c r="Z33">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="AA33">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AB33">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AC33">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AD33">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE33">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF33">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AG33">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK33">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL33">
         <v>0</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -1145,7 +1145,7 @@
         <v>3.34</v>
       </c>
       <c r="U5">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="V5">
         <v>1.73</v>
@@ -1160,7 +1160,7 @@
         <v>1.1</v>
       </c>
       <c r="Z5">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AA5">
         <v>1.39</v>
@@ -1175,7 +1175,7 @@
         <v>1.72</v>
       </c>
       <c r="AE5">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AF5">
         <v>1.74</v>
@@ -1287,34 +1287,34 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="O6">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="P6">
-        <v>5.51</v>
+        <v>4</v>
       </c>
       <c r="Q6">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="R6">
         <v>2.2</v>
       </c>
       <c r="S6">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T6">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="U6">
         <v>2.8</v>
       </c>
       <c r="V6">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
         <v>1.01</v>
@@ -1329,7 +1329,7 @@
         <v>1.93</v>
       </c>
       <c r="AB6">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AC6">
         <v>3.08</v>
@@ -1341,7 +1341,7 @@
         <v>1.07</v>
       </c>
       <c r="AF6">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG6">
         <v>2</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AK6">
         <v>2</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.21</v>
+        <v>1.76</v>
       </c>
       <c r="AK7">
         <v>1.18</v>
@@ -1622,16 +1622,16 @@
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>3.74</v>
+        <v>4.47</v>
       </c>
       <c r="R8">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="S8">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T8">
-        <v>3.05</v>
+        <v>2.82</v>
       </c>
       <c r="U8">
         <v>2.5</v>
@@ -1649,10 +1649,10 @@
         <v>1.25</v>
       </c>
       <c r="Z8">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AA8">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AB8">
         <v>2.05</v>
@@ -1667,7 +1667,7 @@
         <v>1.13</v>
       </c>
       <c r="AF8">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG8">
         <v>2.02</v>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK8">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1785,10 +1785,10 @@
         <v>4.2</v>
       </c>
       <c r="Q9">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="R9">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S9">
         <v>1.3</v>
@@ -1797,10 +1797,10 @@
         <v>3.25</v>
       </c>
       <c r="U9">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="V9">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W9">
         <v>1.07</v>
@@ -1815,7 +1815,7 @@
         <v>3.82</v>
       </c>
       <c r="AA9">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB9">
         <v>2.01</v>
@@ -1827,7 +1827,7 @@
         <v>1.36</v>
       </c>
       <c r="AE9">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF9">
         <v>1.68</v>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK9">
         <v>2.01</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>10.6</v>
+        <v>6.73</v>
       </c>
       <c r="O11">
-        <v>4.75</v>
+        <v>4.35</v>
       </c>
       <c r="P11">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Q11">
         <v>7.5</v>
@@ -2117,7 +2117,7 @@
         <v>2.55</v>
       </c>
       <c r="S11">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T11">
         <v>3.3</v>
@@ -2129,7 +2129,7 @@
         <v>1.5</v>
       </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
         <v>1.01</v>
@@ -2138,28 +2138,28 @@
         <v>1.18</v>
       </c>
       <c r="Z11">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AA11">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB11">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC11">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="AD11">
         <v>1.4</v>
       </c>
       <c r="AE11">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF11">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AG11">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="AK11">
         <v>1.02</v>
@@ -2274,7 +2274,7 @@
         <v>3.3</v>
       </c>
       <c r="Q12">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="R12">
         <v>2.25</v>
@@ -2286,16 +2286,16 @@
         <v>3.08</v>
       </c>
       <c r="U12">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V12">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W12">
         <v>1.12</v>
       </c>
       <c r="X12">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
         <v>1.18</v>
@@ -2307,7 +2307,7 @@
         <v>1.7</v>
       </c>
       <c r="AB12">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="AC12">
         <v>2.88</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AK12">
         <v>1.73</v>
@@ -2440,7 +2440,7 @@
         <v>3.46</v>
       </c>
       <c r="R13">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="S13">
         <v>1.55</v>
@@ -2594,7 +2594,7 @@
         <v>2.7</v>
       </c>
       <c r="O14">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="P14">
         <v>2.47</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="O15">
-        <v>3.3</v>
+        <v>3.21</v>
       </c>
       <c r="P15">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="Q15">
         <v>3.3</v>
@@ -2781,22 +2781,22 @@
         <v>1.46</v>
       </c>
       <c r="W15">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z15">
         <v>4.1</v>
       </c>
       <c r="AA15">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AB15">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AC15">
         <v>2.8</v>
@@ -2920,22 +2920,22 @@
         <v>1.7</v>
       </c>
       <c r="O16">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="P16">
-        <v>4.5</v>
+        <v>4.78</v>
       </c>
       <c r="Q16">
         <v>2.2</v>
       </c>
       <c r="R16">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="S16">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T16">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="U16">
         <v>2.56</v>
@@ -2959,16 +2959,16 @@
         <v>1.73</v>
       </c>
       <c r="AB16">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC16">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AD16">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE16">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF16">
         <v>1.67</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK16">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="O18">
         <v>3.9</v>
@@ -3297,7 +3297,7 @@
         <v>1.25</v>
       </c>
       <c r="AF18">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AG18">
         <v>2.5</v>
@@ -3316,7 +3316,7 @@
         <v>1.2</v>
       </c>
       <c r="AK18">
-        <v>1.74</v>
+        <v>1.97</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,22 +3406,22 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="O19">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P19">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="Q19">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="R19">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="S19">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T19">
         <v>3.22</v>
@@ -3430,40 +3430,40 @@
         <v>2.3</v>
       </c>
       <c r="V19">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W19">
         <v>1.08</v>
       </c>
       <c r="X19">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
         <v>1.15</v>
       </c>
       <c r="Z19">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AA19">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB19">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="AC19">
-        <v>2.7</v>
+        <v>2.51</v>
       </c>
       <c r="AD19">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AE19">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF19">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AG19">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.14</v>
       </c>
       <c r="AK19">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3575,7 +3575,7 @@
         <v>4.65</v>
       </c>
       <c r="P20">
-        <v>5.15</v>
+        <v>6.22</v>
       </c>
       <c r="Q20">
         <v>1.78</v>
@@ -3587,7 +3587,7 @@
         <v>1.16</v>
       </c>
       <c r="T20">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="U20">
         <v>1.93</v>
@@ -3608,10 +3608,10 @@
         <v>6.25</v>
       </c>
       <c r="AA20">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AB20">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AC20">
         <v>1.85</v>
@@ -3623,10 +3623,10 @@
         <v>1.35</v>
       </c>
       <c r="AF20">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AG20">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O21">
-        <v>3.29</v>
+        <v>3.6</v>
       </c>
       <c r="P21">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="Q21">
         <v>3</v>
@@ -3747,19 +3747,19 @@
         <v>2.45</v>
       </c>
       <c r="S21">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T21">
         <v>3.5</v>
       </c>
       <c r="U21">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="V21">
         <v>1.6</v>
       </c>
       <c r="W21">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X21">
         <v>1.01</v>
@@ -3774,13 +3774,13 @@
         <v>1.57</v>
       </c>
       <c r="AB21">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AC21">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AD21">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AE21">
         <v>1.24</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="O23">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P23">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q23">
         <v>2.72</v>
@@ -4094,19 +4094,19 @@
         <v>1.18</v>
       </c>
       <c r="Z23">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="AA23">
         <v>1.71</v>
       </c>
       <c r="AB23">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AC23">
         <v>2.7</v>
       </c>
       <c r="AD23">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE23">
         <v>1.1</v>
@@ -4224,19 +4224,19 @@
         <v>1.66</v>
       </c>
       <c r="O24">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="P24">
         <v>3.85</v>
       </c>
       <c r="Q24">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="R24">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="S24">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T24">
         <v>4.1</v>
@@ -4260,7 +4260,7 @@
         <v>5.9</v>
       </c>
       <c r="AA24">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AB24">
         <v>2.83</v>
@@ -4384,19 +4384,19 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="O25">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="P25">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Q25">
-        <v>1.98</v>
+        <v>2.19</v>
       </c>
       <c r="R25">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S25">
         <v>1.35</v>
@@ -4405,43 +4405,43 @@
         <v>2.9</v>
       </c>
       <c r="U25">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V25">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W25">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X25">
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z25">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA25">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB25">
         <v>2</v>
       </c>
       <c r="AC25">
-        <v>2.88</v>
+        <v>3.13</v>
       </c>
       <c r="AD25">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AE25">
         <v>1.08</v>
       </c>
       <c r="AF25">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG25">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK25">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4553,13 +4553,13 @@
         <v>3.04</v>
       </c>
       <c r="P26">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q26">
         <v>3.5</v>
       </c>
       <c r="R26">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="S26">
         <v>1.4</v>
@@ -4568,7 +4568,7 @@
         <v>2.59</v>
       </c>
       <c r="U26">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="V26">
         <v>1.33</v>
@@ -4577,7 +4577,7 @@
         <v>1.02</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
         <v>1.28</v>
@@ -4586,7 +4586,7 @@
         <v>3</v>
       </c>
       <c r="AA26">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AB26">
         <v>1.73</v>
@@ -4595,10 +4595,10 @@
         <v>3.5</v>
       </c>
       <c r="AD26">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE26">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF26">
         <v>1.77</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.26</v>
+        <v>1.53</v>
       </c>
       <c r="AK26">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4752,7 +4752,7 @@
         <v>1.44</v>
       </c>
       <c r="AB27">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AC27">
         <v>2.17</v>
@@ -5036,19 +5036,19 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="O29">
         <v>3.75</v>
       </c>
       <c r="P29">
-        <v>3.39</v>
+        <v>3.95</v>
       </c>
       <c r="Q29">
         <v>2.15</v>
       </c>
       <c r="R29">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="S29">
         <v>1.17</v>
@@ -5057,43 +5057,43 @@
         <v>4.5</v>
       </c>
       <c r="U29">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V29">
         <v>1.74</v>
       </c>
       <c r="W29">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="Z29">
-        <v>5.85</v>
+        <v>3.9</v>
       </c>
       <c r="AA29">
         <v>1.4</v>
       </c>
       <c r="AB29">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="AC29">
-        <v>1.68</v>
+        <v>2.06</v>
       </c>
       <c r="AD29">
-        <v>1.96</v>
+        <v>1.77</v>
       </c>
       <c r="AE29">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="AF29">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AG29">
-        <v>2.66</v>
+        <v>2.25</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AK29">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="O30">
         <v>3.2</v>
@@ -5208,7 +5208,7 @@
         <v>1.91</v>
       </c>
       <c r="Q30">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="R30">
         <v>2.06</v>
@@ -5235,13 +5235,13 @@
         <v>1.32</v>
       </c>
       <c r="Z30">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AA30">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB30">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC30">
         <v>3.45</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK30">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="O31">
         <v>3</v>
       </c>
       <c r="P31">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q31">
         <v>2.58</v>
@@ -5395,19 +5395,19 @@
         <v>1.1</v>
       </c>
       <c r="Y31">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Z31">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="AA31">
-        <v>2.45</v>
+        <v>2.52</v>
       </c>
       <c r="AB31">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AC31">
-        <v>4.75</v>
+        <v>4.88</v>
       </c>
       <c r="AD31">
         <v>1.13</v>
@@ -5416,10 +5416,10 @@
         <v>1.05</v>
       </c>
       <c r="AF31">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AG31">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK31">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5537,7 +5537,7 @@
         <v>2.5</v>
       </c>
       <c r="R32">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="S32">
         <v>1.37</v>
@@ -5552,7 +5552,7 @@
         <v>1.38</v>
       </c>
       <c r="W32">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X32">
         <v>1.04</v>
@@ -5564,7 +5564,7 @@
         <v>3.14</v>
       </c>
       <c r="AA32">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB32">
         <v>1.7</v>
@@ -5582,7 +5582,7 @@
         <v>1.86</v>
       </c>
       <c r="AG32">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK32">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5697,10 +5697,10 @@
         <v>3.7</v>
       </c>
       <c r="Q33">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="R33">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="S33">
         <v>1.4</v>
@@ -5709,13 +5709,13 @@
         <v>2.55</v>
       </c>
       <c r="U33">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="V33">
         <v>1.3</v>
       </c>
       <c r="W33">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X33">
         <v>1.02</v>
@@ -5724,19 +5724,19 @@
         <v>1.38</v>
       </c>
       <c r="Z33">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="AA33">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="AB33">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="AC33">
         <v>3.58</v>
       </c>
       <c r="AD33">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AE33">
         <v>1.03</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="O34">
         <v>3.4</v>
       </c>
       <c r="P34">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="Q34">
         <v>2.44</v>
@@ -5866,49 +5866,49 @@
         <v>2.2</v>
       </c>
       <c r="S34">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="U34">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V34">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W34">
         <v>1.1</v>
       </c>
       <c r="X34">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y34">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="Z34">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA34">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AB34">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AC34">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD34">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE34">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF34">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AG34">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6014,16 +6014,16 @@
         </is>
       </c>
       <c r="N35">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="O35">
         <v>3</v>
       </c>
       <c r="P35">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q35">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="R35">
         <v>2</v>
@@ -6041,34 +6041,34 @@
         <v>1.31</v>
       </c>
       <c r="W35">
+        <v>1.06</v>
+      </c>
+      <c r="X35">
         <v>1.03</v>
       </c>
-      <c r="X35">
-        <v>1.05</v>
-      </c>
       <c r="Y35">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z35">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="AA35">
         <v>2.12</v>
       </c>
       <c r="AB35">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC35">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AD35">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE35">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF35">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG35">
         <v>1.83</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="O36">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="P36">
-        <v>4.43</v>
+        <v>4.4</v>
       </c>
       <c r="Q36">
         <v>2.2</v>
@@ -6195,7 +6195,7 @@
         <v>1.36</v>
       </c>
       <c r="T36">
-        <v>2.89</v>
+        <v>2.73</v>
       </c>
       <c r="U36">
         <v>2.75</v>
@@ -6213,7 +6213,7 @@
         <v>1.27</v>
       </c>
       <c r="Z36">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AA36">
         <v>1.91</v>
@@ -6234,7 +6234,7 @@
         <v>1.84</v>
       </c>
       <c r="AG36">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK36">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6343,16 +6343,16 @@
         <v>2.3</v>
       </c>
       <c r="O37">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="P37">
-        <v>2.85</v>
+        <v>2.68</v>
       </c>
       <c r="Q37">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R37">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="S37">
         <v>1.42</v>
@@ -6367,37 +6367,37 @@
         <v>1.33</v>
       </c>
       <c r="W37">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X37">
         <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z37">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="AA37">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AB37">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AC37">
-        <v>3.86</v>
+        <v>3.67</v>
       </c>
       <c r="AD37">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE37">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF37">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG37">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.36</v>
       </c>
       <c r="AK37">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6512,10 +6512,10 @@
         <v>5.25</v>
       </c>
       <c r="Q38">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="R38">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="S38">
         <v>1.54</v>
@@ -6527,7 +6527,7 @@
         <v>3.5</v>
       </c>
       <c r="V38">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W38">
         <v>1</v>
@@ -6545,19 +6545,19 @@
         <v>2.6</v>
       </c>
       <c r="AB38">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AC38">
-        <v>5</v>
+        <v>5.06</v>
       </c>
       <c r="AD38">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AE38">
         <v>1.01</v>
       </c>
       <c r="AF38">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="AG38">
         <v>1.47</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="AK38">
         <v>2.12</v>
@@ -6675,19 +6675,19 @@
         <v>3.45</v>
       </c>
       <c r="Q39">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R39">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S39">
         <v>1.48</v>
       </c>
       <c r="T39">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="U39">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="V39">
         <v>1.25</v>
@@ -6699,31 +6699,31 @@
         <v>1.05</v>
       </c>
       <c r="Y39">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="Z39">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="AA39">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="AB39">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AC39">
-        <v>4.75</v>
+        <v>4.83</v>
       </c>
       <c r="AD39">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AE39">
         <v>1.05</v>
       </c>
       <c r="AF39">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AG39">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK39">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AL39">
         <v>0</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="O6">
         <v>3.4</v>
@@ -1305,7 +1305,7 @@
         <v>1.37</v>
       </c>
       <c r="T6">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="U6">
         <v>2.8</v>
@@ -1326,16 +1326,16 @@
         <v>3.2</v>
       </c>
       <c r="AA6">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AB6">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC6">
         <v>3.08</v>
       </c>
       <c r="AD6">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE6">
         <v>1.07</v>
@@ -1655,7 +1655,7 @@
         <v>1.77</v>
       </c>
       <c r="AB8">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC8">
         <v>2.9</v>
@@ -1664,7 +1664,7 @@
         <v>1.36</v>
       </c>
       <c r="AE8">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF8">
         <v>1.65</v>
@@ -2120,7 +2120,7 @@
         <v>1.3</v>
       </c>
       <c r="T11">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U11">
         <v>2.3</v>
@@ -2153,10 +2153,10 @@
         <v>1.4</v>
       </c>
       <c r="AE11">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF11">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG11">
         <v>1.76</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>3.05</v>
+        <v>1.16</v>
       </c>
       <c r="AK11">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,16 +2265,16 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="O12">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P12">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="Q12">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="R12">
         <v>2.25</v>
@@ -2286,7 +2286,7 @@
         <v>3.08</v>
       </c>
       <c r="U12">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="V12">
         <v>1.47</v>
@@ -2307,7 +2307,7 @@
         <v>1.7</v>
       </c>
       <c r="AB12">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AC12">
         <v>2.88</v>
@@ -2322,7 +2322,7 @@
         <v>1.57</v>
       </c>
       <c r="AG12">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK12">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="O14">
         <v>3.1</v>
@@ -2609,7 +2609,7 @@
         <v>1.4</v>
       </c>
       <c r="T14">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="U14">
         <v>3.16</v>
@@ -2639,16 +2639,16 @@
         <v>4.2</v>
       </c>
       <c r="AD14">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE14">
         <v>1.06</v>
       </c>
       <c r="AF14">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AG14">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>1.46</v>
       </c>
       <c r="AK14">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="O20">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="P20">
-        <v>6.22</v>
+        <v>5.15</v>
       </c>
       <c r="Q20">
         <v>1.78</v>
@@ -3593,7 +3593,7 @@
         <v>1.93</v>
       </c>
       <c r="V20">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W20">
         <v>1.21</v>
@@ -3611,7 +3611,7 @@
         <v>1.36</v>
       </c>
       <c r="AB20">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AC20">
         <v>1.85</v>
@@ -3623,10 +3623,10 @@
         <v>1.35</v>
       </c>
       <c r="AF20">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG20">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -4061,10 +4061,10 @@
         <v>2.1</v>
       </c>
       <c r="O23">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P23">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="Q23">
         <v>2.72</v>
@@ -4088,19 +4088,19 @@
         <v>1.12</v>
       </c>
       <c r="X23">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z23">
-        <v>3.82</v>
+        <v>4.33</v>
       </c>
       <c r="AA23">
         <v>1.71</v>
       </c>
       <c r="AB23">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC23">
         <v>2.7</v>
@@ -4387,22 +4387,22 @@
         <v>1.71</v>
       </c>
       <c r="O25">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="P25">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="Q25">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="R25">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="S25">
         <v>1.35</v>
       </c>
       <c r="T25">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="U25">
         <v>2.6</v>
@@ -4414,13 +4414,13 @@
         <v>1.1</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z25">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="AA25">
         <v>1.8</v>
@@ -4429,19 +4429,19 @@
         <v>2</v>
       </c>
       <c r="AC25">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="AD25">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE25">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF25">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG25">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK25">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4550,7 +4550,7 @@
         <v>2.95</v>
       </c>
       <c r="O26">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="P26">
         <v>2.2</v>
@@ -6506,16 +6506,16 @@
         <v>1.56</v>
       </c>
       <c r="O38">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P38">
         <v>5.25</v>
       </c>
       <c r="Q38">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="R38">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="S38">
         <v>1.54</v>
@@ -6545,10 +6545,10 @@
         <v>2.6</v>
       </c>
       <c r="AB38">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AC38">
-        <v>5.06</v>
+        <v>5.05</v>
       </c>
       <c r="AD38">
         <v>1.15</v>
@@ -6560,7 +6560,7 @@
         <v>2.38</v>
       </c>
       <c r="AG38">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.07</v>
+        <v>1.23</v>
       </c>
       <c r="AK38">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AL38">
         <v>0</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -1133,19 +1133,19 @@
         <v>1.14</v>
       </c>
       <c r="Q5">
-        <v>8.1</v>
+        <v>7</v>
       </c>
       <c r="R5">
-        <v>3</v>
+        <v>2.49</v>
       </c>
       <c r="S5">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="T5">
         <v>3.34</v>
       </c>
       <c r="U5">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="V5">
         <v>1.73</v>
@@ -1175,7 +1175,7 @@
         <v>1.72</v>
       </c>
       <c r="AE5">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AF5">
         <v>1.74</v>
@@ -1782,13 +1782,13 @@
         <v>3.75</v>
       </c>
       <c r="P9">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="Q9">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="R9">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S9">
         <v>1.3</v>
@@ -1827,7 +1827,7 @@
         <v>1.36</v>
       </c>
       <c r="AE9">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF9">
         <v>1.68</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK9">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -4224,7 +4224,7 @@
         <v>1.66</v>
       </c>
       <c r="O24">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="P24">
         <v>3.85</v>
@@ -4236,10 +4236,10 @@
         <v>2.63</v>
       </c>
       <c r="S24">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T24">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="U24">
         <v>1.95</v>
@@ -4275,7 +4275,7 @@
         <v>1.25</v>
       </c>
       <c r="AF24">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AG24">
         <v>2.77</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AK24">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -5042,19 +5042,19 @@
         <v>3.75</v>
       </c>
       <c r="P29">
-        <v>3.95</v>
+        <v>3.39</v>
       </c>
       <c r="Q29">
         <v>2.15</v>
       </c>
       <c r="R29">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="S29">
         <v>1.17</v>
       </c>
       <c r="T29">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="U29">
         <v>2.06</v>
@@ -5081,7 +5081,7 @@
         <v>2.81</v>
       </c>
       <c r="AC29">
-        <v>2.06</v>
+        <v>1.68</v>
       </c>
       <c r="AD29">
         <v>1.77</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="O34">
         <v>3.4</v>
       </c>
       <c r="P34">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="Q34">
         <v>2.44</v>
@@ -5872,7 +5872,7 @@
         <v>3</v>
       </c>
       <c r="U34">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V34">
         <v>1.4</v>
@@ -5884,10 +5884,10 @@
         <v>1</v>
       </c>
       <c r="Y34">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z34">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="AA34">
         <v>1.79</v>
@@ -5896,7 +5896,7 @@
         <v>1.92</v>
       </c>
       <c r="AC34">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AD34">
         <v>1.31</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AK34">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6023,43 +6023,43 @@
         <v>2.3</v>
       </c>
       <c r="Q35">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="R35">
         <v>2</v>
       </c>
       <c r="S35">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="T35">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="U35">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="V35">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W35">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X35">
         <v>1.03</v>
       </c>
       <c r="Y35">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z35">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AA35">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AB35">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AC35">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="AD35">
         <v>1.19</v>
@@ -6068,10 +6068,10 @@
         <v>1.03</v>
       </c>
       <c r="AF35">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG35">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>4.4</v>
       </c>
       <c r="Q36">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R36">
         <v>2.12</v>
@@ -6195,7 +6195,7 @@
         <v>1.36</v>
       </c>
       <c r="T36">
-        <v>2.73</v>
+        <v>2.89</v>
       </c>
       <c r="U36">
         <v>2.75</v>
@@ -6210,7 +6210,7 @@
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z36">
         <v>3.25</v>
@@ -6234,7 +6234,7 @@
         <v>1.84</v>
       </c>
       <c r="AG36">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6343,13 +6343,13 @@
         <v>2.3</v>
       </c>
       <c r="O37">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="P37">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="Q37">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="R37">
         <v>2.16</v>
@@ -6364,7 +6364,7 @@
         <v>2.99</v>
       </c>
       <c r="V37">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W37">
         <v>1.05</v>
@@ -6373,16 +6373,16 @@
         <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z37">
         <v>2.88</v>
       </c>
       <c r="AA37">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AB37">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AC37">
         <v>3.67</v>
@@ -6391,10 +6391,10 @@
         <v>1.22</v>
       </c>
       <c r="AE37">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF37">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG37">
         <v>1.91</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -1287,25 +1287,25 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="O6">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P6">
         <v>4</v>
       </c>
       <c r="Q6">
-        <v>2.21</v>
+        <v>2.33</v>
       </c>
       <c r="R6">
         <v>2.2</v>
       </c>
       <c r="S6">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T6">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="U6">
         <v>2.8</v>
@@ -1314,7 +1314,7 @@
         <v>1.39</v>
       </c>
       <c r="W6">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
         <v>1.01</v>
@@ -1323,16 +1323,16 @@
         <v>1.28</v>
       </c>
       <c r="Z6">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA6">
         <v>1.94</v>
       </c>
       <c r="AB6">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AC6">
-        <v>3.08</v>
+        <v>3.35</v>
       </c>
       <c r="AD6">
         <v>1.3</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK6">
         <v>2</v>
@@ -1939,34 +1939,34 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q10">
         <v>2.8</v>
       </c>
       <c r="R10">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="S10">
         <v>1.33</v>
       </c>
       <c r="T10">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U10">
         <v>2.6</v>
       </c>
       <c r="V10">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W10">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
         <v>1.01</v>
@@ -1981,7 +1981,7 @@
         <v>1.85</v>
       </c>
       <c r="AB10">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AC10">
         <v>2.92</v>
@@ -2606,7 +2606,7 @@
         <v>2.05</v>
       </c>
       <c r="S14">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T14">
         <v>2.53</v>
@@ -2618,10 +2618,10 @@
         <v>1.3</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X14">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
         <v>1.38</v>
@@ -2639,10 +2639,10 @@
         <v>4.2</v>
       </c>
       <c r="AD14">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE14">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF14">
         <v>1.87</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="AK14">
         <v>1.39</v>
@@ -4553,16 +4553,16 @@
         <v>3.2</v>
       </c>
       <c r="P26">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q26">
         <v>3.5</v>
       </c>
       <c r="R26">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S26">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T26">
         <v>2.59</v>
@@ -4577,7 +4577,7 @@
         <v>1.02</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y26">
         <v>1.28</v>
@@ -4595,7 +4595,7 @@
         <v>3.5</v>
       </c>
       <c r="AD26">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE26">
         <v>1.04</v>
@@ -4719,10 +4719,10 @@
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="R27">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="S27">
         <v>1.22</v>
@@ -4731,7 +4731,7 @@
         <v>3.8</v>
       </c>
       <c r="U27">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="V27">
         <v>1.62</v>
@@ -4740,16 +4740,16 @@
         <v>1.16</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z27">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AA27">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AB27">
         <v>2.4</v>
@@ -4764,7 +4764,7 @@
         <v>1.22</v>
       </c>
       <c r="AF27">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AG27">
         <v>2.45</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK27">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="O28">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P28">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5202,10 +5202,10 @@
         <v>3.4</v>
       </c>
       <c r="O30">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P30">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="Q30">
         <v>4.35</v>
@@ -5217,16 +5217,16 @@
         <v>1.36</v>
       </c>
       <c r="T30">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="U30">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V30">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W30">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X30">
         <v>1.02</v>
@@ -5247,10 +5247,10 @@
         <v>3.45</v>
       </c>
       <c r="AD30">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE30">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF30">
         <v>1.75</v>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="O38">
         <v>3.3</v>
@@ -6524,13 +6524,13 @@
         <v>2.39</v>
       </c>
       <c r="U38">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="V38">
         <v>1.21</v>
       </c>
       <c r="W38">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X38">
         <v>1.1</v>
@@ -6542,13 +6542,13 @@
         <v>2.39</v>
       </c>
       <c r="AA38">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="AB38">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AC38">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="AD38">
         <v>1.15</v>
@@ -6675,16 +6675,16 @@
         <v>3.45</v>
       </c>
       <c r="Q39">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R39">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="S39">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="T39">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="U39">
         <v>3.2</v>
@@ -6708,22 +6708,22 @@
         <v>2.41</v>
       </c>
       <c r="AB39">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AC39">
-        <v>4.83</v>
+        <v>4.5</v>
       </c>
       <c r="AD39">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AE39">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF39">
         <v>2.03</v>
       </c>
       <c r="AG39">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK39">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AL39">
         <v>0</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -1133,22 +1133,22 @@
         <v>1.14</v>
       </c>
       <c r="Q5">
-        <v>7</v>
+        <v>8.1</v>
       </c>
       <c r="R5">
         <v>2.49</v>
       </c>
       <c r="S5">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="T5">
-        <v>3.34</v>
+        <v>4</v>
       </c>
       <c r="U5">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="V5">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="W5">
         <v>1.15</v>
@@ -1181,7 +1181,7 @@
         <v>1.74</v>
       </c>
       <c r="AG5">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.76</v>
+        <v>1.21</v>
       </c>
       <c r="AK7">
         <v>1.18</v>
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>4.47</v>
+        <v>4.2</v>
       </c>
       <c r="R8">
         <v>2.21</v>
@@ -1631,16 +1631,16 @@
         <v>1.36</v>
       </c>
       <c r="T8">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="U8">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V8">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W8">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X8">
         <v>1.02</v>
@@ -1664,13 +1664,13 @@
         <v>1.36</v>
       </c>
       <c r="AE8">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF8">
         <v>1.65</v>
       </c>
       <c r="AG8">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1782,13 +1782,13 @@
         <v>3.75</v>
       </c>
       <c r="P9">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="Q9">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="R9">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S9">
         <v>1.3</v>
@@ -1797,22 +1797,22 @@
         <v>3.25</v>
       </c>
       <c r="U9">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V9">
         <v>1.44</v>
       </c>
       <c r="W9">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z9">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="AA9">
         <v>1.7</v>
@@ -1821,7 +1821,7 @@
         <v>2.01</v>
       </c>
       <c r="AC9">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD9">
         <v>1.36</v>
@@ -1833,7 +1833,7 @@
         <v>1.68</v>
       </c>
       <c r="AG9">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK9">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2102,31 +2102,31 @@
         </is>
       </c>
       <c r="N11">
-        <v>6.73</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="P11">
         <v>1.25</v>
       </c>
       <c r="Q11">
-        <v>7.5</v>
+        <v>6.87</v>
       </c>
       <c r="R11">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="S11">
         <v>1.3</v>
       </c>
       <c r="T11">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="U11">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V11">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W11">
         <v>1.07</v>
@@ -2135,31 +2135,31 @@
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z11">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AA11">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB11">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC11">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AD11">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE11">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF11">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AG11">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.16</v>
+        <v>2.83</v>
       </c>
       <c r="AK11">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,40 +2265,40 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="O12">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P12">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q12">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="R12">
         <v>2.25</v>
       </c>
       <c r="S12">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T12">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="U12">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="V12">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W12">
         <v>1.12</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z12">
         <v>3.84</v>
@@ -2307,13 +2307,13 @@
         <v>1.7</v>
       </c>
       <c r="AB12">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC12">
         <v>2.88</v>
       </c>
       <c r="AD12">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE12">
         <v>1.16</v>
@@ -2322,7 +2322,7 @@
         <v>1.57</v>
       </c>
       <c r="AG12">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>1.24</v>
       </c>
       <c r="W13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X13">
         <v>1.05</v>
@@ -2470,10 +2470,10 @@
         <v>2.48</v>
       </c>
       <c r="AB13">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AC13">
-        <v>4.6</v>
+        <v>4.67</v>
       </c>
       <c r="AD13">
         <v>1.13</v>
@@ -2485,7 +2485,7 @@
         <v>2.01</v>
       </c>
       <c r="AG13">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="AK13">
         <v>1.3</v>
@@ -2594,40 +2594,40 @@
         <v>2.75</v>
       </c>
       <c r="O14">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P14">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="Q14">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R14">
         <v>2.05</v>
       </c>
       <c r="S14">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T14">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="U14">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="V14">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W14">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y14">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z14">
-        <v>2.98</v>
+        <v>2.74</v>
       </c>
       <c r="AA14">
         <v>2.2</v>
@@ -2639,16 +2639,16 @@
         <v>4.2</v>
       </c>
       <c r="AD14">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE14">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF14">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AG14">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2760,16 +2760,16 @@
         <v>3.21</v>
       </c>
       <c r="P15">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="Q15">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R15">
         <v>2.34</v>
       </c>
       <c r="S15">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T15">
         <v>3.05</v>
@@ -2787,10 +2787,10 @@
         <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z15">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA15">
         <v>1.75</v>
@@ -2802,16 +2802,16 @@
         <v>2.8</v>
       </c>
       <c r="AD15">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE15">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF15">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG15">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>1.26</v>
       </c>
       <c r="AK15">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2920,10 +2920,10 @@
         <v>1.7</v>
       </c>
       <c r="O16">
-        <v>3.94</v>
+        <v>3.78</v>
       </c>
       <c r="P16">
-        <v>4.78</v>
+        <v>4.16</v>
       </c>
       <c r="Q16">
         <v>2.2</v>
@@ -2935,7 +2935,7 @@
         <v>1.33</v>
       </c>
       <c r="T16">
-        <v>3.04</v>
+        <v>2.87</v>
       </c>
       <c r="U16">
         <v>2.56</v>
@@ -2962,10 +2962,10 @@
         <v>2.07</v>
       </c>
       <c r="AC16">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AD16">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE16">
         <v>1.1</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q17">
         <v>5.4</v>
@@ -3243,16 +3243,16 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="O18">
         <v>3.9</v>
       </c>
       <c r="P18">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="Q18">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R18">
         <v>2.5</v>
@@ -3264,7 +3264,7 @@
         <v>3.8</v>
       </c>
       <c r="U18">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="V18">
         <v>1.6</v>
@@ -3273,10 +3273,10 @@
         <v>1.17</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z18">
         <v>5.39</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,10 +3406,10 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="O19">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="P19">
         <v>3.73</v>
@@ -3421,7 +3421,7 @@
         <v>2.38</v>
       </c>
       <c r="S19">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T19">
         <v>3.22</v>
@@ -3436,13 +3436,13 @@
         <v>1.08</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
         <v>1.15</v>
       </c>
       <c r="Z19">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AA19">
         <v>1.65</v>
@@ -3451,19 +3451,19 @@
         <v>2.19</v>
       </c>
       <c r="AC19">
-        <v>2.51</v>
+        <v>2.48</v>
       </c>
       <c r="AD19">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE19">
         <v>1.17</v>
       </c>
       <c r="AF19">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AG19">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="O20">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="P20">
         <v>5.15</v>
@@ -3587,7 +3587,7 @@
         <v>1.16</v>
       </c>
       <c r="T20">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="U20">
         <v>1.93</v>
@@ -3605,13 +3605,13 @@
         <v>1.06</v>
       </c>
       <c r="Z20">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="AA20">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB20">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AC20">
         <v>1.85</v>
@@ -3620,13 +3620,13 @@
         <v>1.82</v>
       </c>
       <c r="AE20">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AF20">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AG20">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="O21">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P21">
         <v>2.2</v>
@@ -3744,22 +3744,22 @@
         <v>3</v>
       </c>
       <c r="R21">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S21">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T21">
         <v>3.5</v>
       </c>
       <c r="U21">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="V21">
         <v>1.6</v>
       </c>
       <c r="W21">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
         <v>1.01</v>
@@ -3774,22 +3774,22 @@
         <v>1.57</v>
       </c>
       <c r="AB21">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="AC21">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AD21">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AE21">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AF21">
         <v>1.44</v>
       </c>
       <c r="AG21">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.23</v>
+        <v>1.62</v>
       </c>
       <c r="AK21">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4058,10 +4058,10 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="O23">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P23">
         <v>2.95</v>
@@ -4073,7 +4073,7 @@
         <v>2.18</v>
       </c>
       <c r="S23">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T23">
         <v>3.2</v>
@@ -4091,22 +4091,22 @@
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z23">
-        <v>4.33</v>
+        <v>3.95</v>
       </c>
       <c r="AA23">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AB23">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AC23">
         <v>2.7</v>
       </c>
       <c r="AD23">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE23">
         <v>1.1</v>
@@ -4115,7 +4115,7 @@
         <v>1.57</v>
       </c>
       <c r="AG23">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK23">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,10 +4221,10 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="O24">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="P24">
         <v>3.85</v>
@@ -4233,13 +4233,13 @@
         <v>2.12</v>
       </c>
       <c r="R24">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="S24">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T24">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="U24">
         <v>1.95</v>
@@ -4257,10 +4257,10 @@
         <v>1.07</v>
       </c>
       <c r="Z24">
-        <v>5.9</v>
+        <v>5.85</v>
       </c>
       <c r="AA24">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AB24">
         <v>2.83</v>
@@ -4272,13 +4272,13 @@
         <v>1.63</v>
       </c>
       <c r="AE24">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AF24">
         <v>1.36</v>
       </c>
       <c r="AG24">
-        <v>2.77</v>
+        <v>2.38</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="AK24">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.71</v>
+        <v>1.43</v>
       </c>
       <c r="O25">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="P25">
-        <v>4.25</v>
+        <v>6.65</v>
       </c>
       <c r="Q25">
         <v>2.25</v>
@@ -4399,10 +4399,10 @@
         <v>2.14</v>
       </c>
       <c r="S25">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T25">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="U25">
         <v>2.6</v>
@@ -4411,16 +4411,16 @@
         <v>1.42</v>
       </c>
       <c r="W25">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X25">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z25">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="AA25">
         <v>1.8</v>
@@ -4432,16 +4432,16 @@
         <v>3.25</v>
       </c>
       <c r="AD25">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE25">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF25">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AG25">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4719,10 +4719,10 @@
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R27">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="S27">
         <v>1.22</v>
@@ -4731,28 +4731,28 @@
         <v>3.8</v>
       </c>
       <c r="U27">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="V27">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W27">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z27">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AA27">
         <v>1.49</v>
       </c>
       <c r="AB27">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AC27">
         <v>2.17</v>
@@ -4764,7 +4764,7 @@
         <v>1.22</v>
       </c>
       <c r="AF27">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AG27">
         <v>2.45</v>
@@ -5039,28 +5039,28 @@
         <v>1.63</v>
       </c>
       <c r="O29">
-        <v>3.75</v>
+        <v>4.15</v>
       </c>
       <c r="P29">
-        <v>3.39</v>
+        <v>3.95</v>
       </c>
       <c r="Q29">
         <v>2.15</v>
       </c>
       <c r="R29">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="S29">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T29">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="U29">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="V29">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="W29">
         <v>1.18</v>
@@ -5069,10 +5069,10 @@
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z29">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="AA29">
         <v>1.4</v>
@@ -5081,19 +5081,19 @@
         <v>2.81</v>
       </c>
       <c r="AC29">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AD29">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AE29">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AF29">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AG29">
-        <v>2.25</v>
+        <v>2.61</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AK29">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5208,28 +5208,28 @@
         <v>1.88</v>
       </c>
       <c r="Q30">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="R30">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="S30">
         <v>1.36</v>
       </c>
       <c r="T30">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="U30">
-        <v>2.88</v>
+        <v>3.02</v>
       </c>
       <c r="V30">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W30">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
         <v>1.32</v>
@@ -5247,16 +5247,16 @@
         <v>3.45</v>
       </c>
       <c r="AD30">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AE30">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF30">
         <v>1.75</v>
       </c>
       <c r="AG30">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.24</v>
       </c>
       <c r="AK30">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,31 +5362,31 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="O31">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="P31">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q31">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="R31">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="S31">
         <v>1.54</v>
       </c>
       <c r="T31">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="U31">
         <v>3.42</v>
       </c>
       <c r="V31">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W31">
         <v>1</v>
@@ -5395,25 +5395,25 @@
         <v>1.1</v>
       </c>
       <c r="Y31">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="Z31">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AA31">
         <v>2.52</v>
       </c>
       <c r="AB31">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AC31">
-        <v>4.88</v>
+        <v>4.6</v>
       </c>
       <c r="AD31">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE31">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AF31">
         <v>2.15</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK31">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5537,52 +5537,52 @@
         <v>2.5</v>
       </c>
       <c r="R32">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="S32">
         <v>1.37</v>
       </c>
       <c r="T32">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="U32">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="V32">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="W32">
         <v>1.05</v>
       </c>
       <c r="X32">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z32">
-        <v>3.14</v>
+        <v>2.97</v>
       </c>
       <c r="AA32">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AB32">
         <v>1.7</v>
       </c>
       <c r="AC32">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AD32">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE32">
         <v>1.05</v>
       </c>
       <c r="AF32">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG32">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5694,7 +5694,7 @@
         <v>3.2</v>
       </c>
       <c r="P33">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="Q33">
         <v>2.62</v>
@@ -5703,19 +5703,19 @@
         <v>2.05</v>
       </c>
       <c r="S33">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T33">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="U33">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="V33">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W33">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X33">
         <v>1.02</v>
@@ -5724,10 +5724,10 @@
         <v>1.38</v>
       </c>
       <c r="Z33">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="AA33">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="AB33">
         <v>1.69</v>
@@ -5736,17 +5736,17 @@
         <v>3.58</v>
       </c>
       <c r="AD33">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE33">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF33">
+        <v>1.9</v>
+      </c>
+      <c r="AG33">
         <v>1.83</v>
       </c>
-      <c r="AG33">
-        <v>1.85</v>
-      </c>
       <c r="AH33" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AK33">
         <v>1.73</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="O34">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P34">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="Q34">
         <v>2.44</v>
@@ -5866,10 +5866,10 @@
         <v>2.2</v>
       </c>
       <c r="S34">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T34">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="U34">
         <v>2.62</v>
@@ -5881,19 +5881,19 @@
         <v>1.1</v>
       </c>
       <c r="X34">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z34">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AA34">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AB34">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AC34">
         <v>2.92</v>
@@ -5902,13 +5902,13 @@
         <v>1.31</v>
       </c>
       <c r="AE34">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF34">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG34">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK34">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6023,22 +6023,22 @@
         <v>2.3</v>
       </c>
       <c r="Q35">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="R35">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S35">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T35">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U35">
-        <v>3.04</v>
+        <v>2.82</v>
       </c>
       <c r="V35">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W35">
         <v>1.03</v>
@@ -6047,32 +6047,32 @@
         <v>1.03</v>
       </c>
       <c r="Y35">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z35">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="AA35">
         <v>2.05</v>
       </c>
       <c r="AB35">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AC35">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="AD35">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AE35">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF35">
+        <v>1.7</v>
+      </c>
+      <c r="AG35">
         <v>1.83</v>
       </c>
-      <c r="AG35">
-        <v>1.84</v>
-      </c>
       <c r="AH35" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="AK35">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="O36">
         <v>3.4</v>
@@ -6186,16 +6186,16 @@
         <v>4.4</v>
       </c>
       <c r="Q36">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="R36">
         <v>2.12</v>
       </c>
       <c r="S36">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T36">
-        <v>2.89</v>
+        <v>2.73</v>
       </c>
       <c r="U36">
         <v>2.75</v>
@@ -6204,16 +6204,16 @@
         <v>1.36</v>
       </c>
       <c r="W36">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X36">
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z36">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="AA36">
         <v>1.91</v>
@@ -6234,7 +6234,7 @@
         <v>1.84</v>
       </c>
       <c r="AG36">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6346,13 +6346,13 @@
         <v>3</v>
       </c>
       <c r="P37">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="Q37">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="R37">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="S37">
         <v>1.42</v>
@@ -6370,13 +6370,13 @@
         <v>1.05</v>
       </c>
       <c r="X37">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y37">
         <v>1.32</v>
       </c>
       <c r="Z37">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AA37">
         <v>2.08</v>
@@ -6385,19 +6385,19 @@
         <v>1.71</v>
       </c>
       <c r="AC37">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="AD37">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE37">
         <v>1.05</v>
       </c>
       <c r="AF37">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG37">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6503,19 +6503,19 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="O38">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P38">
-        <v>5.25</v>
+        <v>6.15</v>
       </c>
       <c r="Q38">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="R38">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="S38">
         <v>1.54</v>
@@ -6530,10 +6530,10 @@
         <v>1.21</v>
       </c>
       <c r="W38">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X38">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y38">
         <v>1.51</v>
@@ -6542,13 +6542,13 @@
         <v>2.39</v>
       </c>
       <c r="AA38">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="AB38">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AC38">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="AD38">
         <v>1.15</v>
@@ -6557,7 +6557,7 @@
         <v>1.01</v>
       </c>
       <c r="AF38">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AG38">
         <v>1.48</v>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="AK38">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6675,16 +6675,16 @@
         <v>3.45</v>
       </c>
       <c r="Q39">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="R39">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="S39">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="T39">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="U39">
         <v>3.2</v>
@@ -6693,37 +6693,37 @@
         <v>1.25</v>
       </c>
       <c r="W39">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X39">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Y39">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="Z39">
-        <v>2.43</v>
+        <v>2.85</v>
       </c>
       <c r="AA39">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AB39">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AC39">
-        <v>4.5</v>
+        <v>4.83</v>
       </c>
       <c r="AD39">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AE39">
         <v>1.01</v>
       </c>
       <c r="AF39">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AG39">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK39">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AL39">
         <v>0</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="O13">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="P13">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="Q13">
         <v>3.46</v>
       </c>
       <c r="R13">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="S13">
         <v>1.55</v>
@@ -2455,7 +2455,7 @@
         <v>1.24</v>
       </c>
       <c r="W13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X13">
         <v>1.05</v>
@@ -2467,13 +2467,13 @@
         <v>2.49</v>
       </c>
       <c r="AA13">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="AB13">
         <v>1.52</v>
       </c>
       <c r="AC13">
-        <v>4.67</v>
+        <v>4.73</v>
       </c>
       <c r="AD13">
         <v>1.13</v>
@@ -6524,10 +6524,10 @@
         <v>2.39</v>
       </c>
       <c r="U38">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="V38">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="W38">
         <v>1.05</v>
@@ -6545,7 +6545,7 @@
         <v>2.6</v>
       </c>
       <c r="AB38">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AC38">
         <v>5.05</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -1969,7 +1969,7 @@
         <v>1.05</v>
       </c>
       <c r="X10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
         <v>1.22</v>
@@ -1987,7 +1987,7 @@
         <v>2.92</v>
       </c>
       <c r="AD10">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE10">
         <v>1.08</v>
@@ -2464,7 +2464,7 @@
         <v>1.42</v>
       </c>
       <c r="Z13">
-        <v>2.49</v>
+        <v>2.66</v>
       </c>
       <c r="AA13">
         <v>2.49</v>
@@ -2476,7 +2476,7 @@
         <v>4.73</v>
       </c>
       <c r="AD13">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE13">
         <v>1.01</v>
@@ -2633,7 +2633,7 @@
         <v>2.2</v>
       </c>
       <c r="AB14">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC14">
         <v>4.2</v>
@@ -2754,7 +2754,7 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="O15">
         <v>3.21</v>
@@ -2781,13 +2781,13 @@
         <v>1.46</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
         <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z15">
         <v>4.33</v>
@@ -2802,10 +2802,10 @@
         <v>2.8</v>
       </c>
       <c r="AD15">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AE15">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF15">
         <v>1.56</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AK15">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>3</v>
       </c>
       <c r="R21">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S21">
         <v>1.24</v>
@@ -3786,10 +3786,10 @@
         <v>1.18</v>
       </c>
       <c r="AF21">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG21">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
         <v>1.4</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>7.05</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1290,7 +1290,7 @@
         <v>1.75</v>
       </c>
       <c r="O6">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P6">
         <v>4</v>
@@ -1305,37 +1305,37 @@
         <v>1.4</v>
       </c>
       <c r="T6">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="U6">
         <v>2.8</v>
       </c>
       <c r="V6">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z6">
         <v>3.5</v>
       </c>
       <c r="AA6">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB6">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC6">
         <v>3.35</v>
       </c>
       <c r="AD6">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE6">
         <v>1.07</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK6">
         <v>2</v>
@@ -1622,16 +1622,16 @@
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="R8">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S8">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T8">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="U8">
         <v>2.6</v>
@@ -1649,7 +1649,7 @@
         <v>1.25</v>
       </c>
       <c r="Z8">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AA8">
         <v>1.77</v>
@@ -1658,10 +1658,10 @@
         <v>2</v>
       </c>
       <c r="AC8">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AD8">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE8">
         <v>1.11</v>
@@ -1670,7 +1670,7 @@
         <v>1.65</v>
       </c>
       <c r="AG8">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1.22</v>
       </c>
       <c r="AK8">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1942,13 +1942,13 @@
         <v>2.25</v>
       </c>
       <c r="O10">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
         <v>2.7</v>
       </c>
       <c r="Q10">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R10">
         <v>2.11</v>
@@ -1957,22 +1957,22 @@
         <v>1.33</v>
       </c>
       <c r="T10">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U10">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="V10">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W10">
         <v>1.05</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y10">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z10">
         <v>3.5</v>
@@ -1981,10 +1981,10 @@
         <v>1.85</v>
       </c>
       <c r="AB10">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AC10">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AD10">
         <v>1.33</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AK10">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2105,13 +2105,13 @@
         <v>7</v>
       </c>
       <c r="O11">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="P11">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Q11">
-        <v>6.87</v>
+        <v>7.43</v>
       </c>
       <c r="R11">
         <v>2.45</v>
@@ -2120,7 +2120,7 @@
         <v>1.3</v>
       </c>
       <c r="T11">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="U11">
         <v>2.38</v>
@@ -2135,10 +2135,10 @@
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z11">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="AA11">
         <v>1.67</v>
@@ -2147,7 +2147,7 @@
         <v>2.15</v>
       </c>
       <c r="AC11">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="AD11">
         <v>1.42</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="AK11">
         <v>1.02</v>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="O12">
         <v>3.5</v>
@@ -2274,10 +2274,10 @@
         <v>3.1</v>
       </c>
       <c r="Q12">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="R12">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S12">
         <v>1.29</v>
@@ -2295,19 +2295,19 @@
         <v>1.12</v>
       </c>
       <c r="X12">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
         <v>1.2</v>
       </c>
       <c r="Z12">
-        <v>3.84</v>
+        <v>4.33</v>
       </c>
       <c r="AA12">
         <v>1.7</v>
       </c>
       <c r="AB12">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC12">
         <v>2.88</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK12">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AK13">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2594,10 +2594,10 @@
         <v>2.75</v>
       </c>
       <c r="O14">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="P14">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q14">
         <v>3.4</v>
@@ -2645,10 +2645,10 @@
         <v>1.02</v>
       </c>
       <c r="AF14">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AG14">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>1.06</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
         <v>1.2</v>
@@ -2796,13 +2796,13 @@
         <v>1.75</v>
       </c>
       <c r="AB15">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AC15">
         <v>2.8</v>
       </c>
       <c r="AD15">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE15">
         <v>1.17</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK15">
         <v>1.4</v>
@@ -2923,19 +2923,19 @@
         <v>3.78</v>
       </c>
       <c r="P16">
-        <v>4.16</v>
+        <v>4.2</v>
       </c>
       <c r="Q16">
         <v>2.2</v>
       </c>
       <c r="R16">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="S16">
         <v>1.33</v>
       </c>
       <c r="T16">
-        <v>2.87</v>
+        <v>3.04</v>
       </c>
       <c r="U16">
         <v>2.56</v>
@@ -2947,7 +2947,7 @@
         <v>1.11</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
         <v>1.19</v>
@@ -2965,7 +2965,7 @@
         <v>2.95</v>
       </c>
       <c r="AD16">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE16">
         <v>1.1</v>
@@ -3089,28 +3089,28 @@
         <v>1.47</v>
       </c>
       <c r="Q17">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="R17">
         <v>2.43</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U17">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="V17">
         <v>1.48</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
         <v>1.18</v>
@@ -3122,19 +3122,19 @@
         <v>1.61</v>
       </c>
       <c r="AB17">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="AC17">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AD17">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE17">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF17">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG17">
         <v>1.89</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AK17">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="O18">
         <v>3.9</v>
@@ -3264,7 +3264,7 @@
         <v>3.8</v>
       </c>
       <c r="U18">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="V18">
         <v>1.6</v>
@@ -3279,25 +3279,25 @@
         <v>1.14</v>
       </c>
       <c r="Z18">
-        <v>5.39</v>
+        <v>5.46</v>
       </c>
       <c r="AA18">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AB18">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="AC18">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD18">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE18">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF18">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AG18">
         <v>2.5</v>
@@ -3406,16 +3406,16 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="O19">
-        <v>3.73</v>
+        <v>3.78</v>
       </c>
       <c r="P19">
         <v>3.73</v>
       </c>
       <c r="Q19">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R19">
         <v>2.38</v>
@@ -3439,10 +3439,10 @@
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z19">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AA19">
         <v>1.65</v>
@@ -3463,7 +3463,7 @@
         <v>1.54</v>
       </c>
       <c r="AG19">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>4.65</v>
       </c>
       <c r="P20">
-        <v>5.15</v>
+        <v>6.2</v>
       </c>
       <c r="Q20">
         <v>1.78</v>
@@ -3587,13 +3587,13 @@
         <v>1.16</v>
       </c>
       <c r="T20">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="U20">
         <v>1.93</v>
       </c>
       <c r="V20">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W20">
         <v>1.21</v>
@@ -3605,13 +3605,13 @@
         <v>1.06</v>
       </c>
       <c r="Z20">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="AA20">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AB20">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AC20">
         <v>1.85</v>
@@ -3620,7 +3620,7 @@
         <v>1.82</v>
       </c>
       <c r="AE20">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AF20">
         <v>1.5</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK20">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O21">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="P21">
         <v>2.2</v>
@@ -3744,7 +3744,7 @@
         <v>3</v>
       </c>
       <c r="R21">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S21">
         <v>1.24</v>
@@ -3774,7 +3774,7 @@
         <v>1.57</v>
       </c>
       <c r="AB21">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="AC21">
         <v>2.38</v>
@@ -3805,7 +3805,7 @@
         <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4061,10 +4061,10 @@
         <v>2.09</v>
       </c>
       <c r="O23">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P23">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="Q23">
         <v>2.72</v>
@@ -4091,10 +4091,10 @@
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z23">
-        <v>3.95</v>
+        <v>4.02</v>
       </c>
       <c r="AA23">
         <v>1.73</v>
@@ -4106,16 +4106,16 @@
         <v>2.7</v>
       </c>
       <c r="AD23">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AE23">
         <v>1.1</v>
       </c>
       <c r="AF23">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AG23">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4384,22 +4384,22 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="O25">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="P25">
-        <v>6.65</v>
+        <v>4.3</v>
       </c>
       <c r="Q25">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="R25">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="S25">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T25">
         <v>3.2</v>
@@ -4411,37 +4411,37 @@
         <v>1.42</v>
       </c>
       <c r="W25">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
         <v>1.25</v>
       </c>
       <c r="Z25">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA25">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB25">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC25">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD25">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE25">
         <v>1.08</v>
       </c>
       <c r="AF25">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG25">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK25">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4556,10 +4556,10 @@
         <v>2.25</v>
       </c>
       <c r="Q26">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R26">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S26">
         <v>1.43</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="O31">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P31">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q31">
         <v>2.55</v>
@@ -5386,7 +5386,7 @@
         <v>3.42</v>
       </c>
       <c r="V31">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="W31">
         <v>1</v>
@@ -5395,19 +5395,19 @@
         <v>1.1</v>
       </c>
       <c r="Y31">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="Z31">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AA31">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="AB31">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AC31">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AD31">
         <v>1.17</v>
@@ -5416,10 +5416,10 @@
         <v>1</v>
       </c>
       <c r="AF31">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AG31">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5534,22 +5534,22 @@
         <v>3.86</v>
       </c>
       <c r="Q32">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="R32">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S32">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="T32">
         <v>2.8</v>
       </c>
       <c r="U32">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="V32">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W32">
         <v>1.05</v>
@@ -5570,13 +5570,13 @@
         <v>1.7</v>
       </c>
       <c r="AC32">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="AD32">
         <v>1.23</v>
       </c>
       <c r="AE32">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF32">
         <v>1.85</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK32">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,25 +5688,25 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="O33">
         <v>3.2</v>
       </c>
       <c r="P33">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="Q33">
         <v>2.62</v>
       </c>
       <c r="R33">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S33">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T33">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="U33">
         <v>3.2</v>
@@ -5718,19 +5718,19 @@
         <v>1.05</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y33">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="Z33">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="AA33">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AB33">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AC33">
         <v>3.58</v>
@@ -5742,7 +5742,7 @@
         <v>1.07</v>
       </c>
       <c r="AF33">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG33">
         <v>1.83</v>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AK33">
         <v>1.73</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G2">
@@ -635,80 +635,80 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.36</v>
+        <v>2.11</v>
       </c>
       <c r="O2">
-        <v>4.25</v>
+        <v>3.35</v>
       </c>
       <c r="P2">
-        <v>7.05</v>
+        <v>3.37</v>
       </c>
       <c r="Q2">
-        <v>1.85</v>
+        <v>2.55</v>
       </c>
       <c r="R2">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="S2">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="T2">
-        <v>2.92</v>
+        <v>2.39</v>
       </c>
       <c r="U2">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="V2">
-        <v>1.49</v>
+        <v>1.27</v>
       </c>
       <c r="W2">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X2">
+        <v>1.04</v>
+      </c>
+      <c r="Y2">
+        <v>1.4</v>
+      </c>
+      <c r="Z2">
+        <v>2.88</v>
+      </c>
+      <c r="AA2">
+        <v>2.21</v>
+      </c>
+      <c r="AB2">
+        <v>1.57</v>
+      </c>
+      <c r="AC2">
+        <v>4.86</v>
+      </c>
+      <c r="AD2">
+        <v>1.18</v>
+      </c>
+      <c r="AE2">
         <v>1.02</v>
       </c>
-      <c r="Y2">
+      <c r="AF2">
+        <v>1.95</v>
+      </c>
+      <c r="AG2">
+        <v>1.74</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2">
         <v>1.2</v>
       </c>
-      <c r="Z2">
-        <v>3.85</v>
-      </c>
-      <c r="AA2">
-        <v>1.71</v>
-      </c>
-      <c r="AB2">
-        <v>2.1</v>
-      </c>
-      <c r="AC2">
-        <v>2.79</v>
-      </c>
-      <c r="AD2">
-        <v>1.44</v>
-      </c>
-      <c r="AE2">
-        <v>1.17</v>
-      </c>
-      <c r="AF2">
-        <v>1.85</v>
-      </c>
-      <c r="AG2">
-        <v>1.76</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2">
-        <v>1.07</v>
-      </c>
       <c r="AK2">
-        <v>2.74</v>
+        <v>1.78</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.11</v>
+        <v>1.36</v>
       </c>
       <c r="O3">
-        <v>3.35</v>
+        <v>4.25</v>
       </c>
       <c r="P3">
-        <v>3.37</v>
+        <v>7.05</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1133,52 +1133,52 @@
         <v>1.14</v>
       </c>
       <c r="Q5">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
       <c r="R5">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="S5">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T5">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="U5">
+        <v>2.14</v>
+      </c>
+      <c r="V5">
+        <v>1.62</v>
+      </c>
+      <c r="W5">
+        <v>1.14</v>
+      </c>
+      <c r="X5">
+        <v>1.02</v>
+      </c>
+      <c r="Y5">
+        <v>1.11</v>
+      </c>
+      <c r="Z5">
+        <v>4.95</v>
+      </c>
+      <c r="AA5">
+        <v>1.43</v>
+      </c>
+      <c r="AB5">
+        <v>2.46</v>
+      </c>
+      <c r="AC5">
         <v>2.08</v>
       </c>
-      <c r="V5">
+      <c r="AD5">
         <v>1.65</v>
-      </c>
-      <c r="W5">
-        <v>1.15</v>
-      </c>
-      <c r="X5">
-        <v>1</v>
-      </c>
-      <c r="Y5">
-        <v>1.1</v>
-      </c>
-      <c r="Z5">
-        <v>5.2</v>
-      </c>
-      <c r="AA5">
-        <v>1.39</v>
-      </c>
-      <c r="AB5">
-        <v>2.59</v>
-      </c>
-      <c r="AC5">
-        <v>1.98</v>
-      </c>
-      <c r="AD5">
-        <v>1.72</v>
       </c>
       <c r="AE5">
         <v>1.28</v>
       </c>
       <c r="AF5">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AG5">
         <v>1.81</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AK5">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O7">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P7">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -1465,22 +1465,22 @@
         <v>2.25</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U7">
-        <v>2.38</v>
+        <v>2.67</v>
       </c>
       <c r="V7">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
         <v>1.21</v>
@@ -1489,7 +1489,7 @@
         <v>3.6</v>
       </c>
       <c r="AA7">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AB7">
         <v>1.94</v>
@@ -1498,10 +1498,10 @@
         <v>2.75</v>
       </c>
       <c r="AD7">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE7">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF7">
         <v>1.65</v>
@@ -1776,10 +1776,10 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="O9">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P9">
         <v>4.2</v>
@@ -1788,7 +1788,7 @@
         <v>2.15</v>
       </c>
       <c r="R9">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="S9">
         <v>1.3</v>
@@ -1800,10 +1800,10 @@
         <v>2.5</v>
       </c>
       <c r="V9">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W9">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
         <v>1.02</v>
@@ -1815,10 +1815,10 @@
         <v>3.6</v>
       </c>
       <c r="AA9">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AB9">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AC9">
         <v>2.88</v>
@@ -1827,10 +1827,10 @@
         <v>1.36</v>
       </c>
       <c r="AE9">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF9">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AG9">
         <v>1.97</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="O20">
         <v>4.65</v>
       </c>
       <c r="P20">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="Q20">
         <v>1.78</v>
@@ -3593,7 +3593,7 @@
         <v>1.93</v>
       </c>
       <c r="V20">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="W20">
         <v>1.21</v>
@@ -3602,31 +3602,31 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Z20">
-        <v>6.25</v>
+        <v>5.8</v>
       </c>
       <c r="AA20">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB20">
         <v>2.97</v>
       </c>
       <c r="AC20">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AD20">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AE20">
         <v>1.39</v>
       </c>
       <c r="AF20">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG20">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK20">
         <v>2.71</v>
@@ -4227,13 +4227,13 @@
         <v>4.1</v>
       </c>
       <c r="P24">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="Q24">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="R24">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="S24">
         <v>1.17</v>
@@ -4272,7 +4272,7 @@
         <v>1.63</v>
       </c>
       <c r="AE24">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF24">
         <v>1.36</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK24">
         <v>2.1</v>
@@ -4719,7 +4719,7 @@
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="R27">
         <v>2.4</v>
@@ -4731,10 +4731,10 @@
         <v>3.8</v>
       </c>
       <c r="U27">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V27">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W27">
         <v>1.17</v>
@@ -4752,7 +4752,7 @@
         <v>1.49</v>
       </c>
       <c r="AB27">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="AC27">
         <v>2.17</v>
@@ -4767,7 +4767,7 @@
         <v>1.45</v>
       </c>
       <c r="AG27">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>3.8</v>
       </c>
       <c r="P28">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5042,25 +5042,25 @@
         <v>4.15</v>
       </c>
       <c r="P29">
-        <v>3.95</v>
+        <v>3.39</v>
       </c>
       <c r="Q29">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="R29">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="S29">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T29">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U29">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="V29">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="W29">
         <v>1.18</v>
@@ -5078,7 +5078,7 @@
         <v>1.4</v>
       </c>
       <c r="AB29">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="AC29">
         <v>2</v>
@@ -5090,10 +5090,10 @@
         <v>1.22</v>
       </c>
       <c r="AF29">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AG29">
-        <v>2.61</v>
+        <v>2.68</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK29">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5217,16 +5217,16 @@
         <v>1.36</v>
       </c>
       <c r="T30">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="U30">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="V30">
         <v>1.36</v>
       </c>
       <c r="W30">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X30">
         <v>1.01</v>
@@ -5272,7 +5272,7 @@
         <v>1.24</v>
       </c>
       <c r="AK30">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5851,16 +5851,16 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="O34">
         <v>3.3</v>
       </c>
       <c r="P34">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="Q34">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="R34">
         <v>2.2</v>
@@ -5869,13 +5869,13 @@
         <v>1.34</v>
       </c>
       <c r="T34">
-        <v>3.01</v>
+        <v>2.84</v>
       </c>
       <c r="U34">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="V34">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W34">
         <v>1.1</v>
@@ -5884,10 +5884,10 @@
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z34">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="AA34">
         <v>1.9</v>
@@ -5896,16 +5896,16 @@
         <v>1.9</v>
       </c>
       <c r="AC34">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="AD34">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE34">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF34">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG34">
         <v>2</v>
@@ -5924,7 +5924,7 @@
         <v>1.19</v>
       </c>
       <c r="AK34">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,22 +6014,22 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="O35">
         <v>3</v>
       </c>
       <c r="P35">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q35">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R35">
         <v>2.05</v>
       </c>
       <c r="S35">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T35">
         <v>2.75</v>
@@ -6038,31 +6038,31 @@
         <v>2.82</v>
       </c>
       <c r="V35">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W35">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z35">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AA35">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AB35">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC35">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD35">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE35">
         <v>1.08</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AK35">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="O36">
         <v>3.4</v>
@@ -6186,7 +6186,7 @@
         <v>4.4</v>
       </c>
       <c r="Q36">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="R36">
         <v>2.12</v>
@@ -6216,7 +6216,7 @@
         <v>3.14</v>
       </c>
       <c r="AA36">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AB36">
         <v>1.78</v>
@@ -6228,7 +6228,7 @@
         <v>1.26</v>
       </c>
       <c r="AE36">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF36">
         <v>1.84</v>
@@ -6340,19 +6340,19 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O37">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="P37">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="Q37">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="R37">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S37">
         <v>1.42</v>
@@ -6361,10 +6361,10 @@
         <v>2.65</v>
       </c>
       <c r="U37">
-        <v>2.99</v>
+        <v>2.86</v>
       </c>
       <c r="V37">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W37">
         <v>1.05</v>
@@ -6382,7 +6382,7 @@
         <v>2.08</v>
       </c>
       <c r="AB37">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC37">
         <v>3.7</v>
@@ -6413,7 +6413,7 @@
         <v>1.36</v>
       </c>
       <c r="AK37">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6518,28 +6518,28 @@
         <v>1.92</v>
       </c>
       <c r="S38">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="T38">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="U38">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="V38">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W38">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X38">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y38">
         <v>1.51</v>
       </c>
       <c r="Z38">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="AA38">
         <v>2.6</v>
@@ -6548,10 +6548,10 @@
         <v>1.42</v>
       </c>
       <c r="AC38">
-        <v>5.05</v>
+        <v>5.11</v>
       </c>
       <c r="AD38">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AE38">
         <v>1.01</v>
@@ -6666,31 +6666,31 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="O39">
         <v>3</v>
       </c>
       <c r="P39">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="Q39">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R39">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="S39">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="T39">
-        <v>2.6</v>
+        <v>2.31</v>
       </c>
       <c r="U39">
         <v>3.2</v>
       </c>
       <c r="V39">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W39">
         <v>1.01</v>
@@ -6699,22 +6699,22 @@
         <v>1.09</v>
       </c>
       <c r="Y39">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="Z39">
-        <v>2.85</v>
+        <v>2.43</v>
       </c>
       <c r="AA39">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="AB39">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AC39">
-        <v>4.83</v>
+        <v>4.89</v>
       </c>
       <c r="AD39">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AE39">
         <v>1.01</v>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK39">
         <v>1.54</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.11</v>
+        <v>1.36</v>
       </c>
       <c r="O2">
-        <v>3.35</v>
+        <v>4.25</v>
       </c>
       <c r="P2">
-        <v>3.37</v>
+        <v>7.05</v>
       </c>
       <c r="Q2">
+        <v>1.85</v>
+      </c>
+      <c r="R2">
+        <v>2.4</v>
+      </c>
+      <c r="S2">
+        <v>1.32</v>
+      </c>
+      <c r="T2">
+        <v>2.92</v>
+      </c>
+      <c r="U2">
         <v>2.55</v>
       </c>
-      <c r="R2">
-        <v>1.91</v>
-      </c>
-      <c r="S2">
+      <c r="V2">
+        <v>1.49</v>
+      </c>
+      <c r="W2">
+        <v>1.11</v>
+      </c>
+      <c r="X2">
+        <v>1.02</v>
+      </c>
+      <c r="Y2">
+        <v>1.2</v>
+      </c>
+      <c r="Z2">
+        <v>3.85</v>
+      </c>
+      <c r="AA2">
+        <v>1.71</v>
+      </c>
+      <c r="AB2">
+        <v>2.1</v>
+      </c>
+      <c r="AC2">
+        <v>2.79</v>
+      </c>
+      <c r="AD2">
         <v>1.44</v>
       </c>
-      <c r="T2">
-        <v>2.39</v>
-      </c>
-      <c r="U2">
-        <v>3.2</v>
-      </c>
-      <c r="V2">
-        <v>1.27</v>
-      </c>
-      <c r="W2">
-        <v>1.05</v>
-      </c>
-      <c r="X2">
-        <v>1.04</v>
-      </c>
-      <c r="Y2">
-        <v>1.4</v>
-      </c>
-      <c r="Z2">
-        <v>2.88</v>
-      </c>
-      <c r="AA2">
-        <v>2.21</v>
-      </c>
-      <c r="AB2">
-        <v>1.57</v>
-      </c>
-      <c r="AC2">
-        <v>4.86</v>
-      </c>
-      <c r="AD2">
-        <v>1.18</v>
-      </c>
       <c r="AE2">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="AF2">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG2">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AK2">
-        <v>1.78</v>
+        <v>2.74</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G3">
@@ -798,80 +798,80 @@
         </is>
       </c>
       <c r="N3">
+        <v>1.75</v>
+      </c>
+      <c r="O3">
+        <v>3.4</v>
+      </c>
+      <c r="P3">
+        <v>4.1</v>
+      </c>
+      <c r="Q3">
+        <v>2.3</v>
+      </c>
+      <c r="R3">
+        <v>2.28</v>
+      </c>
+      <c r="S3">
+        <v>1.35</v>
+      </c>
+      <c r="T3">
+        <v>2.98</v>
+      </c>
+      <c r="U3">
+        <v>2.67</v>
+      </c>
+      <c r="V3">
+        <v>1.43</v>
+      </c>
+      <c r="W3">
+        <v>1.1</v>
+      </c>
+      <c r="X3">
+        <v>1.01</v>
+      </c>
+      <c r="Y3">
+        <v>1.25</v>
+      </c>
+      <c r="Z3">
+        <v>3.8</v>
+      </c>
+      <c r="AA3">
+        <v>1.85</v>
+      </c>
+      <c r="AB3">
+        <v>1.91</v>
+      </c>
+      <c r="AC3">
+        <v>3.1</v>
+      </c>
+      <c r="AD3">
         <v>1.36</v>
       </c>
-      <c r="O3">
-        <v>4.25</v>
-      </c>
-      <c r="P3">
-        <v>7.05</v>
-      </c>
-      <c r="Q3">
-        <v>1.85</v>
-      </c>
-      <c r="R3">
-        <v>2.4</v>
-      </c>
-      <c r="S3">
-        <v>1.32</v>
-      </c>
-      <c r="T3">
-        <v>2.92</v>
-      </c>
-      <c r="U3">
-        <v>2.55</v>
-      </c>
-      <c r="V3">
-        <v>1.49</v>
-      </c>
-      <c r="W3">
-        <v>1.11</v>
-      </c>
-      <c r="X3">
-        <v>1.02</v>
-      </c>
-      <c r="Y3">
+      <c r="AE3">
+        <v>1.07</v>
+      </c>
+      <c r="AF3">
+        <v>1.8</v>
+      </c>
+      <c r="AG3">
+        <v>1.95</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3">
         <v>1.2</v>
       </c>
-      <c r="Z3">
-        <v>3.85</v>
-      </c>
-      <c r="AA3">
-        <v>1.71</v>
-      </c>
-      <c r="AB3">
-        <v>2.1</v>
-      </c>
-      <c r="AC3">
-        <v>2.79</v>
-      </c>
-      <c r="AD3">
-        <v>1.44</v>
-      </c>
-      <c r="AE3">
-        <v>1.17</v>
-      </c>
-      <c r="AF3">
-        <v>1.85</v>
-      </c>
-      <c r="AG3">
-        <v>1.76</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3">
-        <v>1.07</v>
-      </c>
       <c r="AK3">
-        <v>2.74</v>
+        <v>1.9</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P4">
-        <v>4.1</v>
+        <v>3.37</v>
       </c>
       <c r="Q4">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="R4">
-        <v>2.28</v>
+        <v>1.91</v>
       </c>
       <c r="S4">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="T4">
-        <v>2.98</v>
+        <v>2.39</v>
       </c>
       <c r="U4">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="V4">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="W4">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="Z4">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA4">
-        <v>1.85</v>
+        <v>2.21</v>
       </c>
       <c r="AB4">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AC4">
-        <v>3.1</v>
+        <v>4.86</v>
       </c>
       <c r="AD4">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AE4">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF4">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AG4">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.2</v>
       </c>
       <c r="AK4">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1290,13 +1290,13 @@
         <v>1.75</v>
       </c>
       <c r="O6">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P6">
         <v>4</v>
       </c>
       <c r="Q6">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="R6">
         <v>2.2</v>
@@ -1326,13 +1326,13 @@
         <v>3.5</v>
       </c>
       <c r="AA6">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AB6">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AC6">
-        <v>3.35</v>
+        <v>3.08</v>
       </c>
       <c r="AD6">
         <v>1.31</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AK6">
         <v>2</v>
@@ -1631,7 +1631,7 @@
         <v>1.33</v>
       </c>
       <c r="T8">
-        <v>2.99</v>
+        <v>3.17</v>
       </c>
       <c r="U8">
         <v>2.6</v>
@@ -2111,7 +2111,7 @@
         <v>1.33</v>
       </c>
       <c r="Q11">
-        <v>7.43</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="R11">
         <v>2.45</v>
@@ -2120,7 +2120,7 @@
         <v>1.3</v>
       </c>
       <c r="T11">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U11">
         <v>2.38</v>
@@ -2129,7 +2129,7 @@
         <v>1.48</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
         <v>1.01</v>
@@ -2138,25 +2138,25 @@
         <v>1.18</v>
       </c>
       <c r="Z11">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AA11">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB11">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC11">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="AD11">
         <v>1.42</v>
       </c>
       <c r="AE11">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF11">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AG11">
         <v>1.68</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>3.05</v>
+        <v>3.18</v>
       </c>
       <c r="AK11">
         <v>1.02</v>
@@ -2274,7 +2274,7 @@
         <v>3.1</v>
       </c>
       <c r="Q12">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="R12">
         <v>2.21</v>
@@ -2292,7 +2292,7 @@
         <v>1.5</v>
       </c>
       <c r="W12">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
         <v>1.02</v>
@@ -2307,7 +2307,7 @@
         <v>1.7</v>
       </c>
       <c r="AB12">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AC12">
         <v>2.88</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK12">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2594,10 +2594,10 @@
         <v>2.75</v>
       </c>
       <c r="O14">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="P14">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="Q14">
         <v>3.4</v>
@@ -2609,19 +2609,19 @@
         <v>1.4</v>
       </c>
       <c r="T14">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="U14">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V14">
         <v>1.35</v>
       </c>
       <c r="W14">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X14">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
         <v>1.35</v>
@@ -2645,10 +2645,10 @@
         <v>1.02</v>
       </c>
       <c r="AF14">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AG14">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>1.7</v>
       </c>
       <c r="O16">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="P16">
         <v>4.2</v>
@@ -2935,7 +2935,7 @@
         <v>1.33</v>
       </c>
       <c r="T16">
-        <v>3.04</v>
+        <v>3.33</v>
       </c>
       <c r="U16">
         <v>2.56</v>
@@ -2953,19 +2953,19 @@
         <v>1.19</v>
       </c>
       <c r="Z16">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="AA16">
         <v>1.73</v>
       </c>
       <c r="AB16">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="AC16">
         <v>2.95</v>
       </c>
       <c r="AD16">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE16">
         <v>1.1</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AK16">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="O23">
         <v>3.4</v>
       </c>
       <c r="P23">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q23">
         <v>2.72</v>
@@ -4079,43 +4079,43 @@
         <v>3.2</v>
       </c>
       <c r="U23">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V23">
         <v>1.42</v>
       </c>
       <c r="W23">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X23">
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z23">
-        <v>4.02</v>
+        <v>3.82</v>
       </c>
       <c r="AA23">
         <v>1.73</v>
       </c>
       <c r="AB23">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AC23">
         <v>2.7</v>
       </c>
       <c r="AD23">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE23">
         <v>1.1</v>
       </c>
       <c r="AF23">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AG23">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="O24">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P24">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="Q24">
         <v>2.11</v>
@@ -4257,10 +4257,10 @@
         <v>1.07</v>
       </c>
       <c r="Z24">
-        <v>5.85</v>
+        <v>5.9</v>
       </c>
       <c r="AA24">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AB24">
         <v>2.83</v>
@@ -4384,19 +4384,19 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="O25">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="P25">
         <v>4.3</v>
       </c>
       <c r="Q25">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="R25">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="S25">
         <v>1.34</v>
@@ -4414,16 +4414,16 @@
         <v>1.06</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z25">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA25">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AB25">
         <v>1.95</v>
@@ -4432,13 +4432,13 @@
         <v>3.1</v>
       </c>
       <c r="AD25">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE25">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF25">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AG25">
         <v>1.87</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="O26">
         <v>3.2</v>
@@ -4556,13 +4556,13 @@
         <v>2.25</v>
       </c>
       <c r="Q26">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="R26">
         <v>2.1</v>
       </c>
       <c r="S26">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T26">
         <v>2.59</v>
@@ -4574,7 +4574,7 @@
         <v>1.33</v>
       </c>
       <c r="W26">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
         <v>1.06</v>
@@ -4589,7 +4589,7 @@
         <v>2</v>
       </c>
       <c r="AB26">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC26">
         <v>3.5</v>
@@ -4601,7 +4601,7 @@
         <v>1.04</v>
       </c>
       <c r="AF26">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG26">
         <v>1.85</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AK26">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4722,7 +4722,7 @@
         <v>2.17</v>
       </c>
       <c r="R27">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="S27">
         <v>1.22</v>
@@ -4737,7 +4737,7 @@
         <v>1.62</v>
       </c>
       <c r="W27">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X27">
         <v>1.02</v>
@@ -4767,7 +4767,7 @@
         <v>1.45</v>
       </c>
       <c r="AG27">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AK27">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5036,19 +5036,19 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="O29">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="P29">
-        <v>3.39</v>
+        <v>3.96</v>
       </c>
       <c r="Q29">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="R29">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="S29">
         <v>1.22</v>
@@ -5078,7 +5078,7 @@
         <v>1.4</v>
       </c>
       <c r="AB29">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AC29">
         <v>2</v>
@@ -5087,10 +5087,10 @@
         <v>1.8</v>
       </c>
       <c r="AE29">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AF29">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG29">
         <v>2.68</v>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK29">
         <v>2.02</v>
@@ -5223,7 +5223,7 @@
         <v>3.08</v>
       </c>
       <c r="V30">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W30">
         <v>1.03</v>
@@ -5232,25 +5232,25 @@
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z30">
         <v>3</v>
       </c>
       <c r="AA30">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB30">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC30">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="AD30">
         <v>1.19</v>
       </c>
       <c r="AE30">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF30">
         <v>1.75</v>
@@ -5386,7 +5386,7 @@
         <v>3.42</v>
       </c>
       <c r="V31">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W31">
         <v>1</v>
@@ -5395,10 +5395,10 @@
         <v>1.1</v>
       </c>
       <c r="Y31">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="Z31">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="AA31">
         <v>2.54</v>
@@ -5407,7 +5407,7 @@
         <v>1.5</v>
       </c>
       <c r="AC31">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AD31">
         <v>1.17</v>
@@ -5419,7 +5419,7 @@
         <v>2</v>
       </c>
       <c r="AG31">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="O32">
+        <v>3.1</v>
+      </c>
+      <c r="P32">
+        <v>3.3</v>
+      </c>
+      <c r="Q32">
+        <v>2.62</v>
+      </c>
+      <c r="R32">
+        <v>2</v>
+      </c>
+      <c r="S32">
+        <v>1.46</v>
+      </c>
+      <c r="T32">
+        <v>2.47</v>
+      </c>
+      <c r="U32">
         <v>3.2</v>
       </c>
-      <c r="P32">
-        <v>3.86</v>
-      </c>
-      <c r="Q32">
-        <v>2.55</v>
-      </c>
-      <c r="R32">
-        <v>2.05</v>
-      </c>
-      <c r="S32">
-        <v>1.43</v>
-      </c>
-      <c r="T32">
-        <v>2.8</v>
-      </c>
-      <c r="U32">
-        <v>3</v>
-      </c>
       <c r="V32">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W32">
         <v>1.05</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="Z32">
-        <v>2.97</v>
+        <v>2.91</v>
       </c>
       <c r="AA32">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB32">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AC32">
-        <v>3.42</v>
+        <v>3.88</v>
       </c>
       <c r="AD32">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE32">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF32">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG32">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>1.29</v>
       </c>
       <c r="AK32">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,58 +5688,58 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="O33">
         <v>3.2</v>
       </c>
       <c r="P33">
-        <v>3.3</v>
+        <v>3.86</v>
       </c>
       <c r="Q33">
-        <v>2.62</v>
+        <v>2.39</v>
       </c>
       <c r="R33">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="S33">
         <v>1.43</v>
       </c>
       <c r="T33">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="U33">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="V33">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W33">
         <v>1.05</v>
       </c>
       <c r="X33">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z33">
-        <v>3.07</v>
+        <v>2.97</v>
       </c>
       <c r="AA33">
         <v>2.1</v>
       </c>
       <c r="AB33">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC33">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="AD33">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE33">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF33">
         <v>1.85</v>
@@ -5761,7 +5761,7 @@
         <v>1.29</v>
       </c>
       <c r="AK33">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="O34">
         <v>3.3</v>
       </c>
       <c r="P34">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="Q34">
         <v>2.6</v>
@@ -5869,7 +5869,7 @@
         <v>1.34</v>
       </c>
       <c r="T34">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="U34">
         <v>2.74</v>
@@ -5884,16 +5884,16 @@
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z34">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="AA34">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB34">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC34">
         <v>3.08</v>
@@ -6029,7 +6029,7 @@
         <v>2.05</v>
       </c>
       <c r="S35">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T35">
         <v>2.75</v>
@@ -6041,31 +6041,31 @@
         <v>1.32</v>
       </c>
       <c r="W35">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X35">
         <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z35">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AA35">
         <v>2.04</v>
       </c>
       <c r="AB35">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AC35">
         <v>3.5</v>
       </c>
       <c r="AD35">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE35">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF35">
         <v>1.7</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="AK35">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,58 +6177,58 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="O36">
         <v>3.4</v>
       </c>
       <c r="P36">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="Q36">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="R36">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="S36">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T36">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="U36">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="V36">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W36">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z36">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="AA36">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AB36">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AC36">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AD36">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE36">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AF36">
         <v>1.84</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AK36">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6343,10 +6343,10 @@
         <v>2.2</v>
       </c>
       <c r="O37">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="P37">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="Q37">
         <v>2.9</v>
@@ -6376,13 +6376,13 @@
         <v>1.32</v>
       </c>
       <c r="Z37">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA37">
         <v>2.08</v>
       </c>
       <c r="AB37">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC37">
         <v>3.7</v>
@@ -6394,7 +6394,7 @@
         <v>1.05</v>
       </c>
       <c r="AF37">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG37">
         <v>1.9</v>
@@ -6503,10 +6503,10 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="O38">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="P38">
         <v>6.15</v>
@@ -6539,7 +6539,7 @@
         <v>1.51</v>
       </c>
       <c r="Z38">
-        <v>2.35</v>
+        <v>2.47</v>
       </c>
       <c r="AA38">
         <v>2.6</v>
@@ -6675,7 +6675,7 @@
         <v>2.9</v>
       </c>
       <c r="Q39">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="R39">
         <v>1.9</v>
@@ -6690,13 +6690,13 @@
         <v>3.2</v>
       </c>
       <c r="V39">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="W39">
         <v>1.01</v>
       </c>
       <c r="X39">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="Y39">
         <v>1.44</v>
@@ -6708,13 +6708,13 @@
         <v>2.47</v>
       </c>
       <c r="AB39">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC39">
         <v>4.89</v>
       </c>
       <c r="AD39">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="AE39">
         <v>1.01</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="O3">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P3">
-        <v>4.1</v>
+        <v>3.37</v>
       </c>
       <c r="Q3">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="R3">
-        <v>2.28</v>
+        <v>1.91</v>
       </c>
       <c r="S3">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="T3">
-        <v>2.98</v>
+        <v>2.39</v>
       </c>
       <c r="U3">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="V3">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="W3">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y3">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="Z3">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA3">
-        <v>1.85</v>
+        <v>2.21</v>
       </c>
       <c r="AB3">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AC3">
-        <v>3.1</v>
+        <v>4.86</v>
       </c>
       <c r="AD3">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AE3">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF3">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AG3">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.2</v>
       </c>
       <c r="AK3">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="O4">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>3.37</v>
+        <v>4.1</v>
       </c>
       <c r="Q4">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="R4">
+        <v>2.28</v>
+      </c>
+      <c r="S4">
+        <v>1.35</v>
+      </c>
+      <c r="T4">
+        <v>2.98</v>
+      </c>
+      <c r="U4">
+        <v>2.67</v>
+      </c>
+      <c r="V4">
+        <v>1.43</v>
+      </c>
+      <c r="W4">
+        <v>1.1</v>
+      </c>
+      <c r="X4">
+        <v>1.01</v>
+      </c>
+      <c r="Y4">
+        <v>1.25</v>
+      </c>
+      <c r="Z4">
+        <v>3.8</v>
+      </c>
+      <c r="AA4">
+        <v>1.85</v>
+      </c>
+      <c r="AB4">
         <v>1.91</v>
       </c>
-      <c r="S4">
-        <v>1.44</v>
-      </c>
-      <c r="T4">
-        <v>2.39</v>
-      </c>
-      <c r="U4">
-        <v>3.2</v>
-      </c>
-      <c r="V4">
-        <v>1.27</v>
-      </c>
-      <c r="W4">
-        <v>1.05</v>
-      </c>
-      <c r="X4">
-        <v>1.04</v>
-      </c>
-      <c r="Y4">
-        <v>1.4</v>
-      </c>
-      <c r="Z4">
-        <v>2.88</v>
-      </c>
-      <c r="AA4">
-        <v>2.21</v>
-      </c>
-      <c r="AB4">
-        <v>1.57</v>
-      </c>
       <c r="AC4">
-        <v>4.86</v>
+        <v>3.1</v>
       </c>
       <c r="AD4">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AE4">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF4">
+        <v>1.8</v>
+      </c>
+      <c r="AG4">
         <v>1.95</v>
-      </c>
-      <c r="AG4">
-        <v>1.74</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.2</v>
       </c>
       <c r="AK4">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -2594,10 +2594,10 @@
         <v>2.75</v>
       </c>
       <c r="O14">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="P14">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="Q14">
         <v>3.4</v>
@@ -2606,13 +2606,13 @@
         <v>2.05</v>
       </c>
       <c r="S14">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T14">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="U14">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="V14">
         <v>1.35</v>
@@ -2642,13 +2642,13 @@
         <v>1.18</v>
       </c>
       <c r="AE14">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF14">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AG14">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>1.22</v>
       </c>
       <c r="T27">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U27">
         <v>2.16</v>
@@ -4752,7 +4752,7 @@
         <v>1.49</v>
       </c>
       <c r="AB27">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AC27">
         <v>2.17</v>
@@ -4764,7 +4764,7 @@
         <v>1.22</v>
       </c>
       <c r="AF27">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AG27">
         <v>2.45</v>
@@ -4879,7 +4879,7 @@
         <v>3.8</v>
       </c>
       <c r="P28">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5199,16 +5199,16 @@
         </is>
       </c>
       <c r="N30">
+        <v>3.77</v>
+      </c>
+      <c r="O30">
         <v>3.4</v>
       </c>
-      <c r="O30">
-        <v>3.3</v>
-      </c>
       <c r="P30">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q30">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R30">
         <v>2.02</v>
@@ -5217,13 +5217,13 @@
         <v>1.36</v>
       </c>
       <c r="T30">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="U30">
         <v>3.08</v>
       </c>
       <c r="V30">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W30">
         <v>1.03</v>
@@ -5232,7 +5232,7 @@
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z30">
         <v>3</v>
@@ -5244,7 +5244,7 @@
         <v>1.75</v>
       </c>
       <c r="AC30">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="AD30">
         <v>1.19</v>
@@ -5362,25 +5362,25 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="O31">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P31">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q31">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="R31">
         <v>1.92</v>
       </c>
       <c r="S31">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="T31">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="U31">
         <v>3.42</v>
@@ -5401,13 +5401,13 @@
         <v>2.46</v>
       </c>
       <c r="AA31">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="AB31">
         <v>1.5</v>
       </c>
       <c r="AC31">
-        <v>5.25</v>
+        <v>5.02</v>
       </c>
       <c r="AD31">
         <v>1.17</v>
@@ -5419,7 +5419,7 @@
         <v>2</v>
       </c>
       <c r="AG31">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK31">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,19 +5525,19 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="O32">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P32">
-        <v>3.3</v>
+        <v>3.86</v>
       </c>
       <c r="Q32">
         <v>2.62</v>
       </c>
       <c r="R32">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="S32">
         <v>1.46</v>
@@ -5546,7 +5546,7 @@
         <v>2.47</v>
       </c>
       <c r="U32">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V32">
         <v>1.31</v>
@@ -5558,7 +5558,7 @@
         <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="Z32">
         <v>2.91</v>
@@ -5573,10 +5573,10 @@
         <v>3.88</v>
       </c>
       <c r="AD32">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AE32">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF32">
         <v>1.9</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK32">
         <v>1.73</v>
@@ -5697,28 +5697,28 @@
         <v>3.86</v>
       </c>
       <c r="Q33">
-        <v>2.39</v>
+        <v>2.48</v>
       </c>
       <c r="R33">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="S33">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="T33">
         <v>2.8</v>
       </c>
       <c r="U33">
-        <v>2.95</v>
+        <v>3.11</v>
       </c>
       <c r="V33">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W33">
         <v>1.05</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y33">
         <v>1.36</v>
@@ -5733,16 +5733,16 @@
         <v>1.7</v>
       </c>
       <c r="AC33">
-        <v>3.42</v>
+        <v>3.76</v>
       </c>
       <c r="AD33">
         <v>1.23</v>
       </c>
       <c r="AE33">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF33">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG33">
         <v>1.83</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK33">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="O34">
         <v>3.3</v>
       </c>
       <c r="P34">
-        <v>3.35</v>
+        <v>3.22</v>
       </c>
       <c r="Q34">
         <v>2.6</v>
@@ -5875,10 +5875,10 @@
         <v>2.74</v>
       </c>
       <c r="V34">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W34">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X34">
         <v>1.01</v>
@@ -6014,19 +6014,19 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O35">
         <v>3</v>
       </c>
       <c r="P35">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="Q35">
         <v>3.4</v>
       </c>
       <c r="R35">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="S35">
         <v>1.44</v>
@@ -6035,7 +6035,7 @@
         <v>2.75</v>
       </c>
       <c r="U35">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="V35">
         <v>1.32</v>
@@ -6044,31 +6044,31 @@
         <v>1.05</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y35">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z35">
         <v>2.92</v>
       </c>
       <c r="AA35">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AB35">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC35">
         <v>3.5</v>
       </c>
       <c r="AD35">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE35">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF35">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AG35">
         <v>1.83</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AK35">
         <v>1.33</v>
@@ -6177,19 +6177,19 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="O36">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="P36">
-        <v>3.9</v>
+        <v>4.17</v>
       </c>
       <c r="Q36">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="R36">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="S36">
         <v>1.38</v>
@@ -6216,7 +6216,7 @@
         <v>3.04</v>
       </c>
       <c r="AA36">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AB36">
         <v>1.73</v>
@@ -6250,7 +6250,7 @@
         <v>1.15</v>
       </c>
       <c r="AK36">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6352,7 +6352,7 @@
         <v>2.9</v>
       </c>
       <c r="R37">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="S37">
         <v>1.42</v>
@@ -6382,7 +6382,7 @@
         <v>2.08</v>
       </c>
       <c r="AB37">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC37">
         <v>3.7</v>
@@ -6397,7 +6397,7 @@
         <v>1.8</v>
       </c>
       <c r="AG37">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6539,13 +6539,13 @@
         <v>1.51</v>
       </c>
       <c r="Z38">
-        <v>2.47</v>
+        <v>2.35</v>
       </c>
       <c r="AA38">
         <v>2.6</v>
       </c>
       <c r="AB38">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AC38">
         <v>5.11</v>
@@ -6576,7 +6576,7 @@
         <v>1.07</v>
       </c>
       <c r="AK38">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6669,10 +6669,10 @@
         <v>2.25</v>
       </c>
       <c r="O39">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="P39">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="Q39">
         <v>2.98</v>
@@ -6723,7 +6723,7 @@
         <v>1.95</v>
       </c>
       <c r="AG39">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -1287,16 +1287,16 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="O6">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P6">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="Q6">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="R6">
         <v>2.2</v>
@@ -1305,7 +1305,7 @@
         <v>1.4</v>
       </c>
       <c r="T6">
-        <v>2.77</v>
+        <v>3.01</v>
       </c>
       <c r="U6">
         <v>2.8</v>
@@ -1323,28 +1323,28 @@
         <v>1.29</v>
       </c>
       <c r="Z6">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA6">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AB6">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AC6">
-        <v>3.08</v>
+        <v>3.36</v>
       </c>
       <c r="AD6">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE6">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF6">
         <v>1.75</v>
       </c>
       <c r="AG6">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AK6">
         <v>2</v>
@@ -1622,25 +1622,25 @@
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>4.33</v>
+        <v>4.38</v>
       </c>
       <c r="R8">
         <v>2.2</v>
       </c>
       <c r="S8">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T8">
         <v>3.17</v>
       </c>
       <c r="U8">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V8">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W8">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X8">
         <v>1.02</v>
@@ -1664,7 +1664,7 @@
         <v>1.33</v>
       </c>
       <c r="AE8">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF8">
         <v>1.65</v>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="O10">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="P10">
         <v>2.7</v>
@@ -1957,7 +1957,7 @@
         <v>1.33</v>
       </c>
       <c r="T10">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="U10">
         <v>2.63</v>
@@ -1969,7 +1969,7 @@
         <v>1.05</v>
       </c>
       <c r="X10">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
         <v>1.25</v>
@@ -1981,22 +1981,22 @@
         <v>1.85</v>
       </c>
       <c r="AB10">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AC10">
-        <v>2.97</v>
+        <v>3.13</v>
       </c>
       <c r="AD10">
         <v>1.33</v>
       </c>
       <c r="AE10">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF10">
         <v>1.67</v>
       </c>
       <c r="AG10">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK10">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,25 +2102,25 @@
         </is>
       </c>
       <c r="N11">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="O11">
-        <v>4.6</v>
+        <v>4.35</v>
       </c>
       <c r="P11">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Q11">
-        <v>8.109999999999999</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="R11">
         <v>2.45</v>
       </c>
       <c r="S11">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T11">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="U11">
         <v>2.38</v>
@@ -2147,19 +2147,19 @@
         <v>2.1</v>
       </c>
       <c r="AC11">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="AD11">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE11">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF11">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AG11">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>3.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="N12">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O12">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P12">
         <v>3.1</v>
@@ -2277,28 +2277,28 @@
         <v>2.58</v>
       </c>
       <c r="R12">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="S12">
         <v>1.29</v>
       </c>
       <c r="T12">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="U12">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="V12">
         <v>1.5</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z12">
         <v>4.33</v>
@@ -2307,13 +2307,13 @@
         <v>1.7</v>
       </c>
       <c r="AB12">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="AC12">
         <v>2.88</v>
       </c>
       <c r="AD12">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE12">
         <v>1.16</v>
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="O13">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P13">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q13">
-        <v>3.46</v>
+        <v>3.9</v>
       </c>
       <c r="R13">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="S13">
         <v>1.55</v>
@@ -2455,7 +2455,7 @@
         <v>1.24</v>
       </c>
       <c r="W13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X13">
         <v>1.05</v>
@@ -2464,19 +2464,19 @@
         <v>1.42</v>
       </c>
       <c r="Z13">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="AA13">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AB13">
         <v>1.52</v>
       </c>
       <c r="AC13">
-        <v>4.73</v>
+        <v>4.6</v>
       </c>
       <c r="AD13">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE13">
         <v>1.01</v>
@@ -3406,22 +3406,22 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="O19">
-        <v>3.78</v>
+        <v>3.84</v>
       </c>
       <c r="P19">
         <v>3.73</v>
       </c>
       <c r="Q19">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R19">
         <v>2.38</v>
       </c>
       <c r="S19">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T19">
         <v>3.22</v>
@@ -3436,25 +3436,25 @@
         <v>1.08</v>
       </c>
       <c r="X19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z19">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="AA19">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB19">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AC19">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="AD19">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE19">
         <v>1.17</v>
@@ -3479,7 +3479,7 @@
         <v>1.14</v>
       </c>
       <c r="AK19">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="O20">
         <v>4.65</v>
       </c>
       <c r="P20">
-        <v>6.3</v>
+        <v>5.25</v>
       </c>
       <c r="Q20">
         <v>1.78</v>
@@ -3587,7 +3587,7 @@
         <v>1.16</v>
       </c>
       <c r="T20">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="U20">
         <v>1.93</v>
@@ -3602,16 +3602,16 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Z20">
         <v>5.8</v>
       </c>
       <c r="AA20">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AB20">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AC20">
         <v>1.87</v>
@@ -3620,13 +3620,13 @@
         <v>1.84</v>
       </c>
       <c r="AE20">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AF20">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG20">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK20">
-        <v>2.71</v>
+        <v>2.83</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4058,22 +4058,22 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O23">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P23">
         <v>2.9</v>
       </c>
       <c r="Q23">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="R23">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="S23">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T23">
         <v>3.2</v>
@@ -4091,16 +4091,16 @@
         <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z23">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="AA23">
         <v>1.73</v>
       </c>
       <c r="AB23">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AC23">
         <v>2.7</v>
@@ -4115,7 +4115,7 @@
         <v>1.58</v>
       </c>
       <c r="AG23">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK23">
         <v>1.62</v>
@@ -4384,25 +4384,25 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="O25">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P25">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q25">
         <v>2.07</v>
       </c>
       <c r="R25">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="S25">
         <v>1.34</v>
       </c>
       <c r="T25">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U25">
         <v>2.6</v>
@@ -4414,34 +4414,34 @@
         <v>1.06</v>
       </c>
       <c r="X25">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z25">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA25">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AB25">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC25">
         <v>3.1</v>
       </c>
       <c r="AD25">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE25">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF25">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AG25">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK25">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4550,7 +4550,7 @@
         <v>3</v>
       </c>
       <c r="O26">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P26">
         <v>2.25</v>
@@ -4559,22 +4559,22 @@
         <v>3.45</v>
       </c>
       <c r="R26">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S26">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T26">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="U26">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="V26">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W26">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X26">
         <v>1.06</v>
@@ -4583,7 +4583,7 @@
         <v>1.28</v>
       </c>
       <c r="Z26">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA26">
         <v>2</v>
@@ -4592,16 +4592,16 @@
         <v>1.7</v>
       </c>
       <c r="AC26">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AD26">
         <v>1.25</v>
       </c>
       <c r="AE26">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF26">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AG26">
         <v>1.85</v>
@@ -4620,7 +4620,7 @@
         <v>1.54</v>
       </c>
       <c r="AK26">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="Q27">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T27">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="V27">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="W27">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y27">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z27">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA27">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AB27">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AC27">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AD27">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AE27">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF27">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG27">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK27">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="O31">
         <v>3</v>
@@ -5371,22 +5371,22 @@
         <v>3.8</v>
       </c>
       <c r="Q31">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="R31">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="S31">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="T31">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="U31">
         <v>3.42</v>
       </c>
       <c r="V31">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="W31">
         <v>1</v>
@@ -5401,25 +5401,25 @@
         <v>2.46</v>
       </c>
       <c r="AA31">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="AB31">
         <v>1.5</v>
       </c>
       <c r="AC31">
-        <v>5.02</v>
+        <v>5.09</v>
       </c>
       <c r="AD31">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AE31">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AF31">
         <v>2</v>
       </c>
       <c r="AG31">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK31">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5528,40 +5528,40 @@
         <v>2.05</v>
       </c>
       <c r="O32">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="P32">
-        <v>3.86</v>
+        <v>3.49</v>
       </c>
       <c r="Q32">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="R32">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="S32">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T32">
-        <v>2.47</v>
+        <v>2.69</v>
       </c>
       <c r="U32">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V32">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W32">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="Z32">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="AA32">
         <v>2.15</v>
@@ -5570,19 +5570,19 @@
         <v>1.63</v>
       </c>
       <c r="AC32">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="AD32">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AE32">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF32">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG32">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK32">
         <v>1.73</v>
@@ -5703,16 +5703,16 @@
         <v>2.01</v>
       </c>
       <c r="S33">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="T33">
         <v>2.8</v>
       </c>
       <c r="U33">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="V33">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
         <v>1.05</v>
@@ -5727,19 +5727,19 @@
         <v>2.97</v>
       </c>
       <c r="AA33">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB33">
         <v>1.7</v>
       </c>
       <c r="AC33">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="AD33">
         <v>1.23</v>
       </c>
       <c r="AE33">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF33">
         <v>1.86</v>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK33">
         <v>1.88</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="O2">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="P2">
-        <v>7.05</v>
+        <v>5.98</v>
       </c>
       <c r="Q2">
+        <v>1.88</v>
+      </c>
+      <c r="R2">
+        <v>2.21</v>
+      </c>
+      <c r="S2">
+        <v>1.37</v>
+      </c>
+      <c r="T2">
+        <v>2.71</v>
+      </c>
+      <c r="U2">
+        <v>2.75</v>
+      </c>
+      <c r="V2">
+        <v>1.4</v>
+      </c>
+      <c r="W2">
+        <v>1.08</v>
+      </c>
+      <c r="X2">
+        <v>1.01</v>
+      </c>
+      <c r="Y2">
+        <v>1.25</v>
+      </c>
+      <c r="Z2">
+        <v>3.28</v>
+      </c>
+      <c r="AA2">
+        <v>1.84</v>
+      </c>
+      <c r="AB2">
         <v>1.85</v>
       </c>
-      <c r="R2">
-        <v>2.4</v>
-      </c>
-      <c r="S2">
-        <v>1.32</v>
-      </c>
-      <c r="T2">
-        <v>2.92</v>
-      </c>
-      <c r="U2">
-        <v>2.55</v>
-      </c>
-      <c r="V2">
-        <v>1.49</v>
-      </c>
-      <c r="W2">
-        <v>1.11</v>
-      </c>
-      <c r="X2">
-        <v>1.02</v>
-      </c>
-      <c r="Y2">
-        <v>1.2</v>
-      </c>
-      <c r="Z2">
-        <v>3.85</v>
-      </c>
-      <c r="AA2">
-        <v>1.71</v>
-      </c>
-      <c r="AB2">
-        <v>2.1</v>
-      </c>
       <c r="AC2">
-        <v>2.79</v>
+        <v>2.97</v>
       </c>
       <c r="AD2">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AE2">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AF2">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="AG2">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK2">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -807,46 +807,46 @@
         <v>3.37</v>
       </c>
       <c r="Q3">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="R3">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="S3">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T3">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="U3">
         <v>3.2</v>
       </c>
       <c r="V3">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W3">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X3">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z3">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AA3">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="AB3">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC3">
-        <v>4.86</v>
+        <v>4.73</v>
       </c>
       <c r="AD3">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE3">
         <v>1.02</v>
@@ -855,7 +855,7 @@
         <v>1.95</v>
       </c>
       <c r="AG3">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK3">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O4">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P4">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="Q4">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="R4">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="S4">
         <v>1.35</v>
       </c>
       <c r="T4">
-        <v>2.98</v>
+        <v>2.79</v>
       </c>
       <c r="U4">
-        <v>2.67</v>
+        <v>2.73</v>
       </c>
       <c r="V4">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W4">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
         <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z4">
         <v>3.8</v>
       </c>
       <c r="AA4">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB4">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AC4">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AD4">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AE4">
         <v>1.07</v>
       </c>
       <c r="AF4">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AG4">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK4">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1133,55 +1133,55 @@
         <v>1.14</v>
       </c>
       <c r="Q5">
-        <v>7.4</v>
+        <v>6.38</v>
       </c>
       <c r="R5">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="S5">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="T5">
-        <v>3.28</v>
+        <v>4.5</v>
       </c>
       <c r="U5">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="V5">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="W5">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z5">
-        <v>4.95</v>
+        <v>5.8</v>
       </c>
       <c r="AA5">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AB5">
-        <v>2.46</v>
+        <v>2.83</v>
       </c>
       <c r="AC5">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="AD5">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="AE5">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF5">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AG5">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AK5">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="O7">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P7">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="Q7">
         <v>4</v>
@@ -1465,22 +1465,22 @@
         <v>2.25</v>
       </c>
       <c r="S7">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T7">
-        <v>2.97</v>
+        <v>2.86</v>
       </c>
       <c r="U7">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="V7">
         <v>1.43</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
         <v>1.21</v>
@@ -1489,10 +1489,10 @@
         <v>3.6</v>
       </c>
       <c r="AA7">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AB7">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AC7">
         <v>2.75</v>
@@ -1501,13 +1501,13 @@
         <v>1.3</v>
       </c>
       <c r="AE7">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF7">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG7">
-        <v>2.07</v>
+        <v>1.78</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK7">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="O9">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P9">
         <v>4.2</v>
       </c>
       <c r="Q9">
+        <v>2.2</v>
+      </c>
+      <c r="R9">
         <v>2.15</v>
       </c>
-      <c r="R9">
-        <v>2.22</v>
-      </c>
       <c r="S9">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T9">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="U9">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="V9">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W9">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="Z9">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AA9">
-        <v>1.71</v>
+        <v>2.02</v>
       </c>
       <c r="AB9">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AC9">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="AD9">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AE9">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF9">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AG9">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AK9">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2594,7 +2594,7 @@
         <v>2.75</v>
       </c>
       <c r="O14">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="P14">
         <v>2.4</v>
@@ -2606,13 +2606,13 @@
         <v>2.05</v>
       </c>
       <c r="S14">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="T14">
         <v>2.45</v>
       </c>
       <c r="U14">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="V14">
         <v>1.35</v>
@@ -2760,58 +2760,58 @@
         <v>3.21</v>
       </c>
       <c r="P15">
-        <v>2.21</v>
+        <v>2.37</v>
       </c>
       <c r="Q15">
         <v>3.4</v>
       </c>
       <c r="R15">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="S15">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T15">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="U15">
         <v>2.4</v>
       </c>
       <c r="V15">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W15">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z15">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AA15">
         <v>1.75</v>
       </c>
       <c r="AB15">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AC15">
         <v>2.8</v>
       </c>
       <c r="AD15">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE15">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF15">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG15">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="AK15">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,25 +2917,25 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="O16">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P16">
-        <v>4.2</v>
+        <v>4.55</v>
       </c>
       <c r="Q16">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R16">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="S16">
         <v>1.33</v>
       </c>
       <c r="T16">
-        <v>3.33</v>
+        <v>3.04</v>
       </c>
       <c r="U16">
         <v>2.56</v>
@@ -2947,7 +2947,7 @@
         <v>1.11</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
         <v>1.19</v>
@@ -2956,13 +2956,13 @@
         <v>3.8</v>
       </c>
       <c r="AA16">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB16">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="AC16">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="AD16">
         <v>1.42</v>
@@ -3089,7 +3089,7 @@
         <v>1.47</v>
       </c>
       <c r="Q17">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="R17">
         <v>2.43</v>
@@ -3098,10 +3098,10 @@
         <v>1.25</v>
       </c>
       <c r="T17">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="U17">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="V17">
         <v>1.48</v>
@@ -3113,31 +3113,31 @@
         <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z17">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AA17">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB17">
         <v>2.23</v>
       </c>
       <c r="AC17">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AD17">
         <v>1.44</v>
       </c>
       <c r="AE17">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF17">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG17">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3243,16 +3243,16 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="O18">
         <v>3.9</v>
       </c>
       <c r="P18">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="Q18">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="R18">
         <v>2.5</v>
@@ -3261,10 +3261,10 @@
         <v>1.2</v>
       </c>
       <c r="T18">
-        <v>3.8</v>
+        <v>3.66</v>
       </c>
       <c r="U18">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="V18">
         <v>1.6</v>
@@ -3273,31 +3273,31 @@
         <v>1.17</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z18">
-        <v>5.46</v>
+        <v>5.1</v>
       </c>
       <c r="AA18">
         <v>1.5</v>
       </c>
       <c r="AB18">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="AC18">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AD18">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AE18">
         <v>1.26</v>
       </c>
       <c r="AF18">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG18">
         <v>2.5</v>
@@ -3316,7 +3316,7 @@
         <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="O21">
         <v>3.29</v>
@@ -3750,13 +3750,13 @@
         <v>1.24</v>
       </c>
       <c r="T21">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="U21">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V21">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W21">
         <v>1.11</v>
@@ -3765,10 +3765,10 @@
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z21">
-        <v>4.9</v>
+        <v>5.48</v>
       </c>
       <c r="AA21">
         <v>1.57</v>
@@ -3777,19 +3777,19 @@
         <v>2.4</v>
       </c>
       <c r="AC21">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AD21">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE21">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF21">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG21">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4224,22 +4224,22 @@
         <v>1.67</v>
       </c>
       <c r="O24">
-        <v>3.9</v>
+        <v>4.25</v>
       </c>
       <c r="P24">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="Q24">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="R24">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="S24">
         <v>1.17</v>
       </c>
       <c r="T24">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="U24">
         <v>1.95</v>
@@ -4260,13 +4260,13 @@
         <v>5.9</v>
       </c>
       <c r="AA24">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AB24">
         <v>2.83</v>
       </c>
       <c r="AC24">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AD24">
         <v>1.63</v>
@@ -4278,7 +4278,7 @@
         <v>1.36</v>
       </c>
       <c r="AG24">
-        <v>2.38</v>
+        <v>2.77</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK24">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4719,55 +4719,55 @@
         <v>4.06</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC27">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AD27">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4879,7 +4879,7 @@
         <v>3.8</v>
       </c>
       <c r="P28">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5036,28 +5036,28 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="O29">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="P29">
-        <v>3.96</v>
+        <v>3.8</v>
       </c>
       <c r="Q29">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="R29">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="S29">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="T29">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="U29">
-        <v>1.99</v>
+        <v>2.07</v>
       </c>
       <c r="V29">
         <v>1.75</v>
@@ -5075,10 +5075,10 @@
         <v>6.5</v>
       </c>
       <c r="AA29">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AB29">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AC29">
         <v>2</v>
@@ -5087,13 +5087,13 @@
         <v>1.8</v>
       </c>
       <c r="AE29">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AF29">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AG29">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5199,19 +5199,19 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.77</v>
+        <v>3.12</v>
       </c>
       <c r="O30">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P30">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q30">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="R30">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="S30">
         <v>1.36</v>
@@ -5857,22 +5857,22 @@
         <v>3.3</v>
       </c>
       <c r="P34">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="Q34">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="R34">
         <v>2.2</v>
       </c>
       <c r="S34">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="U34">
-        <v>2.74</v>
+        <v>2.59</v>
       </c>
       <c r="V34">
         <v>1.42</v>
@@ -5902,7 +5902,7 @@
         <v>1.28</v>
       </c>
       <c r="AE34">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF34">
         <v>1.73</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AK34">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Maringá</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="O35">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P35">
-        <v>2.23</v>
+        <v>4.17</v>
       </c>
       <c r="Q35">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="R35">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="S35">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T35">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U35">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="V35">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W35">
         <v>1.05</v>
       </c>
       <c r="X35">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y35">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z35">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AA35">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB35">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC35">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AD35">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE35">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF35">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AG35">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.53</v>
+        <v>1.14</v>
       </c>
       <c r="AK35">
-        <v>1.33</v>
+        <v>1.89</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Maringá</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.76</v>
+        <v>3</v>
       </c>
       <c r="O36">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="P36">
-        <v>4.17</v>
+        <v>2.25</v>
       </c>
       <c r="Q36">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="R36">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="S36">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="T36">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="U36">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="V36">
+        <v>1.31</v>
+      </c>
+      <c r="W36">
+        <v>1.04</v>
+      </c>
+      <c r="X36">
+        <v>1.05</v>
+      </c>
+      <c r="Y36">
         <v>1.34</v>
-      </c>
-      <c r="W36">
-        <v>1.05</v>
-      </c>
-      <c r="X36">
-        <v>1.02</v>
-      </c>
-      <c r="Y36">
-        <v>1.29</v>
       </c>
       <c r="Z36">
         <v>3.04</v>
       </c>
       <c r="AA36">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AB36">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AC36">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="AD36">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE36">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF36">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AG36">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="AK36">
-        <v>1.95</v>
+        <v>1.32</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,16 +6340,16 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O37">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P37">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="Q37">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="R37">
         <v>1.96</v>
@@ -6361,10 +6361,10 @@
         <v>2.65</v>
       </c>
       <c r="U37">
-        <v>2.86</v>
+        <v>2.99</v>
       </c>
       <c r="V37">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W37">
         <v>1.05</v>
@@ -6397,7 +6397,7 @@
         <v>1.8</v>
       </c>
       <c r="AG37">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6509,19 +6509,19 @@
         <v>3.18</v>
       </c>
       <c r="P38">
-        <v>6.15</v>
+        <v>6.3</v>
       </c>
       <c r="Q38">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="R38">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="S38">
         <v>1.55</v>
       </c>
       <c r="T38">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="U38">
         <v>3.58</v>
@@ -6539,7 +6539,7 @@
         <v>1.51</v>
       </c>
       <c r="Z38">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="AA38">
         <v>2.6</v>
@@ -6548,7 +6548,7 @@
         <v>1.49</v>
       </c>
       <c r="AC38">
-        <v>5.11</v>
+        <v>5.17</v>
       </c>
       <c r="AD38">
         <v>1.1</v>
@@ -6557,7 +6557,7 @@
         <v>1.01</v>
       </c>
       <c r="AF38">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AG38">
         <v>1.48</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="AK38">
         <v>2.04</v>
@@ -6666,46 +6666,46 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="O39">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="P39">
-        <v>2.77</v>
+        <v>3.15</v>
       </c>
       <c r="Q39">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="R39">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="S39">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="T39">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="U39">
         <v>3.2</v>
       </c>
       <c r="V39">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W39">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X39">
         <v>1.05</v>
       </c>
       <c r="Y39">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Z39">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AA39">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="AB39">
         <v>1.5</v>
@@ -6714,7 +6714,7 @@
         <v>4.89</v>
       </c>
       <c r="AD39">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AE39">
         <v>1.01</v>
@@ -6723,7 +6723,7 @@
         <v>1.95</v>
       </c>
       <c r="AG39">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK39">
         <v>1.54</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="N5">
-        <v>12.2</v>
+        <v>8</v>
       </c>
       <c r="O5">
-        <v>6.65</v>
+        <v>5.75</v>
       </c>
       <c r="P5">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Q5">
-        <v>6.38</v>
+        <v>8.15</v>
       </c>
       <c r="R5">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="S5">
         <v>1.19</v>
@@ -1145,10 +1145,10 @@
         <v>4.5</v>
       </c>
       <c r="U5">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="V5">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="W5">
         <v>1.18</v>
@@ -1160,7 +1160,7 @@
         <v>1.07</v>
       </c>
       <c r="Z5">
-        <v>5.8</v>
+        <v>5.85</v>
       </c>
       <c r="AA5">
         <v>1.33</v>
@@ -1169,16 +1169,16 @@
         <v>2.83</v>
       </c>
       <c r="AC5">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="AD5">
         <v>1.81</v>
       </c>
       <c r="AE5">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF5">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG5">
         <v>1.85</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="O9">
         <v>3.4</v>
@@ -1785,43 +1785,43 @@
         <v>4.2</v>
       </c>
       <c r="Q9">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="R9">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="S9">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T9">
         <v>2.88</v>
       </c>
       <c r="U9">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V9">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y9">
         <v>1.28</v>
       </c>
       <c r="Z9">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AA9">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="AB9">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AC9">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AD9">
         <v>1.24</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="O10">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="P10">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="Q10">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="R10">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="S10">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T10">
         <v>3</v>
       </c>
       <c r="U10">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="V10">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W10">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
         <v>1.25</v>
       </c>
       <c r="Z10">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA10">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AB10">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC10">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="AD10">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE10">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF10">
         <v>1.67</v>
       </c>
       <c r="AG10">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AK10">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.12</v>
+        <v>2.9</v>
       </c>
       <c r="O13">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="P13">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="Q13">
-        <v>3.9</v>
+        <v>3.46</v>
       </c>
       <c r="R13">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="S13">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="T13">
-        <v>2.33</v>
+        <v>2.17</v>
       </c>
       <c r="U13">
-        <v>3.44</v>
+        <v>3.58</v>
       </c>
       <c r="V13">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W13">
         <v>1.02</v>
       </c>
       <c r="X13">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y13">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="Z13">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="AA13">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AB13">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AC13">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="AD13">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE13">
         <v>1.01</v>
       </c>
       <c r="AF13">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AG13">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AK13">
         <v>1.36</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="O32">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P32">
-        <v>3.49</v>
+        <v>3.86</v>
       </c>
       <c r="Q32">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="R32">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="S32">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="T32">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="U32">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="V32">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W32">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y32">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Z32">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="AA32">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AB32">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AC32">
-        <v>3.9</v>
+        <v>3.78</v>
       </c>
       <c r="AD32">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE32">
         <v>1.05</v>
       </c>
       <c r="AF32">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG32">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK32">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="O33">
+        <v>3.25</v>
+      </c>
+      <c r="P33">
+        <v>3.49</v>
+      </c>
+      <c r="Q33">
+        <v>2.7</v>
+      </c>
+      <c r="R33">
+        <v>1.95</v>
+      </c>
+      <c r="S33">
+        <v>1.45</v>
+      </c>
+      <c r="T33">
+        <v>2.69</v>
+      </c>
+      <c r="U33">
         <v>3.2</v>
       </c>
-      <c r="P33">
-        <v>3.86</v>
-      </c>
-      <c r="Q33">
-        <v>2.48</v>
-      </c>
-      <c r="R33">
-        <v>2.01</v>
-      </c>
-      <c r="S33">
-        <v>1.43</v>
-      </c>
-      <c r="T33">
-        <v>2.8</v>
-      </c>
-      <c r="U33">
-        <v>3.09</v>
-      </c>
       <c r="V33">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W33">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X33">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y33">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="Z33">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="AA33">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AB33">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AC33">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="AD33">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE33">
         <v>1.05</v>
       </c>
       <c r="AF33">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG33">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK33">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AL33">
         <v>0</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="O15">
-        <v>3.21</v>
+        <v>3.38</v>
       </c>
       <c r="P15">
-        <v>2.37</v>
+        <v>2.21</v>
       </c>
       <c r="Q15">
         <v>3.4</v>
       </c>
       <c r="R15">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="S15">
         <v>1.29</v>
@@ -2775,43 +2775,43 @@
         <v>3.1</v>
       </c>
       <c r="U15">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="V15">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W15">
         <v>1.08</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z15">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA15">
         <v>1.75</v>
       </c>
       <c r="AB15">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AC15">
         <v>2.8</v>
       </c>
       <c r="AD15">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AE15">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF15">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG15">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AK15">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3735,25 +3735,25 @@
         <v>2.43</v>
       </c>
       <c r="O21">
-        <v>3.29</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="Q21">
         <v>3</v>
       </c>
       <c r="R21">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="S21">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T21">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="U21">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="V21">
         <v>1.58</v>
@@ -3768,19 +3768,19 @@
         <v>1.15</v>
       </c>
       <c r="Z21">
-        <v>5.48</v>
+        <v>5.43</v>
       </c>
       <c r="AA21">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB21">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AC21">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AD21">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AE21">
         <v>1.2</v>
@@ -3805,7 +3805,7 @@
         <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL21">
         <v>0</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="O2">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="P2">
-        <v>5.98</v>
+        <v>8.6</v>
       </c>
       <c r="Q2">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="R2">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="S2">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T2">
-        <v>2.71</v>
+        <v>3.2</v>
       </c>
       <c r="U2">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="V2">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W2">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y2">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z2">
-        <v>3.28</v>
+        <v>4.1</v>
       </c>
       <c r="AA2">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AB2">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC2">
-        <v>2.97</v>
+        <v>2.79</v>
       </c>
       <c r="AD2">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE2">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF2">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="AG2">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AK2">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,58 +798,58 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="O3">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="P3">
-        <v>3.37</v>
+        <v>3.5</v>
       </c>
       <c r="Q3">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="R3">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="S3">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="T3">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="U3">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="V3">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W3">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y3">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z3">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AA3">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AB3">
         <v>1.6</v>
       </c>
       <c r="AC3">
-        <v>4.73</v>
+        <v>4.2</v>
       </c>
       <c r="AD3">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE3">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF3">
         <v>1.95</v>
@@ -961,80 +961,80 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="O4">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q4">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="R4">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S4">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="T4">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="U4">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="V4">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W4">
+        <v>1.1</v>
+      </c>
+      <c r="X4">
+        <v>1.04</v>
+      </c>
+      <c r="Y4">
+        <v>1.23</v>
+      </c>
+      <c r="Z4">
+        <v>3.5</v>
+      </c>
+      <c r="AA4">
+        <v>1.79</v>
+      </c>
+      <c r="AB4">
+        <v>1.88</v>
+      </c>
+      <c r="AC4">
+        <v>3.24</v>
+      </c>
+      <c r="AD4">
+        <v>1.33</v>
+      </c>
+      <c r="AE4">
         <v>1.08</v>
       </c>
-      <c r="X4">
-        <v>1.01</v>
-      </c>
-      <c r="Y4">
+      <c r="AF4">
+        <v>1.67</v>
+      </c>
+      <c r="AG4">
+        <v>2.02</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4">
         <v>1.26</v>
       </c>
-      <c r="Z4">
-        <v>3.8</v>
-      </c>
-      <c r="AA4">
-        <v>1.8</v>
-      </c>
-      <c r="AB4">
-        <v>1.86</v>
-      </c>
-      <c r="AC4">
-        <v>3.08</v>
-      </c>
-      <c r="AD4">
-        <v>1.28</v>
-      </c>
-      <c r="AE4">
-        <v>1.07</v>
-      </c>
-      <c r="AF4">
-        <v>1.74</v>
-      </c>
-      <c r="AG4">
-        <v>1.94</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4">
-        <v>1.18</v>
-      </c>
       <c r="AK4">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,31 +1124,31 @@
         </is>
       </c>
       <c r="N5">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O5">
-        <v>5.75</v>
+        <v>6.1</v>
       </c>
       <c r="P5">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Q5">
-        <v>8.15</v>
+        <v>6.47</v>
       </c>
       <c r="R5">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="S5">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="T5">
         <v>4.5</v>
       </c>
       <c r="U5">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="V5">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="W5">
         <v>1.18</v>
@@ -1160,29 +1160,29 @@
         <v>1.07</v>
       </c>
       <c r="Z5">
-        <v>5.85</v>
+        <v>5.8</v>
       </c>
       <c r="AA5">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB5">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AC5">
+        <v>1.86</v>
+      </c>
+      <c r="AD5">
+        <v>1.83</v>
+      </c>
+      <c r="AE5">
+        <v>1.26</v>
+      </c>
+      <c r="AF5">
+        <v>1.7</v>
+      </c>
+      <c r="AG5">
         <v>1.97</v>
       </c>
-      <c r="AD5">
-        <v>1.81</v>
-      </c>
-      <c r="AE5">
-        <v>1.33</v>
-      </c>
-      <c r="AF5">
-        <v>1.73</v>
-      </c>
-      <c r="AG5">
-        <v>1.85</v>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK5">
         <v>1.03</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q8">
-        <v>4.38</v>
+        <v>4.48</v>
       </c>
       <c r="R8">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="S8">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T8">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="U8">
         <v>2.5</v>
       </c>
       <c r="V8">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W8">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X8">
         <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z8">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AA8">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AB8">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC8">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AD8">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE8">
         <v>1.12</v>
       </c>
       <c r="AF8">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG8">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK8">
         <v>1.2</v>
@@ -1776,65 +1776,65 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="O9">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P9">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="Q9">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="R9">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="S9">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T9">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="U9">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="V9">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="W9">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X9">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
         <v>1.28</v>
       </c>
       <c r="Z9">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AA9">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AB9">
+        <v>1.76</v>
+      </c>
+      <c r="AC9">
+        <v>3.5</v>
+      </c>
+      <c r="AD9">
+        <v>1.25</v>
+      </c>
+      <c r="AE9">
+        <v>1.08</v>
+      </c>
+      <c r="AF9">
+        <v>1.81</v>
+      </c>
+      <c r="AG9">
         <v>1.85</v>
       </c>
-      <c r="AC9">
-        <v>3.6</v>
-      </c>
-      <c r="AD9">
-        <v>1.24</v>
-      </c>
-      <c r="AE9">
-        <v>1.05</v>
-      </c>
-      <c r="AF9">
-        <v>1.85</v>
-      </c>
-      <c r="AG9">
-        <v>1.83</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK9">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="O10">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="P10">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="Q10">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="R10">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="S10">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="T10">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="U10">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="V10">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W10">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z10">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="AA10">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB10">
         <v>1.93</v>
       </c>
       <c r="AC10">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AD10">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE10">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF10">
         <v>1.67</v>
       </c>
       <c r="AG10">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.24</v>
       </c>
       <c r="AK10">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,25 +2102,25 @@
         </is>
       </c>
       <c r="N11">
-        <v>7.7</v>
+        <v>6.3</v>
       </c>
       <c r="O11">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="P11">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="Q11">
-        <v>8.140000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="R11">
         <v>2.45</v>
       </c>
       <c r="S11">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T11">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="U11">
         <v>2.38</v>
@@ -2129,16 +2129,16 @@
         <v>1.48</v>
       </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
         <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z11">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA11">
         <v>1.65</v>
@@ -2147,19 +2147,19 @@
         <v>2.1</v>
       </c>
       <c r="AC11">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="AD11">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE11">
         <v>1.15</v>
       </c>
       <c r="AF11">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AG11">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK11">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,31 +2265,31 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="O12">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P12">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q12">
         <v>2.58</v>
       </c>
       <c r="R12">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="S12">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T12">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="U12">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="V12">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W12">
         <v>1.1</v>
@@ -2298,28 +2298,28 @@
         <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z12">
         <v>4.33</v>
       </c>
       <c r="AA12">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB12">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AC12">
         <v>2.88</v>
       </c>
       <c r="AD12">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE12">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF12">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG12">
         <v>2.23</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AK12">
         <v>1.63</v>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.9</v>
+        <v>3.26</v>
       </c>
       <c r="O13">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="P13">
         <v>2.31</v>
@@ -2440,13 +2440,13 @@
         <v>3.46</v>
       </c>
       <c r="R13">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="S13">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="T13">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="U13">
         <v>3.58</v>
@@ -2461,13 +2461,13 @@
         <v>1.07</v>
       </c>
       <c r="Y13">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Z13">
-        <v>2.66</v>
+        <v>2.43</v>
       </c>
       <c r="AA13">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="AB13">
         <v>1.49</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AK13">
         <v>1.36</v>
@@ -2594,31 +2594,31 @@
         <v>2.75</v>
       </c>
       <c r="O14">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="P14">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q14">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R14">
         <v>2.05</v>
       </c>
       <c r="S14">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T14">
-        <v>2.45</v>
+        <v>2.69</v>
       </c>
       <c r="U14">
         <v>3.2</v>
       </c>
       <c r="V14">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W14">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X14">
         <v>1.03</v>
@@ -2633,22 +2633,22 @@
         <v>2.2</v>
       </c>
       <c r="AB14">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AC14">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AD14">
         <v>1.18</v>
       </c>
       <c r="AE14">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF14">
         <v>1.9</v>
       </c>
       <c r="AG14">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2917,28 +2917,28 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="O16">
         <v>4</v>
       </c>
       <c r="P16">
-        <v>4.55</v>
+        <v>5.4</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
       </c>
       <c r="R16">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="S16">
         <v>1.33</v>
       </c>
       <c r="T16">
-        <v>3.04</v>
+        <v>3.33</v>
       </c>
       <c r="U16">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="V16">
         <v>1.44</v>
@@ -2950,31 +2950,31 @@
         <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z16">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="AA16">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AB16">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="AC16">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="AD16">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE16">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF16">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG16">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK16">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3243,16 +3243,16 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="O18">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="P18">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q18">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="R18">
         <v>2.5</v>
@@ -3261,46 +3261,46 @@
         <v>1.2</v>
       </c>
       <c r="T18">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="U18">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="V18">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="W18">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X18">
         <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z18">
-        <v>5.1</v>
+        <v>6.17</v>
       </c>
       <c r="AA18">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB18">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="AC18">
         <v>2.08</v>
       </c>
       <c r="AD18">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="AE18">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AF18">
         <v>1.4</v>
       </c>
       <c r="AG18">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK18">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="O19">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="P19">
-        <v>3.73</v>
+        <v>3.92</v>
       </c>
       <c r="Q19">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R19">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="S19">
         <v>1.25</v>
       </c>
       <c r="T19">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="U19">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V19">
+        <v>1.53</v>
+      </c>
+      <c r="W19">
+        <v>1.12</v>
+      </c>
+      <c r="X19">
+        <v>1.04</v>
+      </c>
+      <c r="Y19">
+        <v>1.2</v>
+      </c>
+      <c r="Z19">
+        <v>4.5</v>
+      </c>
+      <c r="AA19">
+        <v>1.59</v>
+      </c>
+      <c r="AB19">
+        <v>2.31</v>
+      </c>
+      <c r="AC19">
+        <v>2.45</v>
+      </c>
+      <c r="AD19">
+        <v>1.47</v>
+      </c>
+      <c r="AE19">
+        <v>1.18</v>
+      </c>
+      <c r="AF19">
         <v>1.55</v>
       </c>
-      <c r="W19">
-        <v>1.08</v>
-      </c>
-      <c r="X19">
-        <v>1.03</v>
-      </c>
-      <c r="Y19">
-        <v>1.15</v>
-      </c>
-      <c r="Z19">
-        <v>4.4</v>
-      </c>
-      <c r="AA19">
-        <v>1.64</v>
-      </c>
-      <c r="AB19">
-        <v>2.21</v>
-      </c>
-      <c r="AC19">
-        <v>2.63</v>
-      </c>
-      <c r="AD19">
-        <v>1.44</v>
-      </c>
-      <c r="AE19">
-        <v>1.17</v>
-      </c>
-      <c r="AF19">
-        <v>1.54</v>
-      </c>
       <c r="AG19">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AK19">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3572,16 +3572,16 @@
         <v>1.3</v>
       </c>
       <c r="O20">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="P20">
-        <v>5.25</v>
+        <v>5.15</v>
       </c>
       <c r="Q20">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="R20">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="S20">
         <v>1.16</v>
@@ -3593,7 +3593,7 @@
         <v>1.93</v>
       </c>
       <c r="V20">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="W20">
         <v>1.21</v>
@@ -3602,31 +3602,31 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Z20">
         <v>5.8</v>
       </c>
       <c r="AA20">
+        <v>1.33</v>
+      </c>
+      <c r="AB20">
+        <v>3.4</v>
+      </c>
+      <c r="AC20">
+        <v>1.84</v>
+      </c>
+      <c r="AD20">
+        <v>1.92</v>
+      </c>
+      <c r="AE20">
         <v>1.36</v>
       </c>
-      <c r="AB20">
-        <v>3.1</v>
-      </c>
-      <c r="AC20">
-        <v>1.87</v>
-      </c>
-      <c r="AD20">
-        <v>1.84</v>
-      </c>
-      <c r="AE20">
-        <v>1.35</v>
-      </c>
       <c r="AF20">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG20">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AK20">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4384,25 +4384,25 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="O25">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P25">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="Q25">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="R25">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="S25">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T25">
-        <v>3.12</v>
+        <v>2.95</v>
       </c>
       <c r="U25">
         <v>2.6</v>
@@ -4414,34 +4414,34 @@
         <v>1.06</v>
       </c>
       <c r="X25">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
         <v>1.25</v>
       </c>
       <c r="Z25">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AA25">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB25">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC25">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AD25">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE25">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF25">
         <v>1.78</v>
       </c>
       <c r="AG25">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>1.23</v>
       </c>
       <c r="AK25">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="O32">
+        <v>3.25</v>
+      </c>
+      <c r="P32">
+        <v>3.49</v>
+      </c>
+      <c r="Q32">
+        <v>2.7</v>
+      </c>
+      <c r="R32">
+        <v>1.95</v>
+      </c>
+      <c r="S32">
+        <v>1.45</v>
+      </c>
+      <c r="T32">
+        <v>2.69</v>
+      </c>
+      <c r="U32">
         <v>3.2</v>
       </c>
-      <c r="P32">
-        <v>3.86</v>
-      </c>
-      <c r="Q32">
-        <v>2.48</v>
-      </c>
-      <c r="R32">
-        <v>2.01</v>
-      </c>
-      <c r="S32">
-        <v>1.43</v>
-      </c>
-      <c r="T32">
-        <v>2.8</v>
-      </c>
-      <c r="U32">
-        <v>3.09</v>
-      </c>
       <c r="V32">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W32">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X32">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y32">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="Z32">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="AA32">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AB32">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AC32">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="AD32">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE32">
         <v>1.05</v>
       </c>
       <c r="AF32">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG32">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK32">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="O33">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P33">
-        <v>3.49</v>
+        <v>3.86</v>
       </c>
       <c r="Q33">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="R33">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="S33">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="T33">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="U33">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="V33">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W33">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X33">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y33">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="Z33">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="AA33">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AB33">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AC33">
-        <v>3.9</v>
+        <v>3.78</v>
       </c>
       <c r="AD33">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE33">
         <v>1.05</v>
       </c>
       <c r="AF33">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG33">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK33">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AL33">
         <v>0</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -612,26 +612,26 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
@@ -696,12 +696,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["31", "90+3"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20"]</t>
         </is>
       </c>
       <c r="AJ2">
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -787,14 +787,14 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -859,7 +859,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["53", "89"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -950,14 +950,14 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["57", "66", "90+3"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+6"]</t>
         </is>
       </c>
       <c r="AJ4">
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1104,13 +1104,13 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8"]</t>
         </is>
       </c>
       <c r="AJ5">
@@ -1203,28 +1203,28 @@
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1264,36 +1264,36 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="O6">
-        <v>3.4</v>
+        <v>3.72</v>
       </c>
       <c r="P6">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q6">
         <v>2.3</v>
@@ -1302,19 +1302,19 @@
         <v>2.2</v>
       </c>
       <c r="S6">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T6">
-        <v>3.01</v>
+        <v>2.7</v>
       </c>
       <c r="U6">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="V6">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
         <v>1.01</v>
@@ -1326,68 +1326,68 @@
         <v>3.2</v>
       </c>
       <c r="AA6">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AB6">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AC6">
-        <v>3.36</v>
+        <v>3.08</v>
       </c>
       <c r="AD6">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE6">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF6">
         <v>1.75</v>
       </c>
       <c r="AG6">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
+          <t>["26", "39", "43", "49", "86"]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ6">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AK6">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1427,100 +1427,100 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="O7">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P7">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="Q7">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="R7">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S7">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T7">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="U7">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="V7">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W7">
         <v>1.1</v>
       </c>
       <c r="X7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z7">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AA7">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AB7">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AC7">
         <v>2.75</v>
       </c>
       <c r="AD7">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE7">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF7">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AG7">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "51"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19", "74", "90+3"]</t>
         </is>
       </c>
       <c r="AJ7">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK7">
         <v>1.15</v>
@@ -1529,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1590,51 +1590,51 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O8">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P8">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q8">
-        <v>4.48</v>
+        <v>4.4</v>
       </c>
       <c r="R8">
-        <v>2.19</v>
+        <v>2.36</v>
       </c>
       <c r="S8">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T8">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="U8">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="V8">
         <v>1.42</v>
@@ -1646,19 +1646,19 @@
         <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z8">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AA8">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AB8">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC8">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="AD8">
         <v>1.36</v>
@@ -1667,23 +1667,23 @@
         <v>1.12</v>
       </c>
       <c r="AF8">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG8">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19", "59"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["5", "21", "65", "72"]</t>
         </is>
       </c>
       <c r="AJ8">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK8">
         <v>1.2</v>
@@ -1692,28 +1692,28 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1753,130 +1753,130 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="O9">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="P9">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="Q9">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="R9">
-        <v>2.05</v>
+        <v>2.29</v>
       </c>
       <c r="S9">
         <v>1.36</v>
       </c>
       <c r="T9">
+        <v>2.88</v>
+      </c>
+      <c r="U9">
         <v>2.67</v>
       </c>
-      <c r="U9">
-        <v>2.83</v>
-      </c>
       <c r="V9">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W9">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y9">
+        <v>1.24</v>
+      </c>
+      <c r="Z9">
+        <v>3.6</v>
+      </c>
+      <c r="AA9">
+        <v>1.89</v>
+      </c>
+      <c r="AB9">
+        <v>1.93</v>
+      </c>
+      <c r="AC9">
+        <v>3.05</v>
+      </c>
+      <c r="AD9">
         <v>1.28</v>
-      </c>
-      <c r="Z9">
-        <v>3.14</v>
-      </c>
-      <c r="AA9">
-        <v>1.93</v>
-      </c>
-      <c r="AB9">
-        <v>1.76</v>
-      </c>
-      <c r="AC9">
-        <v>3.5</v>
-      </c>
-      <c r="AD9">
-        <v>1.25</v>
       </c>
       <c r="AE9">
         <v>1.08</v>
       </c>
       <c r="AF9">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AG9">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["65", "90"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["13", "44"]</t>
         </is>
       </c>
       <c r="AJ9">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK9">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1916,26 +1916,26 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["44", "72"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -2018,28 +2018,28 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2082,23 +2082,23 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["14", "47"]</t>
         </is>
       </c>
       <c r="AJ11">
@@ -2181,28 +2181,28 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="O12">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P12">
         <v>3.2</v>
@@ -2277,31 +2277,31 @@
         <v>2.58</v>
       </c>
       <c r="R12">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="S12">
         <v>1.3</v>
       </c>
       <c r="T12">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="U12">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="V12">
         <v>1.51</v>
       </c>
       <c r="W12">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
         <v>1</v>
       </c>
       <c r="Y12">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z12">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA12">
         <v>1.66</v>
@@ -2310,10 +2310,10 @@
         <v>2.15</v>
       </c>
       <c r="AC12">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AD12">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE12">
         <v>1.12</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="O13">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="P13">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="Q13">
         <v>3.46</v>
@@ -2449,13 +2449,13 @@
         <v>2.2</v>
       </c>
       <c r="U13">
-        <v>3.58</v>
+        <v>3.52</v>
       </c>
       <c r="V13">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X13">
         <v>1.07</v>
@@ -2464,13 +2464,13 @@
         <v>1.49</v>
       </c>
       <c r="Z13">
-        <v>2.43</v>
+        <v>2.64</v>
       </c>
       <c r="AA13">
         <v>2.59</v>
       </c>
       <c r="AB13">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AC13">
         <v>4.65</v>
@@ -2479,13 +2479,13 @@
         <v>1.12</v>
       </c>
       <c r="AE13">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF13">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AG13">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>1.45</v>
       </c>
       <c r="AK13">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2600,16 +2600,16 @@
         <v>2.25</v>
       </c>
       <c r="Q14">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="R14">
         <v>2.05</v>
       </c>
       <c r="S14">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T14">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="U14">
         <v>3.2</v>
@@ -2618,7 +2618,7 @@
         <v>1.33</v>
       </c>
       <c r="W14">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
         <v>1.03</v>
@@ -2630,16 +2630,16 @@
         <v>2.74</v>
       </c>
       <c r="AA14">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB14">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AC14">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AD14">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE14">
         <v>1.02</v>
@@ -2754,16 +2754,16 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="O15">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P15">
-        <v>2.21</v>
+        <v>2.37</v>
       </c>
       <c r="Q15">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R15">
         <v>2.36</v>
@@ -2772,13 +2772,13 @@
         <v>1.29</v>
       </c>
       <c r="T15">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="U15">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="V15">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W15">
         <v>1.08</v>
@@ -2787,25 +2787,25 @@
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z15">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AA15">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB15">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC15">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="AD15">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AE15">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF15">
         <v>1.53</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AK15">
         <v>1.4</v>
@@ -2917,16 +2917,16 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="O16">
         <v>4</v>
       </c>
       <c r="P16">
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="Q16">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R16">
         <v>2.16</v>
@@ -2935,62 +2935,62 @@
         <v>1.33</v>
       </c>
       <c r="T16">
-        <v>3.33</v>
+        <v>3.35</v>
       </c>
       <c r="U16">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="V16">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W16">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z16">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="AA16">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AB16">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AC16">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AD16">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE16">
+        <v>1.14</v>
+      </c>
+      <c r="AF16">
+        <v>1.67</v>
+      </c>
+      <c r="AG16">
+        <v>2.05</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
         <v>1.12</v>
       </c>
-      <c r="AF16">
-        <v>1.7</v>
-      </c>
-      <c r="AG16">
-        <v>2</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.22</v>
-      </c>
       <c r="AK16">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>5.96</v>
+        <v>5.35</v>
       </c>
       <c r="O17">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P17">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="Q17">
-        <v>4.8</v>
+        <v>5.75</v>
       </c>
       <c r="R17">
-        <v>2.43</v>
+        <v>2.34</v>
       </c>
       <c r="S17">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T17">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="U17">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="V17">
         <v>1.48</v>
       </c>
       <c r="W17">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X17">
         <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z17">
-        <v>4.5</v>
+        <v>3.96</v>
       </c>
       <c r="AA17">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AB17">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="AC17">
         <v>2.5</v>
       </c>
       <c r="AD17">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE17">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF17">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG17">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3243,22 +3243,22 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="O18">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P18">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Q18">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="R18">
         <v>2.5</v>
       </c>
       <c r="S18">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T18">
         <v>3.75</v>
@@ -3270,37 +3270,37 @@
         <v>1.73</v>
       </c>
       <c r="W18">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z18">
-        <v>6.17</v>
+        <v>6.5</v>
       </c>
       <c r="AA18">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AB18">
         <v>2.7</v>
       </c>
       <c r="AC18">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AD18">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AE18">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF18">
         <v>1.4</v>
       </c>
       <c r="AG18">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK18">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3383,16 +3383,16 @@
         </is>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10"]</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+1"]</t>
         </is>
       </c>
       <c r="AJ19">
@@ -3485,28 +3485,28 @@
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3546,26 +3546,26 @@
         </is>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["19", "28", "45+1", "60", "70", "78"]</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
@@ -3648,28 +3648,28 @@
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3732,19 +3732,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="O21">
-        <v>3.4</v>
+        <v>3.29</v>
       </c>
       <c r="P21">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="Q21">
         <v>3</v>
       </c>
       <c r="R21">
-        <v>2.48</v>
+        <v>2.29</v>
       </c>
       <c r="S21">
         <v>1.25</v>
@@ -3753,43 +3753,43 @@
         <v>3.6</v>
       </c>
       <c r="U21">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="V21">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="W21">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z21">
-        <v>5.43</v>
+        <v>5.25</v>
       </c>
       <c r="AA21">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AB21">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="AC21">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AD21">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AE21">
         <v>1.2</v>
       </c>
       <c r="AF21">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG21">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK21">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="O23">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P23">
-        <v>2.9</v>
+        <v>3.12</v>
       </c>
       <c r="Q23">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="R23">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="S23">
         <v>1.32</v>
       </c>
       <c r="T23">
-        <v>3.2</v>
+        <v>3.31</v>
       </c>
       <c r="U23">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="V23">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="W23">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z23">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AA23">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AB23">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="AC23">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="AD23">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AE23">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF23">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AG23">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK23">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="O24">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="P24">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="Q24">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="R24">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="S24">
         <v>1.17</v>
       </c>
       <c r="T24">
-        <v>4.5</v>
+        <v>3.92</v>
       </c>
       <c r="U24">
         <v>1.95</v>
       </c>
       <c r="V24">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="W24">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X24">
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z24">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="AA24">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AB24">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="AC24">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AD24">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AE24">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AF24">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AG24">
-        <v>2.77</v>
+        <v>2.58</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK24">
         <v>2.03</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="N26">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="O26">
         <v>3.1</v>
@@ -4556,52 +4556,52 @@
         <v>2.25</v>
       </c>
       <c r="Q26">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="R26">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="S26">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T26">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="U26">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="V26">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W26">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X26">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z26">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA26">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AB26">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC26">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AD26">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE26">
         <v>1.1</v>
       </c>
       <c r="AF26">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AG26">
         <v>1.85</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AK26">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="O27">
-        <v>3.98</v>
+        <v>3.75</v>
       </c>
       <c r="P27">
-        <v>4.06</v>
+        <v>4.1</v>
       </c>
       <c r="Q27">
         <v>2.2</v>
       </c>
       <c r="R27">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="S27">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T27">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U27">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V27">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="W27">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X27">
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z27">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA27">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AB27">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="AC27">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AD27">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AE27">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF27">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AG27">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK27">
-        <v>1.99</v>
+        <v>1.86</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="O28">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P28">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA28">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AB28">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="O29">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="P29">
-        <v>3.8</v>
+        <v>3.92</v>
       </c>
       <c r="Q29">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="R29">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="S29">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T29">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="U29">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="V29">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="W29">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z29">
-        <v>6.5</v>
+        <v>6.29</v>
       </c>
       <c r="AA29">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AB29">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="AC29">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AD29">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AE29">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AF29">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AG29">
-        <v>2.73</v>
+        <v>2.38</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK29">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,16 +5199,16 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.12</v>
+        <v>2.91</v>
       </c>
       <c r="O30">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P30">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="Q30">
-        <v>4.55</v>
+        <v>3.8</v>
       </c>
       <c r="R30">
         <v>2.03</v>
@@ -5217,25 +5217,25 @@
         <v>1.36</v>
       </c>
       <c r="T30">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="U30">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="V30">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W30">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z30">
-        <v>3</v>
+        <v>3.23</v>
       </c>
       <c r="AA30">
         <v>2.05</v>
@@ -5244,19 +5244,19 @@
         <v>1.75</v>
       </c>
       <c r="AC30">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="AD30">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE30">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AF30">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AG30">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK30">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="O31">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="P31">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Q31">
-        <v>2.51</v>
+        <v>2.81</v>
       </c>
       <c r="R31">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="S31">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="T31">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="U31">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="V31">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="W31">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X31">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y31">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="Z31">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="AA31">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AB31">
         <v>1.5</v>
       </c>
       <c r="AC31">
-        <v>5.09</v>
+        <v>4.75</v>
       </c>
       <c r="AD31">
         <v>1.12</v>
       </c>
       <c r="AE31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF31">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG31">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AK31">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="O32">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P32">
-        <v>3.49</v>
+        <v>3.92</v>
       </c>
       <c r="Q32">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="R32">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="S32">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="T32">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="U32">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="V32">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W32">
         <v>1.04</v>
       </c>
       <c r="X32">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y32">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="Z32">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AA32">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB32">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AC32">
-        <v>3.9</v>
+        <v>3.42</v>
       </c>
       <c r="AD32">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE32">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF32">
         <v>1.85</v>
       </c>
       <c r="AG32">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK32">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="O33">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P33">
-        <v>3.86</v>
+        <v>3.71</v>
       </c>
       <c r="Q33">
-        <v>2.48</v>
+        <v>2.76</v>
       </c>
       <c r="R33">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="S33">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="T33">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="U33">
-        <v>3.09</v>
+        <v>3.36</v>
       </c>
       <c r="V33">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W33">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X33">
         <v>1.05</v>
       </c>
       <c r="Y33">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="Z33">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AA33">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AB33">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AC33">
-        <v>3.78</v>
+        <v>3.95</v>
       </c>
       <c r="AD33">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AE33">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF33">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AG33">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AK33">
-        <v>1.88</v>
+        <v>1.69</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O34">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P34">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="Q34">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="R34">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S34">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T34">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="U34">
         <v>2.59</v>
       </c>
       <c r="V34">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W34">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y34">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z34">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="AA34">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB34">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC34">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AD34">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AE34">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF34">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG34">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK34">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,58 +6014,58 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="O35">
         <v>3.4</v>
       </c>
       <c r="P35">
-        <v>4.17</v>
+        <v>4.45</v>
       </c>
       <c r="Q35">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="R35">
         <v>2.07</v>
       </c>
       <c r="S35">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T35">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="U35">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="V35">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W35">
         <v>1.05</v>
       </c>
       <c r="X35">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z35">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AA35">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB35">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC35">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="AD35">
         <v>1.25</v>
       </c>
       <c r="AE35">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF35">
         <v>1.9</v>
@@ -6087,7 +6087,7 @@
         <v>1.14</v>
       </c>
       <c r="AK35">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,31 +6177,31 @@
         </is>
       </c>
       <c r="N36">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O36">
         <v>3</v>
       </c>
       <c r="P36">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q36">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="R36">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S36">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T36">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="U36">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="V36">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W36">
         <v>1.04</v>
@@ -6210,31 +6210,31 @@
         <v>1.05</v>
       </c>
       <c r="Y36">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="Z36">
-        <v>3.04</v>
+        <v>2.59</v>
       </c>
       <c r="AA36">
-        <v>2.05</v>
+        <v>2.37</v>
       </c>
       <c r="AB36">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AC36">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="AD36">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AE36">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF36">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AG36">
-        <v>1.96</v>
+        <v>1.78</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AK36">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,19 +6340,19 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="O37">
         <v>3.1</v>
       </c>
       <c r="P37">
-        <v>2.95</v>
+        <v>3.02</v>
       </c>
       <c r="Q37">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="R37">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="S37">
         <v>1.42</v>
@@ -6361,13 +6361,13 @@
         <v>2.65</v>
       </c>
       <c r="U37">
-        <v>2.99</v>
+        <v>3.17</v>
       </c>
       <c r="V37">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W37">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X37">
         <v>1.06</v>
@@ -6379,19 +6379,19 @@
         <v>2.88</v>
       </c>
       <c r="AA37">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AB37">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC37">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AD37">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE37">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF37">
         <v>1.8</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK37">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6509,55 +6509,55 @@
         <v>3.18</v>
       </c>
       <c r="P38">
-        <v>6.3</v>
+        <v>5.25</v>
       </c>
       <c r="Q38">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="R38">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="S38">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="T38">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="U38">
         <v>3.58</v>
       </c>
       <c r="V38">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="W38">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X38">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Y38">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="Z38">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="AA38">
         <v>2.6</v>
       </c>
       <c r="AB38">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AC38">
-        <v>5.17</v>
+        <v>5.4</v>
       </c>
       <c r="AD38">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE38">
         <v>1.01</v>
       </c>
       <c r="AF38">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AG38">
         <v>1.48</v>
@@ -6666,31 +6666,31 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="O39">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="P39">
-        <v>3.15</v>
+        <v>3.26</v>
       </c>
       <c r="Q39">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="R39">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="S39">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T39">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="U39">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="V39">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="W39">
         <v>1.02</v>
@@ -6699,28 +6699,28 @@
         <v>1.05</v>
       </c>
       <c r="Y39">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z39">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="AA39">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AB39">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AC39">
-        <v>4.89</v>
+        <v>3.4</v>
       </c>
       <c r="AD39">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AE39">
         <v>1.01</v>
       </c>
       <c r="AF39">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AG39">
         <v>1.78</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK39">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AL39">
         <v>0</v>

--- a/jogos_2026-07-27.xlsx
+++ b/jogos_2026-07-27.xlsx
@@ -2242,26 +2242,26 @@
         </is>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
@@ -2326,12 +2326,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["89"]</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34"]</t>
         </is>
       </c>
       <c r="AJ12">
@@ -2344,28 +2344,28 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2408,23 +2408,23 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11", "54"]</t>
         </is>
       </c>
       <c r="AJ13">
@@ -2507,28 +2507,28 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -2580,14 +2580,14 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["72", "86"]</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
@@ -2670,28 +2670,28 @@
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
@@ -2833,28 +2833,28 @@
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2894,26 +2894,26 @@
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "13", "77", "88"]</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
@@ -2996,28 +2996,28 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3057,13 +3057,13 @@
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20"]</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
@@ -3159,28 +3159,28 @@
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
@@ -3322,28 +3322,28 @@
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -3721,14 +3721,14 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51", "68", "86"]</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
@@ -3811,28 +3811,28 @@
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN21">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP21">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -4035,26 +4035,26 @@
         </is>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H23">
         <v>0</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23">
         <v>0</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N23">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["12", "66", "71"]</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
@@ -4137,28 +4137,28 @@
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN23">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         </is>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -4210,14 +4210,14 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24">
         <v>0</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N24">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51"]</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
@@ -4300,28 +4300,28 @@
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN24">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
@@ -4361,26 +4361,26 @@
         </is>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N25">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["41", "90", "90+1"]</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38", "90+4"]</t>
         </is>
       </c>
       <c r="AJ25">
@@ -4463,28 +4463,28 @@
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO25">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP25">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ25">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AR25">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AS25">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AT25">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
@@ -4524,26 +4524,26 @@
         </is>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26">
         <v>0</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N26">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+1"]</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45"]</t>
         </is>
       </c>
       <c r="AJ26">
@@ -4626,28 +4626,28 @@
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO26">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP26">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
@@ -4687,26 +4687,26 @@
         </is>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N27">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["59", "85"]</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["27"]</t>
         </is>
       </c>
       <c r="AJ27">
@@ -4789,28 +4789,28 @@
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP27">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -4865,11 +4865,11 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N28">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["84", "90"]</t>
         </is>
       </c>
       <c r="AJ28">
@@ -4952,28 +4952,28 @@
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO28">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AP28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="O29">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="P29">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="Q29">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="R29">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="S29">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T29">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="U29">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="V29">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="W29">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="X29">
         <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z29">
-        <v>6.29</v>
+        <v>6.51</v>
       </c>
       <c r="AA29">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB29">
-        <v>2.96</v>
+        <v>3.03</v>
       </c>
       <c r="AC29">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AD29">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AE29">
         <v>1.34</v>
       </c>
       <c r="AF29">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AG29">
-        <v>2.38</v>
+        <v>2.81</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AK29">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="O30">
         <v>3.2</v>
@@ -5208,71 +5208,71 @@
         <v>2</v>
       </c>
       <c r="Q30">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="R30">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="S30">
         <v>1.36</v>
       </c>
       <c r="T30">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="U30">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="V30">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W30">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X30">
         <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z30">
-        <v>3.23</v>
+        <v>3</v>
       </c>
       <c r="AA30">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AB30">
+        <v>1.58</v>
+      </c>
+      <c r="AC30">
+        <v>3.45</v>
+      </c>
+      <c r="AD30">
+        <v>1.25</v>
+      </c>
+      <c r="AE30">
+        <v>1.04</v>
+      </c>
+      <c r="AF30">
+        <v>1.82</v>
+      </c>
+      <c r="AG30">
+        <v>1.73</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
         <v>1.75</v>
       </c>
-      <c r="AC30">
-        <v>3.5</v>
-      </c>
-      <c r="AD30">
-        <v>1.22</v>
-      </c>
-      <c r="AE30">
-        <v>1.1</v>
-      </c>
-      <c r="AF30">
-        <v>1.65</v>
-      </c>
-      <c r="AG30">
-        <v>1.95</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.27</v>
-      </c>
       <c r="AK30">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="O31">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="P31">
         <v>3.75</v>
       </c>
       <c r="Q31">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="R31">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="S31">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="T31">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="U31">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="V31">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="W31">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X31">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y31">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="Z31">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="AA31">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="AB31">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AC31">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AD31">
         <v>1.12</v>
       </c>
       <c r="AE31">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF31">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AG31">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AK31">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,65 +5525,65 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="O32">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="P32">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="Q32">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="R32">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="S32">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T32">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="U32">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="V32">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W32">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X32">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z32">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AA32">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AB32">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC32">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="AD32">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE32">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF32">
+        <v>2</v>
+      </c>
+      <c r="AG32">
         <v>1.85</v>
       </c>
-      <c r="AG32">
-        <v>1.95</v>
-      </c>
       <c r="AH32" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK32">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,16 +5688,16 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="O33">
         <v>3.1</v>
       </c>
       <c r="P33">
-        <v>3.71</v>
+        <v>2.98</v>
       </c>
       <c r="Q33">
-        <v>2.76</v>
+        <v>2.85</v>
       </c>
       <c r="R33">
         <v>2</v>
@@ -5706,46 +5706,46 @@
         <v>1.47</v>
       </c>
       <c r="T33">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="U33">
-        <v>3.36</v>
+        <v>3.16</v>
       </c>
       <c r="V33">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W33">
+        <v>1.01</v>
+      </c>
+      <c r="X33">
+        <v>1.08</v>
+      </c>
+      <c r="Y33">
+        <v>1.4</v>
+      </c>
+      <c r="Z33">
+        <v>2.8</v>
+      </c>
+      <c r="AA33">
+        <v>2.3</v>
+      </c>
+      <c r="AB33">
+        <v>1.66</v>
+      </c>
+      <c r="AC33">
+        <v>3.96</v>
+      </c>
+      <c r="AD33">
+        <v>1.22</v>
+      </c>
+      <c r="AE33">
         <v>1.04</v>
       </c>
-      <c r="X33">
-        <v>1.05</v>
-      </c>
-      <c r="Y33">
-        <v>1.41</v>
-      </c>
-      <c r="Z33">
-        <v>2.88</v>
-      </c>
-      <c r="AA33">
-        <v>2.25</v>
-      </c>
-      <c r="AB33">
-        <v>1.61</v>
-      </c>
-      <c r="AC33">
-        <v>3.95</v>
-      </c>
-      <c r="AD33">
-        <v>1.17</v>
-      </c>
-      <c r="AE33">
-        <v>1.02</v>
-      </c>
       <c r="AF33">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AG33">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AK33">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="O35">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P35">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="Q35">
         <v>2.28</v>
@@ -6032,13 +6032,13 @@
         <v>1.4</v>
       </c>
       <c r="T35">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="U35">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="V35">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="W35">
         <v>1.05</v>
@@ -6050,10 +6050,10 @@
         <v>1.33</v>
       </c>
       <c r="Z35">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="AA35">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AB35">
         <v>1.75</v>
@@ -6068,7 +6068,7 @@
         <v>1.09</v>
       </c>
       <c r="AF35">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AG35">
         <v>1.8</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK35">
         <v>2</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="O36">
         <v>3</v>
       </c>
       <c r="P36">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="Q36">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="R36">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="S36">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T36">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="U36">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="V36">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="W36">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X36">
         <v>1.05</v>
       </c>
       <c r="Y36">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="Z36">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="AA36">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="AB36">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AC36">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AD36">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AE36">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF36">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="AG36">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.61</v>
+        <v>1.26</v>
       </c>
       <c r="AK36">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,16 +6340,16 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="O37">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P37">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="Q37">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="R37">
         <v>1.95</v>
@@ -6361,7 +6361,7 @@
         <v>2.65</v>
       </c>
       <c r="U37">
-        <v>3.17</v>
+        <v>2.99</v>
       </c>
       <c r="V37">
         <v>1.35</v>
@@ -6370,34 +6370,34 @@
         <v>1.06</v>
       </c>
       <c r="X37">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z37">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA37">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AB37">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AC37">
-        <v>4</v>
+        <v>3.87</v>
       </c>
       <c r="AD37">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AE37">
         <v>1.07</v>
       </c>
       <c r="AF37">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG37">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6506,61 +6506,61 @@
         <v>1.48</v>
       </c>
       <c r="O38">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="P38">
-        <v>5.25</v>
+        <v>6.14</v>
       </c>
       <c r="Q38">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="R38">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="S38">
         <v>1.56</v>
       </c>
       <c r="T38">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="U38">
         <v>3.58</v>
       </c>
       <c r="V38">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W38">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X38">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y38">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="Z38">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="AA38">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AB38">
         <v>1.5</v>
       </c>
       <c r="AC38">
-        <v>5.4</v>
+        <v>5.23</v>
       </c>
       <c r="AD38">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE38">
         <v>1.01</v>
       </c>
       <c r="AF38">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AG38">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK38">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6675,28 +6675,28 @@
         <v>3.26</v>
       </c>
       <c r="Q39">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="R39">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="S39">
         <v>1.44</v>
       </c>
       <c r="T39">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="U39">
         <v>3.38</v>
       </c>
       <c r="V39">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="W39">
         <v>1.02</v>
       </c>
       <c r="X39">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="Y39">
         <v>1.44</v>
@@ -6708,22 +6708,22 @@
         <v>2.4</v>
       </c>
       <c r="AB39">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AC39">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="AD39">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AE39">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF39">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AG39">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AK39">
         <v>1.58</v>
